--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$P$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$P$206</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Needs Dan'!$A$1:$D$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$P$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Needs Dan'!$A$1:$D$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>13</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>139.05</v>
+        <v>299.05</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>93</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>608.0700000000001</v>
+        <v>768.0700000000001</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>153.82</v>
@@ -7743,7 +7743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P206"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -14661,11 +14661,11 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>0</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
@@ -14690,7 +14690,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2.0 m drawn + 15% margin</t>
+          <t>10.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14707,7 +14707,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -14717,11 +14717,11 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F129" s="3" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
@@ -14732,7 +14732,7 @@
         <v>0</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="J129" s="3" t="inlineStr"/>
       <c r="K129" s="3" t="inlineStr"/>
@@ -14746,7 +14746,7 @@
       </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>8.7 m drawn + 15% margin</t>
+          <t>0.3 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14945,7 +14945,7 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
@@ -14956,13 +14956,13 @@
         <v>0</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="J133" s="3" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>8.1 m drawn + 15% margin</t>
+          <t>21.1 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -15009,11 +15009,11 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
@@ -15038,7 +15038,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>7.3 m drawn + 15% margin</t>
+          <t>1.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -15065,11 +15065,11 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="3" t="inlineStr"/>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>1.4 m drawn + 15% margin</t>
+          <t>5.2 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15111,7 +15111,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -15121,11 +15121,11 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -15136,21 +15136,33 @@
         <v>0</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr"/>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-16</t>
+        </is>
+      </c>
       <c r="M136" s="2" t="inlineStr"/>
-      <c r="N136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2.8 m drawn + 15% margin</t>
+          <t>19.5 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15179,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -15177,11 +15189,11 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F137" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
@@ -15192,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J137" s="3" t="inlineStr"/>
       <c r="K137" s="3" t="inlineStr"/>
@@ -15206,7 +15218,7 @@
       </c>
       <c r="P137" s="3" t="inlineStr">
         <is>
-          <t>1.4 m drawn + 15% margin</t>
+          <t>3.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15235,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -15233,11 +15245,11 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -15248,21 +15260,33 @@
         <v>0</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr"/>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-18</t>
+        </is>
+      </c>
       <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>1.4 m drawn + 15% margin</t>
+          <t>21.6 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15303,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -15289,7 +15313,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F139" s="3" t="n">
@@ -15318,7 +15342,7 @@
       </c>
       <c r="P139" s="3" t="inlineStr">
         <is>
-          <t>2.9 m drawn + 15% margin</t>
+          <t>3.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15359,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -15345,11 +15369,11 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -15360,33 +15384,21 @@
         <v>0</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-16</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr"/>
-      <c r="N140" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="N140" s="2" t="inlineStr"/>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>8.4 m drawn + 15% margin</t>
+          <t>7.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15415,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -15413,11 +15425,11 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F141" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
@@ -15428,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J141" s="3" t="inlineStr"/>
       <c r="K141" s="3" t="inlineStr"/>
@@ -15442,7 +15454,7 @@
       </c>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>2.0 m drawn + 15% margin</t>
+          <t>4.7 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15471,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -15469,11 +15481,11 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -15484,21 +15496,33 @@
         <v>0</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr"/>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-20</t>
+        </is>
+      </c>
       <c r="M142" s="2" t="inlineStr"/>
-      <c r="N142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2.4 m drawn + 15% margin</t>
+          <t>5.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15515,7 +15539,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -15525,11 +15549,11 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F143" s="3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
@@ -15540,7 +15564,7 @@
         <v>0</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr"/>
@@ -15554,7 +15578,7 @@
       </c>
       <c r="P143" s="3" t="inlineStr">
         <is>
-          <t>4.2 m drawn + 15% margin</t>
+          <t>7.3 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15571,7 +15595,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -15581,11 +15605,11 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -15596,7 +15620,7 @@
         <v>0</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
@@ -15610,7 +15634,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>4.1 m drawn + 15% margin</t>
+          <t>6.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15651,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -15637,11 +15661,11 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F145" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
@@ -15652,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J145" s="3" t="inlineStr"/>
       <c r="K145" s="3" t="inlineStr"/>
@@ -15666,7 +15690,7 @@
       </c>
       <c r="P145" s="3" t="inlineStr">
         <is>
-          <t>1.4 m drawn + 15% margin</t>
+          <t>3.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15707,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -15693,11 +15717,11 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, WHITE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -15708,21 +15732,29 @@
         <v>0</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
-      <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
+        </is>
+      </c>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
+        </is>
+      </c>
       <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2.3 m drawn + 15% margin</t>
+          <t>35.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15739,7 +15771,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -15749,11 +15781,11 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 6 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F147" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
@@ -15764,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J147" s="3" t="inlineStr"/>
       <c r="K147" s="3" t="inlineStr"/>
@@ -15778,7 +15810,7 @@
       </c>
       <c r="P147" s="3" t="inlineStr">
         <is>
-          <t>0.4 m drawn + 15% margin</t>
+          <t>2.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15795,7 +15827,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -15805,11 +15837,11 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -15820,33 +15852,21 @@
         <v>0</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K148" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-18</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
       <c r="M148" s="2" t="inlineStr"/>
-      <c r="N148" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="N148" s="2" t="inlineStr"/>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>5.7 m drawn + 15% margin</t>
+          <t>3.2 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15883,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
@@ -15873,11 +15893,11 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="F149" s="3" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
@@ -15888,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J149" s="3" t="inlineStr"/>
       <c r="K149" s="3" t="inlineStr"/>
@@ -15902,7 +15922,7 @@
       </c>
       <c r="P149" s="3" t="inlineStr">
         <is>
-          <t>0.4 m drawn + 15% margin</t>
+          <t>9.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15919,32 +15939,32 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Toyota / Sumitomo</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR SET, TOYOTA, 3 HOUSINGS: 90980-12068 2 POS, 90980-10897 6 POS, 90980-10942 2 POS</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H150" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
@@ -15956,11 +15976,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P150" s="2" t="inlineStr">
-        <is>
-          <t>7.2 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -15975,32 +15991,28 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>Micro ISO relays x4</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>RELAY, PLUG-IN, MICRO ISO, 1 FORM A, 12 VDC COIL</t>
         </is>
       </c>
       <c r="F151" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H151" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J151" s="3" t="inlineStr"/>
       <c r="K151" s="3" t="inlineStr"/>
@@ -16012,11 +16024,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P151" s="3" t="inlineStr">
-        <is>
-          <t>8.3 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -16031,32 +16039,32 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H152" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
@@ -16068,11 +16076,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P152" s="2" t="inlineStr">
-        <is>
-          <t>7.4 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -16087,32 +16091,32 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H153" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="3" t="inlineStr"/>
@@ -16124,11 +16128,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P153" s="3" t="inlineStr">
-        <is>
-          <t>2.6 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -16143,32 +16143,32 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>RL9080-301-F1</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, BLACK, MATES RL00801-50BK</t>
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H154" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
@@ -16180,11 +16180,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P154" s="2" t="inlineStr">
-        <is>
-          <t>4.5 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -16199,32 +16195,32 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, RED, MATES RL00801-50RE</t>
         </is>
       </c>
       <c r="F155" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H155" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I155" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J155" s="3" t="inlineStr"/>
       <c r="K155" s="3" t="inlineStr"/>
@@ -16236,11 +16232,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P155" s="3" t="inlineStr">
-        <is>
-          <t>0.6 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -16255,48 +16247,48 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H156" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
-      <c r="L156" s="2" t="inlineStr"/>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-16-4-STK.html</t>
+        </is>
+      </c>
       <c r="M156" s="2" t="inlineStr"/>
       <c r="N156" s="2" t="inlineStr"/>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P156" s="2" t="inlineStr">
-        <is>
-          <t>3.9 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -16311,48 +16303,48 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="F157" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H157" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J157" s="3" t="inlineStr"/>
       <c r="K157" s="3" t="inlineStr"/>
-      <c r="L157" s="3" t="inlineStr"/>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-16-6-STK.html</t>
+        </is>
+      </c>
       <c r="M157" s="3" t="inlineStr"/>
       <c r="N157" s="3" t="inlineStr"/>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P157" s="3" t="inlineStr">
-        <is>
-          <t>6.3 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -16367,60 +16359,48 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H158" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K158" s="2" t="n">
-        <v>14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-20</t>
+          <t>https://www.te.com/en/product-RNF-100-3-16-9-STK.html</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="N158" s="2" t="inlineStr"/>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
-        </is>
-      </c>
-      <c r="P158" s="2" t="inlineStr">
-        <is>
-          <t>3.5 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -16435,48 +16415,48 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H159" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="J159" s="3" t="inlineStr"/>
       <c r="K159" s="3" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr"/>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-32-4-STK.html</t>
+        </is>
+      </c>
       <c r="M159" s="3" t="inlineStr"/>
       <c r="N159" s="3" t="inlineStr"/>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P159" s="3" t="inlineStr">
-        <is>
-          <t>6.6 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -16491,48 +16471,48 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H160" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J160" s="2" t="inlineStr"/>
       <c r="K160" s="2" t="inlineStr"/>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-32-6-STK.html</t>
+        </is>
+      </c>
       <c r="M160" s="2" t="inlineStr"/>
       <c r="N160" s="2" t="inlineStr"/>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P160" s="2" t="inlineStr">
-        <is>
-          <t>1.1 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -16547,48 +16527,48 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="F161" s="3" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="J161" s="3" t="inlineStr"/>
       <c r="K161" s="3" t="inlineStr"/>
-      <c r="L161" s="3" t="inlineStr"/>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-32-9-STK.html</t>
+        </is>
+      </c>
       <c r="M161" s="3" t="inlineStr"/>
       <c r="N161" s="3" t="inlineStr"/>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P161" s="3" t="inlineStr">
-        <is>
-          <t>8.5 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -16603,48 +16583,48 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>RNF-100-3/8-4-STK</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GREEN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-8-4-STK.html</t>
+        </is>
+      </c>
       <c r="M162" s="2" t="inlineStr"/>
       <c r="N162" s="2" t="inlineStr"/>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P162" s="2" t="inlineStr">
-        <is>
-          <t>8.1 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -16659,48 +16639,48 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>RNF-100-3/8-6-STK</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
         </is>
       </c>
       <c r="F163" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="H163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J163" s="3" t="inlineStr"/>
       <c r="K163" s="3" t="inlineStr"/>
-      <c r="L163" s="3" t="inlineStr"/>
+      <c r="L163" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-RNF-100-3-8-6-STK.html</t>
+        </is>
+      </c>
       <c r="M163" s="3" t="inlineStr"/>
       <c r="N163" s="3" t="inlineStr"/>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P163" s="3" t="inlineStr">
-        <is>
-          <t>1.5 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -16715,32 +16695,32 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Sumitomo / Subaru</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, PLUG, SUMITOMO TS 025, 6 POS, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H164" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
@@ -16752,11 +16732,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P164" s="2" t="inlineStr">
-        <is>
-          <t>5.5 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -16771,48 +16747,48 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
+          <t>TMS-SCE-1/2-2.0-9</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GRAY, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="F165" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H165" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J165" s="3" t="inlineStr"/>
       <c r="K165" s="3" t="inlineStr"/>
-      <c r="L165" s="3" t="inlineStr"/>
+      <c r="L165" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-TMS-SCE-1-2-2.0-9.html</t>
+        </is>
+      </c>
       <c r="M165" s="3" t="inlineStr"/>
       <c r="N165" s="3" t="inlineStr"/>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P165" s="3" t="inlineStr">
-        <is>
-          <t>5.3 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -16827,56 +16803,48 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H166" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
-        </is>
-      </c>
-      <c r="M166" s="4" t="inlineStr">
-        <is>
-          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
-        </is>
-      </c>
+          <t>https://www.te.com/en/product-TMS-SCE-3-16-2.0-9.html</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
       <c r="N166" s="2" t="inlineStr"/>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
-        </is>
-      </c>
-      <c r="P166" s="2" t="inlineStr">
-        <is>
-          <t>8.5 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -16891,48 +16859,48 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 6 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="F167" s="3" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H167" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J167" s="3" t="inlineStr"/>
       <c r="K167" s="3" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr"/>
+      <c r="L167" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-TMS-SCE-3-8-2.0-9.html</t>
+        </is>
+      </c>
       <c r="M167" s="3" t="inlineStr"/>
       <c r="N167" s="3" t="inlineStr"/>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P167" s="3" t="inlineStr">
-        <is>
-          <t>2.0 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -16947,48 +16915,48 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>V23132-A2001-B200</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>RELAY, HIGH CURRENT, TE HCR 150, IP67, 1 FORM A, 130 A AT 85 C, 12 VDC COIL 37 OHM 3.9 W, PARALLEL RESISTOR, STUD LOAD TERMINALS</t>
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H168" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-V23132-A2001-B200.html</t>
+        </is>
+      </c>
       <c r="M168" s="2" t="inlineStr"/>
       <c r="N168" s="2" t="inlineStr"/>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P168" s="2" t="inlineStr">
-        <is>
-          <t>3.2 m drawn + 15% margin</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -17003,32 +16971,28 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>W12P</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WEDGELOCK, DT, 12-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="F169" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H169" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J169" s="3" t="inlineStr"/>
       <c r="K169" s="3" t="inlineStr"/>
@@ -17040,11 +17004,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P169" s="3" t="inlineStr">
-        <is>
-          <t>7.8 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -17059,32 +17019,28 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>W12S</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr"/>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H170" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
@@ -17096,11 +17052,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="P170" s="2" t="inlineStr">
-        <is>
-          <t>2.0 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="P170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -17115,21 +17067,21 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Toyota / Sumitomo</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR SET, TOYOTA, 3 HOUSINGS: 90980-12068 2 POS, 90980-10897 6 POS, 90980-10942 2 POS</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="F171" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
@@ -17140,16 +17092,20 @@
         <v>0</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J171" s="3" t="inlineStr"/>
       <c r="K171" s="3" t="inlineStr"/>
-      <c r="L171" s="3" t="inlineStr"/>
+      <c r="L171" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W2P.html</t>
+        </is>
+      </c>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="inlineStr"/>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P171" s="3" t="inlineStr"/>
@@ -17167,17 +17123,21 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Micro ISO relays x4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr"/>
+          <t>W2S</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>RELAY, PLUG-IN, MICRO ISO, 1 FORM A, 12 VDC COIL</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -17185,19 +17145,23 @@
         </is>
       </c>
       <c r="H172" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="inlineStr"/>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W2S.html</t>
+        </is>
+      </c>
       <c r="M172" s="2" t="inlineStr"/>
       <c r="N172" s="2" t="inlineStr"/>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P172" s="2" t="inlineStr"/>
@@ -17215,21 +17179,21 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>W3P</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
+          <t>WEDGELOCK, DT, 3-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
@@ -17240,16 +17204,20 @@
         <v>0</v>
       </c>
       <c r="I173" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J173" s="3" t="inlineStr"/>
       <c r="K173" s="3" t="inlineStr"/>
-      <c r="L173" s="3" t="inlineStr"/>
+      <c r="L173" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W3P.html</t>
+        </is>
+      </c>
       <c r="M173" s="3" t="inlineStr"/>
       <c r="N173" s="3" t="inlineStr"/>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P173" s="3" t="inlineStr"/>
@@ -17267,17 +17235,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="F174" s="2" t="n">
@@ -17296,12 +17264,16 @@
       </c>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W3S.html</t>
+        </is>
+      </c>
       <c r="M174" s="2" t="inlineStr"/>
       <c r="N174" s="2" t="inlineStr"/>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="P174" s="2" t="inlineStr"/>
@@ -17319,21 +17291,21 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, BLACK, MATES RL00801-50BK</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="F175" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
@@ -17344,16 +17316,20 @@
         <v>0</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J175" s="3" t="inlineStr"/>
       <c r="K175" s="3" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr"/>
+      <c r="L175" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W6P.html</t>
+        </is>
+      </c>
       <c r="M175" s="3" t="inlineStr"/>
       <c r="N175" s="3" t="inlineStr"/>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="P175" s="3" t="inlineStr"/>
@@ -17371,21 +17347,21 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, RED, MATES RL00801-50RE</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -17396,16 +17372,20 @@
         <v>0</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W6S.html</t>
+        </is>
+      </c>
       <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr"/>
@@ -17423,38 +17403,38 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="F177" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H177" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J177" s="3" t="inlineStr"/>
       <c r="K177" s="3" t="inlineStr"/>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-16-4-STK.html</t>
+          <t>https://www.te.com/en/product-W8S.html</t>
         </is>
       </c>
       <c r="M177" s="3" t="inlineStr"/>
@@ -17479,17 +17459,17 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
+          <t>WB-51PAL</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, LEFT</t>
         </is>
       </c>
       <c r="F178" s="2" t="n">
@@ -17497,7 +17477,7 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H178" s="2" t="n">
@@ -17510,14 +17490,14 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-16-6-STK.html</t>
+          <t>https://www.te.com/en/product-WB-51PAL.html</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr"/>
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr"/>
@@ -17535,17 +17515,17 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
+          <t>WB-51PAR</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, RIGHT</t>
         </is>
       </c>
       <c r="F179" s="3" t="n">
@@ -17553,7 +17533,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H179" s="3" t="n">
@@ -17566,7 +17546,7 @@
       <c r="K179" s="3" t="inlineStr"/>
       <c r="L179" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-16-9-STK.html</t>
+          <t>https://www.te.com/en/product-WB-51PAR.html</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr"/>
@@ -17591,38 +17571,38 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
+          <t>WB-51SAL</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>WEDGELOCK, DRB 102/128, PLUG, LEFT</t>
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-32-4-STK.html</t>
+          <t>https://www.te.com/en/product-WB-51SAL.html</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr"/>
@@ -17647,45 +17627,45 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
+          <t>WB-51SAR</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>WEDGELOCK, DRB 102/128, PLUG, RIGHT</t>
         </is>
       </c>
       <c r="F181" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H181" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J181" s="3" t="inlineStr"/>
       <c r="K181" s="3" t="inlineStr"/>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-32-6-STK.html</t>
+          <t>https://www.te.com/en/product-WB-51SAR.html</t>
         </is>
       </c>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="inlineStr"/>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P181" s="3" t="inlineStr"/>
@@ -17703,45 +17683,45 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
+          <t>WM-4S</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H182" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-32-9-STK.html</t>
+          <t>https://www.te.com/en/product-WM-4S.html</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr"/>
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P182" s="2" t="inlineStr"/>
@@ -17759,38 +17739,38 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-4-STK</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="F183" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H183" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J183" s="3" t="inlineStr"/>
       <c r="K183" s="3" t="inlineStr"/>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-RNF-100-3-8-4-STK.html</t>
+          <t>https://www.te.com/en/product-WM-6S.html</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr"/>
@@ -17815,45 +17795,37 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-6-STK</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
+          <t>CABLE, SHIELDED, 1 CONDUCTOR, 22 AWG, WHITE, ETFE (TEFZEL), TINNED COPPER BRAID</t>
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="H184" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-RNF-100-3-8-6-STK.html</t>
-        </is>
-      </c>
+      <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr"/>
       <c r="N184" s="2" t="inlineStr"/>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="P184" s="2" t="inlineStr"/>
@@ -17871,17 +17843,17 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Sumitomo TS 025 6-way</t>
+          <t>jump-post-M8</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Sumitomo / Subaru</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, SUMITOMO TS 025, 6 POS, SOCKET CONTACTS</t>
+          <t>POST, JUMP START, M8, INSULATED</t>
         </is>
       </c>
       <c r="F185" s="3" t="n">
@@ -17910,1156 +17882,8 @@
       </c>
       <c r="P185" s="3" t="inlineStr"/>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E186" s="2" t="inlineStr">
-        <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I186" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J186" s="2" t="inlineStr"/>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-TMS-SCE-1-2-2.0-9.html</t>
-        </is>
-      </c>
-      <c r="M186" s="2" t="inlineStr"/>
-      <c r="N186" s="2" t="inlineStr"/>
-      <c r="O186" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P186" s="2" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="G187" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H187" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I187" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="J187" s="3" t="inlineStr"/>
-      <c r="K187" s="3" t="inlineStr"/>
-      <c r="L187" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-TMS-SCE-3-16-2.0-9.html</t>
-        </is>
-      </c>
-      <c r="M187" s="3" t="inlineStr"/>
-      <c r="N187" s="3" t="inlineStr"/>
-      <c r="O187" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P187" s="3" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I188" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J188" s="2" t="inlineStr"/>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-TMS-SCE-3-8-2.0-9.html</t>
-        </is>
-      </c>
-      <c r="M188" s="2" t="inlineStr"/>
-      <c r="N188" s="2" t="inlineStr"/>
-      <c r="O188" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P188" s="2" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>V23132-A2001-B200</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>RELAY, HIGH CURRENT, TE HCR 150, IP67, 1 FORM A, 130 A AT 85 C, 12 VDC COIL 37 OHM 3.9 W, PARALLEL RESISTOR, STUD LOAD TERMINALS</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G189" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H189" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I189" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J189" s="3" t="inlineStr"/>
-      <c r="K189" s="3" t="inlineStr"/>
-      <c r="L189" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-V23132-A2001-B200.html</t>
-        </is>
-      </c>
-      <c r="M189" s="3" t="inlineStr"/>
-      <c r="N189" s="3" t="inlineStr"/>
-      <c r="O189" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P189" s="3" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>W12P</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr"/>
-      <c r="E190" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 12-WAY RECEPTACLE</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I190" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="2" t="inlineStr"/>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="inlineStr"/>
-      <c r="M190" s="2" t="inlineStr"/>
-      <c r="N190" s="2" t="inlineStr"/>
-      <c r="O190" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P190" s="2" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>W12S</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr"/>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H191" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="3" t="inlineStr"/>
-      <c r="K191" s="3" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr"/>
-      <c r="M191" s="3" t="inlineStr"/>
-      <c r="N191" s="3" t="inlineStr"/>
-      <c r="O191" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P191" s="3" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>W2P</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J192" s="2" t="inlineStr"/>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W2P.html</t>
-        </is>
-      </c>
-      <c r="M192" s="2" t="inlineStr"/>
-      <c r="N192" s="2" t="inlineStr"/>
-      <c r="O192" s="2" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P192" s="2" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>W2S</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="G193" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J193" s="3" t="inlineStr"/>
-      <c r="K193" s="3" t="inlineStr"/>
-      <c r="L193" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
-        </is>
-      </c>
-      <c r="M193" s="3" t="inlineStr"/>
-      <c r="N193" s="3" t="inlineStr"/>
-      <c r="O193" s="3" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P193" s="3" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>W3P</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 3-WAY RECEPTACLE</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J194" s="2" t="inlineStr"/>
-      <c r="K194" s="2" t="inlineStr"/>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W3P.html</t>
-        </is>
-      </c>
-      <c r="M194" s="2" t="inlineStr"/>
-      <c r="N194" s="2" t="inlineStr"/>
-      <c r="O194" s="2" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P194" s="2" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>W3S</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J195" s="3" t="inlineStr"/>
-      <c r="K195" s="3" t="inlineStr"/>
-      <c r="L195" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
-        </is>
-      </c>
-      <c r="M195" s="3" t="inlineStr"/>
-      <c r="N195" s="3" t="inlineStr"/>
-      <c r="O195" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P195" s="3" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>W6P</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J196" s="2" t="inlineStr"/>
-      <c r="K196" s="2" t="inlineStr"/>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W6P.html</t>
-        </is>
-      </c>
-      <c r="M196" s="2" t="inlineStr"/>
-      <c r="N196" s="2" t="inlineStr"/>
-      <c r="O196" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P196" s="2" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>W6S</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H197" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I197" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J197" s="3" t="inlineStr"/>
-      <c r="K197" s="3" t="inlineStr"/>
-      <c r="L197" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W6S.html</t>
-        </is>
-      </c>
-      <c r="M197" s="3" t="inlineStr"/>
-      <c r="N197" s="3" t="inlineStr"/>
-      <c r="O197" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P197" s="3" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>W8S</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I198" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J198" s="2" t="inlineStr"/>
-      <c r="K198" s="2" t="inlineStr"/>
-      <c r="L198" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W8S.html</t>
-        </is>
-      </c>
-      <c r="M198" s="2" t="inlineStr"/>
-      <c r="N198" s="2" t="inlineStr"/>
-      <c r="O198" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P198" s="2" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>WB-51PAL</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, LEFT</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I199" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J199" s="3" t="inlineStr"/>
-      <c r="K199" s="3" t="inlineStr"/>
-      <c r="L199" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WB-51PAL.html</t>
-        </is>
-      </c>
-      <c r="M199" s="3" t="inlineStr"/>
-      <c r="N199" s="3" t="inlineStr"/>
-      <c r="O199" s="3" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P199" s="3" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>WB-51PAR</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, RIGHT</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I200" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J200" s="2" t="inlineStr"/>
-      <c r="K200" s="2" t="inlineStr"/>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WB-51PAR.html</t>
-        </is>
-      </c>
-      <c r="M200" s="2" t="inlineStr"/>
-      <c r="N200" s="2" t="inlineStr"/>
-      <c r="O200" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P200" s="2" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>WB-51SAL</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DRB 102/128, PLUG, LEFT</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H201" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I201" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J201" s="3" t="inlineStr"/>
-      <c r="K201" s="3" t="inlineStr"/>
-      <c r="L201" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WB-51SAL.html</t>
-        </is>
-      </c>
-      <c r="M201" s="3" t="inlineStr"/>
-      <c r="N201" s="3" t="inlineStr"/>
-      <c r="O201" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P201" s="3" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>WB-51SAR</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DRB 102/128, PLUG, RIGHT</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J202" s="2" t="inlineStr"/>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WB-51SAR.html</t>
-        </is>
-      </c>
-      <c r="M202" s="2" t="inlineStr"/>
-      <c r="N202" s="2" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P202" s="2" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>WM-4S</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J203" s="3" t="inlineStr"/>
-      <c r="K203" s="3" t="inlineStr"/>
-      <c r="L203" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WM-4S.html</t>
-        </is>
-      </c>
-      <c r="M203" s="3" t="inlineStr"/>
-      <c r="N203" s="3" t="inlineStr"/>
-      <c r="O203" s="3" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P203" s="3" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J204" s="2" t="inlineStr"/>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WM-6S.html</t>
-        </is>
-      </c>
-      <c r="M204" s="2" t="inlineStr"/>
-      <c r="N204" s="2" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="P204" s="2" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr"/>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>CABLE, SHIELDED, 1 CONDUCTOR, 22 AWG, WHITE, ETFE (TEFZEL), TINNED COPPER BRAID</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H205" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I205" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="3" t="inlineStr"/>
-      <c r="K205" s="3" t="inlineStr"/>
-      <c r="L205" s="3" t="inlineStr"/>
-      <c r="M205" s="3" t="inlineStr"/>
-      <c r="N205" s="3" t="inlineStr"/>
-      <c r="O205" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P205" s="3" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>jump-post-M8</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>POST, JUMP START, M8, INSULATED</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I206" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J206" s="2" t="inlineStr"/>
-      <c r="K206" s="2" t="inlineStr"/>
-      <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="2" t="inlineStr"/>
-      <c r="N206" s="2" t="inlineStr"/>
-      <c r="O206" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="P206" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P206"/>
+  <autoFilter ref="A1:P185"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
@@ -19126,36 +17950,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M166" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -19168,7 +17992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21011,7 +19835,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -21033,7 +19857,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -21121,7 +19945,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -21143,7 +19967,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -21165,7 +19989,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -21187,7 +20011,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -21209,7 +20033,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -21231,7 +20055,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -21253,7 +20077,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -21275,7 +20099,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -21297,7 +20121,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -21319,7 +20143,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -21341,7 +20165,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -21363,7 +20187,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -21385,7 +20209,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -21395,7 +20219,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -21407,7 +20231,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -21417,7 +20241,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21429,7 +20253,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -21439,7 +20263,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21451,7 +20275,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>RL9080-301-F1</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -21461,7 +20285,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21473,7 +20297,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -21483,7 +20307,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21495,17 +20319,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21517,17 +20341,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21539,17 +20363,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21561,17 +20385,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21583,17 +20407,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21605,17 +20429,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21627,17 +20451,17 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>RNF-100-3/8-4-STK</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21649,17 +20473,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>RNF-100-3/8-6-STK</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21671,7 +20495,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -21681,7 +20505,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21693,17 +20517,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>TMS-SCE-1/2-2.0-9</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21715,17 +20539,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21737,17 +20561,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21759,17 +20583,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
+          <t>V23132-A2001-B200</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21781,17 +20605,17 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21803,17 +20627,17 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21825,17 +20649,17 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21847,17 +20671,17 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21869,12 +20693,12 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>WB-51PAR</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -21891,12 +20715,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>WB-51SAL</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -21913,12 +20737,12 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -21935,7 +20759,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>jump-post-M8</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -21949,470 +20773,8 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>RNF-100-3/16-4-STK</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>RNF-100-3/16-6-STK</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>RNF-100-3/16-9-STK</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>RNF-100-3/32-4-STK</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>RNF-100-3/32-6-STK</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>RNF-100-3/32-9-STK</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>RNF-100-3/8-4-STK</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>RNF-100-3/8-6-STK</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Sumitomo TS 025 6-way</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>V23132-A2001-B200</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>W3S</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>W6P</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>W6S</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>W8S</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>WB-51PAR</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>WB-51SAL</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>jump-post-M8</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D147"/>
+  <autoFilter ref="A1:D126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Needs Dan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="To do" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$P$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$P$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Needs Dan'!$A$1:$D$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -476,7 +476,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>of which printed-material est. USD</t>
+          <t>lines at $0 (made at work / not priced)</t>
         </is>
       </c>
     </row>
@@ -524,13 +524,13 @@
         <v>103</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>469.02</v>
+        <v>309.07</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>153.82</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -546,13 +546,13 @@
         <v>153</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>299.05</v>
+        <v>360.93</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -568,13 +568,13 @@
         <v>256</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>768.0700000000001</v>
+        <v>670</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>153.82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -1093,16 +1093,16 @@
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19.04</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>19.04</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1153,16 +1153,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1972,14 +1972,22 @@
       <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>made at work (Dan, R210)</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>machined to the drawing (stock supplier not chosen)</t>
+          <t>machined to the drawing (R210: made at work, no buy link)</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2512,14 +2520,22 @@
       <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>made at work (Dan, R210)</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>machined to the drawing (stock supplier not chosen)</t>
+          <t>machined to the drawing (R210: made at work, no buy link)</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr"/>
@@ -2564,14 +2580,22 @@
       <c r="I33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="3" t="inlineStr"/>
       <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>made at work (Dan, R210)</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>machined to the drawing (stock supplier not chosen)</t>
+          <t>machined to the drawing (R210: made at work, no buy link)</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -2634,7 +2658,7 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Mouser qty 1 per TRUSTED-SOURCES 2026-10-18 (TE page distributor panel)</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -2685,10 +2709,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>5.5</v>
+        <v>2.2</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
@@ -2698,7 +2722,7 @@
       <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Mouser qty 22+ per TRUSTED-SOURCES 2026-10-18 (TE page distributor panel)</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
@@ -3797,16 +3821,16 @@
         <v>1</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>40.8</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>40.8</v>
+        <v>0</v>
       </c>
       <c r="L53" s="3" t="inlineStr"/>
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
@@ -3857,16 +3881,16 @@
         <v>1</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>10.31</v>
+        <v>0</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>10.31</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -3917,16 +3941,16 @@
         <v>1</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
@@ -4998,7 +5022,7 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Mouser qty 1 per TRUSTED-SOURCES 2026-10-18 (TE page distributor panel)</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -5049,10 +5073,10 @@
         <v>2</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
@@ -5062,7 +5086,7 @@
       <c r="M73" s="3" t="inlineStr"/>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Mouser qty 22+ per TRUSTED-SOURCES 2026-10-18 (TE page distributor panel)</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
@@ -6325,16 +6349,16 @@
         <v>1</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>36.16</v>
+        <v>0</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>36.16</v>
+        <v>0</v>
       </c>
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
@@ -6385,16 +6409,16 @@
         <v>1</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -6445,16 +6469,16 @@
         <v>1</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>12.04</v>
+        <v>0</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>12.04</v>
+        <v>0</v>
       </c>
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O95" s="3" t="inlineStr">
@@ -6505,16 +6529,16 @@
         <v>1</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>est (printed material)</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -6564,12 +6588,8 @@
       <c r="I97" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J97" s="3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>2.53</v>
-      </c>
+      <c r="J97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="inlineStr"/>
       <c r="L97" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-1-4-0-STK.html</t>
@@ -7576,14 +7596,22 @@
       <c r="I114" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J114" s="2" t="inlineStr"/>
-      <c r="K114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>made at work (Dan, R210)</t>
+        </is>
+      </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>machined to the drawing (stock supplier not chosen)</t>
+          <t>machined to the drawing (R210: made at work, no buy link)</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr"/>
@@ -7628,11 +7656,19 @@
       <c r="I115" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J115" s="3" t="inlineStr"/>
-      <c r="K115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L115" s="3" t="inlineStr"/>
       <c r="M115" s="3" t="inlineStr"/>
-      <c r="N115" s="3" t="inlineStr"/>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
+          <t>made at work (Dan, R210)</t>
+        </is>
+      </c>
       <c r="O115" s="3" t="inlineStr">
         <is>
           <t>printed on Dan's PA12 printer (R82: no buy link)</t>
@@ -8580,7 +8616,7 @@
       <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Mouser qty 1 per TRUSTED-SOURCES 2026-10-18 (TE page distributor panel)</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -8631,10 +8667,10 @@
         <v>24</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -8644,7 +8680,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Mouser qty 22+ per TRUSTED-SOURCES 2026-10-18 (TE page distributor panel)</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12930,18 +12966,26 @@
       <c r="I95" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J95" s="3" t="inlineStr"/>
-      <c r="K95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>3.35</v>
+      </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-2P.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-2P/6566582</t>
         </is>
       </c>
       <c r="M95" s="3" t="inlineStr"/>
-      <c r="N95" s="3" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr"/>
@@ -12986,18 +13030,26 @@
       <c r="I96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="2" t="inlineStr"/>
-      <c r="K96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.96</v>
+      </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-3P.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-3P/6566583</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr"/>
@@ -13042,18 +13094,26 @@
       <c r="I97" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J97" s="3" t="inlineStr"/>
-      <c r="K97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>4.68</v>
+      </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-6P.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-6P/6566585</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr"/>
-      <c r="N97" s="3" t="inlineStr"/>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr"/>
@@ -13098,15 +13158,23 @@
       <c r="I98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2.34</v>
+      </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-DT04-6P-CE03.html</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>family price (DT04-6P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>te.com page opened 2026-10-19</t>
@@ -13154,18 +13222,26 @@
       <c r="I99" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J99" s="3" t="inlineStr"/>
-      <c r="K99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>7.62</v>
+      </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-08SA.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr"/>
-      <c r="N99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P99" s="3" t="inlineStr"/>
@@ -13258,18 +13334,26 @@
       <c r="I101" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="3" t="inlineStr"/>
-      <c r="K101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.77</v>
+      </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-2S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
         </is>
       </c>
       <c r="M101" s="3" t="inlineStr"/>
-      <c r="N101" s="3" t="inlineStr"/>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P101" s="3" t="inlineStr"/>
@@ -13314,15 +13398,23 @@
       <c r="I102" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J102" s="2" t="inlineStr"/>
-      <c r="K102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>6.16</v>
+      </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
           <t>te.com page opened 2026-10-19</t>
@@ -13418,18 +13510,26 @@
       <c r="I104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2.06</v>
+      </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-3S-CE05.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr"/>
@@ -13474,18 +13574,26 @@
       <c r="I105" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J105" s="3" t="inlineStr"/>
-      <c r="K105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>5.04</v>
+      </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-6S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr"/>
-      <c r="N105" s="3" t="inlineStr"/>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P105" s="3" t="inlineStr"/>
@@ -13530,18 +13638,26 @@
       <c r="I106" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>2.68</v>
+      </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-6S-CE05.html</t>
+          <t>https://www.digikey.com/en/products/detail/wee/DT06-6S-CE05/29360522</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key listing opened 2026-10-19 (reseller "wee", not TE direct)</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr"/>
@@ -13586,18 +13702,26 @@
       <c r="I107" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J107" s="3" t="inlineStr"/>
-      <c r="K107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>13.92</v>
+      </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DTHD06-1-8S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr"/>
-      <c r="N107" s="3" t="inlineStr"/>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P107" s="3" t="inlineStr"/>
@@ -16170,14 +16294,26 @@
       <c r="I154" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL9080-301-F1/16271602</t>
+        </is>
+      </c>
       <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr"/>
@@ -16274,15 +16410,23 @@
       <c r="I156" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J156" s="2" t="inlineStr"/>
-      <c r="K156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-16-4-STK.html</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr"/>
-      <c r="N156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16330,15 +16474,23 @@
       <c r="I157" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J157" s="3" t="inlineStr"/>
-      <c r="K157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L157" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-16-6-STK.html</t>
         </is>
       </c>
       <c r="M157" s="3" t="inlineStr"/>
-      <c r="N157" s="3" t="inlineStr"/>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16386,15 +16538,23 @@
       <c r="I158" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="2" t="inlineStr"/>
-      <c r="K158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-16-9-STK.html</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr"/>
-      <c r="N158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16442,15 +16602,23 @@
       <c r="I159" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J159" s="3" t="inlineStr"/>
-      <c r="K159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-32-4-STK.html</t>
         </is>
       </c>
       <c r="M159" s="3" t="inlineStr"/>
-      <c r="N159" s="3" t="inlineStr"/>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O159" s="3" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16498,15 +16666,23 @@
       <c r="I160" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-32-6-STK.html</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr"/>
-      <c r="N160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16554,15 +16730,23 @@
       <c r="I161" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J161" s="3" t="inlineStr"/>
-      <c r="K161" s="3" t="inlineStr"/>
+      <c r="J161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L161" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-32-9-STK.html</t>
         </is>
       </c>
       <c r="M161" s="3" t="inlineStr"/>
-      <c r="N161" s="3" t="inlineStr"/>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O161" s="3" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16610,15 +16794,23 @@
       <c r="I162" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J162" s="2" t="inlineStr"/>
-      <c r="K162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-8-4-STK.html</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr"/>
-      <c r="N162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16666,15 +16858,23 @@
       <c r="I163" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J163" s="3" t="inlineStr"/>
-      <c r="K163" s="3" t="inlineStr"/>
+      <c r="J163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L163" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-RNF-100-3-8-6-STK.html</t>
         </is>
       </c>
       <c r="M163" s="3" t="inlineStr"/>
-      <c r="N163" s="3" t="inlineStr"/>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O163" s="3" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16774,15 +16974,23 @@
       <c r="I165" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="J165" s="3" t="inlineStr"/>
-      <c r="K165" s="3" t="inlineStr"/>
+      <c r="J165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L165" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-TMS-SCE-1-2-2.0-9.html</t>
         </is>
       </c>
       <c r="M165" s="3" t="inlineStr"/>
-      <c r="N165" s="3" t="inlineStr"/>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16830,15 +17038,23 @@
       <c r="I166" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="J166" s="2" t="inlineStr"/>
-      <c r="K166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-TMS-SCE-3-16-2.0-9.html</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr"/>
-      <c r="N166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -16886,15 +17102,23 @@
       <c r="I167" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="J167" s="3" t="inlineStr"/>
-      <c r="K167" s="3" t="inlineStr"/>
+      <c r="J167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L167" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-TMS-SCE-3-8-2.0-9.html</t>
         </is>
       </c>
       <c r="M167" s="3" t="inlineStr"/>
-      <c r="N167" s="3" t="inlineStr"/>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="O167" s="3" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -17094,18 +17318,26 @@
       <c r="I171" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J171" s="3" t="inlineStr"/>
-      <c r="K171" s="3" t="inlineStr"/>
+      <c r="J171" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K171" s="3" t="n">
+        <v>0.65</v>
+      </c>
       <c r="L171" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2P.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr"/>
-      <c r="N171" s="3" t="inlineStr"/>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="P171" s="3" t="inlineStr"/>
@@ -17150,15 +17382,23 @@
       <c r="I172" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J172" s="2" t="inlineStr"/>
-      <c r="K172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>1.43</v>
+      </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-W2S.html</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr"/>
-      <c r="N172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
           <t>te.com page opened 2026-10-19</t>
@@ -17206,15 +17446,23 @@
       <c r="I173" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J173" s="3" t="inlineStr"/>
-      <c r="K173" s="3" t="inlineStr"/>
+      <c r="J173" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K173" s="3" t="n">
+        <v>0.13</v>
+      </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-W3P.html</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr"/>
-      <c r="N173" s="3" t="inlineStr"/>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="O173" s="3" t="inlineStr">
         <is>
           <t>te.com page opened 2026-10-19</t>
@@ -17262,15 +17510,23 @@
       <c r="I174" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J174" s="2" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>0.26</v>
+      </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
           <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr"/>
-      <c r="N174" s="2" t="inlineStr"/>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -17955,31 +18211,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -17992,7 +18249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D126"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18251,12 +18508,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-1/4-0-STK</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -18273,12 +18530,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>50M060100P030</t>
+          <t>6-1419137-4</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -18295,17 +18552,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ISO 10642 M3 x 12 A2</t>
+          <t>RNF-100-1/4-0-STK</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -18317,7 +18574,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>50M060100P030</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -18339,7 +18596,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>ISO 10642 M3 x 12 A2</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -18349,7 +18606,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -18361,7 +18618,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Lemu 2990806014</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -18383,7 +18640,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>N0674-70 2-039</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -18400,12 +18657,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Wire harness</t>
+          <t>Mechanical assemblies</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>1.8k 1/4W</t>
+          <t>Lemu 2990806014</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -18415,19 +18672,19 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Wire harness</t>
+          <t>Mechanical assemblies</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>10k 1/4W</t>
+          <t>N0674-70 2-039</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -18437,7 +18694,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -18449,12 +18706,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>0413-204-2005</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -18471,12 +18728,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>120R 1/4W</t>
+          <t>0413-214-1205</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -18493,12 +18750,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>12110293</t>
+          <t>0462-201-16141</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -18515,12 +18772,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>0462-201-2031</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -18537,7 +18794,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>1.8k 1/4W</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -18547,7 +18804,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18816,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>10k 1/4W</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -18569,7 +18826,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -18581,12 +18838,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>1N5822</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -18603,17 +18860,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1k 1/4W</t>
+          <t>12084200</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Waytek listing seen 2026-10-19 (100 pc min, 0 stock; Aptiv sheet not checked)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -18625,7 +18882,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>120R 1/4W</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -18635,7 +18892,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18904,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>3.9k 1/4W</t>
+          <t>12110293</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -18657,7 +18914,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -18669,12 +18926,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>301A011-25-0</t>
+          <t>12191819</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -18691,12 +18948,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>301A022-25-0</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -18713,12 +18970,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>301A028-25-0</t>
+          <t>15419715</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -18735,12 +18992,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>342A012-25-0</t>
+          <t>1N5822</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -18757,17 +19014,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>342A024-25-0</t>
+          <t>1k 1/4W</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -18779,17 +19036,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>342A034-25-0</t>
+          <t>2.2k 1/4W 1%</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -18801,12 +19058,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>342A048-25-0</t>
+          <t>280919-2</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -18823,17 +19080,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>382A012-25-0</t>
+          <t>3.9k 1/4W</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -18845,7 +19102,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>382A023-25-0</t>
+          <t>301A011-25-0</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -18867,7 +19124,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>382A034-25-0</t>
+          <t>301A022-25-0</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -18889,12 +19146,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>3R5</t>
+          <t>301A028-25-0</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -18911,12 +19168,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>462A023-25-0</t>
+          <t>320238</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -18933,17 +19190,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>470R 1/4W</t>
+          <t>320575</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -18955,12 +19212,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>342A012-25-0</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -18977,12 +19234,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>342A024-25-0</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -18999,12 +19256,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>880014175</t>
+          <t>342A034-25-0</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -19021,17 +19278,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>342A048-25-0</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19043,17 +19300,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>90980-11062</t>
+          <t>382A012-25-0</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19065,17 +19322,17 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>382A023-25-0</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19087,17 +19344,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>382A034-25-0</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19109,7 +19366,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>3R5</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -19119,7 +19376,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19131,17 +19388,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ANL/MEGA 300A + holder</t>
+          <t>462A023-25-0</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19153,7 +19410,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>470R 1/4W</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -19163,7 +19420,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19432,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -19185,7 +19442,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19197,17 +19454,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>6-1419137-4</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19476,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -19229,7 +19486,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19498,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>BDK 2.8</t>
+          <t>880014175</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -19263,17 +19520,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-0-SP</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -19285,17 +19542,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>90980-11062</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -19307,17 +19564,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1/2-0-SP</t>
+          <t>90980-11143</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -19329,17 +19586,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1/4-0-SP</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -19351,17 +19608,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>DR-25-2-0-SP</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -19373,17 +19630,17 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/16-0-SP</t>
+          <t>ANL/MEGA 300A + holder</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19395,17 +19652,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/4-0-SP</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -19417,17 +19674,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/8-0-SP</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -19439,7 +19696,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GENERIC CRIMP SPLICE 14-10</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -19449,7 +19706,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -19461,7 +19718,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>GENERIC FLYING LEAD</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -19471,7 +19728,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -19483,7 +19740,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
+          <t>BDK 2.8</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -19493,7 +19750,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19505,17 +19762,17 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 2AWG</t>
+          <t>DR-25-1-0-SP</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19527,17 +19784,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 4AWG</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19549,17 +19806,17 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 50MM2</t>
+          <t>DR-25-1/2-0-SP</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19571,17 +19828,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 8AWG</t>
+          <t>DR-25-1/4-0-SP</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19593,17 +19850,17 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 2AWG</t>
+          <t>DR-25-2-0-SP</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19615,17 +19872,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 4AWG</t>
+          <t>DR-25-3/16-0-SP</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19637,17 +19894,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 8AWG</t>
+          <t>DR-25-3/4-0-SP</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19659,17 +19916,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 12-10</t>
+          <t>DR-25-3/8-0-SP</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19681,17 +19938,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 22-16</t>
+          <t>DRB12-102PAE-L018</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19703,17 +19960,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M8 22-16</t>
+          <t>DRB16-102SAE-L018</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19725,17 +19982,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>GENERIC SOLDER SPLICE</t>
+          <t>DRBF-1A</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19747,17 +20004,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>GENERIC SPADE RECEPTACLE 12-10</t>
+          <t>DT04-08PA-P021</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19769,12 +20026,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>DT04-12PA-P021</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -19791,7 +20048,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Jump lugs 1/0</t>
+          <t>GENERIC CRIMP SPLICE 14-10</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -19813,7 +20070,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>GENERIC FLYING LEAD</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -19823,7 +20080,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19835,7 +20092,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -19845,7 +20102,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19857,7 +20114,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>GENERIC LUG M10 2AWG</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -19867,7 +20124,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19879,7 +20136,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>GENERIC LUG M10 4AWG</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -19889,7 +20146,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19901,7 +20158,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>GENERIC LUG M10 50MM2</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -19911,7 +20168,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19923,7 +20180,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>GENERIC LUG M10 8AWG</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -19933,7 +20190,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19945,7 +20202,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>GENERIC LUG M8 2AWG</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -19955,7 +20212,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19967,7 +20224,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>GENERIC LUG M8 4AWG</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -19977,7 +20234,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19989,7 +20246,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>GENERIC LUG M8 8AWG</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -19999,7 +20256,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20268,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>GENERIC RING M6 12-10</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -20021,7 +20278,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20290,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>GENERIC RING M6 22-16</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -20043,7 +20300,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20055,7 +20312,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>GENERIC RING M8 22-16</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -20065,7 +20322,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20334,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>GENERIC SOLDER SPLICE</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -20087,7 +20344,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20099,7 +20356,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>GENERIC SPADE RECEPTACLE 12-10</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -20109,7 +20366,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20121,17 +20378,17 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20143,7 +20400,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>Jump lugs 1/0</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -20153,7 +20410,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20165,7 +20422,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -20175,7 +20432,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20187,7 +20444,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -20209,7 +20466,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -20219,7 +20476,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20231,7 +20488,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -20241,7 +20498,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20253,7 +20510,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -20263,7 +20520,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20275,7 +20532,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>RL9080-301-F1</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -20285,7 +20542,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20297,7 +20554,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -20307,7 +20564,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20319,17 +20576,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20341,17 +20598,17 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20363,17 +20620,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20385,17 +20642,17 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20407,17 +20664,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20429,17 +20686,17 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20451,17 +20708,17 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-4-STK</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20473,17 +20730,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-6-STK</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20495,17 +20752,17 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo TS 025 6-way</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20517,17 +20774,17 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20539,17 +20796,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20561,17 +20818,17 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20583,17 +20840,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>V23132-A2001-B200</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20605,12 +20862,12 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -20627,12 +20884,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -20649,12 +20906,12 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -20671,12 +20928,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -20693,7 +20950,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>WB-51PAR</t>
+          <t>V23132-A2001-B200</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -20715,7 +20972,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>WB-51SAL</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -20737,7 +20994,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -20759,22 +21016,176 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
+          <t>W8S</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>WB-51PAL</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>WB-51PAR</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>WB-51SAL</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>WB-51SAR</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>WM-6S</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
           <t>jump-post-M8</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D126"/>
+  <autoFilter ref="A1:D133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$183</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>360.93</v>
+        <v>355.91</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>11</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>670</v>
+        <v>664.98</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>25</v>
@@ -7974,7 +7974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q185"/>
+  <dimension ref="A1:Q183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>DT04-6P-CE03</t>
+          <t>DT06-08SA</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -13459,11 +13459,11 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 6 POS, PIN CONTACTS, E SEAL, INSUL 1.35-3.05 MM, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -13474,28 +13474,28 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.34</v>
+        <v>3.81</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2.34</v>
+        <v>7.62</v>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-6P-CE03.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>family price (DT04-6P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -13513,22 +13513,14 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>DT06-08SA</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DT06-12SA</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
@@ -13540,31 +13532,19 @@
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="L99" s="3" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="M99" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
+      <c r="M99" s="3" t="inlineStr"/>
       <c r="N99" s="3" t="inlineStr"/>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -13582,18 +13562,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>DT06-12SA</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+          <t>DT06-2S</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -13604,16 +13588,28 @@
         <v>2</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -13631,7 +13627,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>DT06-2S</t>
+          <t>DT06-2S-CE05</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -13639,14 +13635,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr"/>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
@@ -13654,31 +13654,31 @@
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0.77</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.77</v>
+        <v>6.16</v>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
+          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr"/>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr"/>
@@ -13696,26 +13696,18 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>DT06-2S-CE05</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DT06-3S</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -13723,31 +13715,19 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="M102" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
+      <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
@@ -13765,14 +13745,22 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>DT06-3S</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr"/>
-      <c r="E103" s="3" t="inlineStr"/>
+          <t>DT06-3S-CE05</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
@@ -13784,19 +13772,31 @@
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
+        </is>
+      </c>
       <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="3" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr"/>
@@ -13814,26 +13814,22 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>DT06-3S-CE05</t>
+          <t>DT06-6S</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -13844,17 +13840,17 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2.06</v>
+        <v>5.04</v>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
@@ -13883,7 +13879,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>DT06-6S</t>
+          <t>DTHD06-1-8S</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -13891,14 +13887,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -13909,17 +13909,17 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>2.52</v>
+        <v>3.48</v>
       </c>
       <c r="L105" s="3" t="n">
-        <v>5.04</v>
+        <v>13.92</v>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr"/>
@@ -13948,22 +13948,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>DT06-6S-CE05</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DTM06-4S</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
@@ -13975,31 +13967,19 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="M106" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/wee/DT06-6S-CE05/29360522</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key listing opened 2026-10-19 (reseller "wee", not TE direct)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>
@@ -14017,26 +13997,18 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>DTHD06-1-8S</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DTM06-6S</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
+          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -14044,31 +14016,19 @@
         </is>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K107" s="3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="L107" s="3" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q107" s="3" t="inlineStr"/>
@@ -14086,18 +14046,22 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>DTM06-4S</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>GENERIC CRIMP SPLICE 14-10</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
+          <t>SPLICE, CRIMP, UNINSULATED, COPPER, TINNED, COMBINED 14-10 AWG, ADHESIVE HEATSHRINK OVER</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -14105,10 +14069,10 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
@@ -14135,18 +14099,22 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>DTM06-6S</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr"/>
+          <t>GENERIC FLYING LEAD</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
+          <t>TERMINAL, FLYING LEAD</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -14154,10 +14122,10 @@
         </is>
       </c>
       <c r="I109" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="K109" s="3" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr"/>
@@ -14184,7 +14152,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>GENERIC CRIMP SPLICE 14-10</t>
+          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -14195,7 +14163,7 @@
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>SPLICE, CRIMP, UNINSULATED, COPPER, TINNED, COMBINED 14-10 AWG, ADHESIVE HEATSHRINK OVER</t>
+          <t>TERMINAL, FLYING LEAD, HEAVY</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -14237,7 +14205,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>GENERIC FLYING LEAD</t>
+          <t>GENERIC LUG M10 2AWG</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -14248,11 +14216,11 @@
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, FLYING LEAD</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -14263,7 +14231,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="K111" s="3" t="inlineStr"/>
       <c r="L111" s="3" t="inlineStr"/>
@@ -14290,7 +14258,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
+          <t>GENERIC LUG M10 4AWG</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -14301,11 +14269,11 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, FLYING LEAD, HEAVY</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -14316,7 +14284,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
@@ -14343,7 +14311,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 2AWG</t>
+          <t>GENERIC LUG M10 50MM2</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -14354,11 +14322,11 @@
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 50 MM2 (1/0) BARREL, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -14369,7 +14337,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr"/>
@@ -14396,7 +14364,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 4AWG</t>
+          <t>GENERIC LUG M10 8AWG</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -14407,7 +14375,7 @@
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
@@ -14449,7 +14417,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 50MM2</t>
+          <t>GENERIC LUG M8 2AWG</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -14460,11 +14428,11 @@
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 50 MM2 (1/0) BARREL, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -14475,7 +14443,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K115" s="3" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr"/>
@@ -14502,7 +14470,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 8AWG</t>
+          <t>GENERIC LUG M8 4AWG</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -14513,7 +14481,7 @@
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
@@ -14555,7 +14523,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 2AWG</t>
+          <t>GENERIC LUG M8 8AWG</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -14566,11 +14534,11 @@
       <c r="E117" s="3" t="inlineStr"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -14581,7 +14549,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K117" s="3" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr"/>
@@ -14608,7 +14576,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 4AWG</t>
+          <t>GENERIC RING M6 12-10</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -14619,11 +14587,11 @@
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 12-10 AWG</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -14634,7 +14602,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
@@ -14661,7 +14629,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 8AWG</t>
+          <t>GENERIC RING M6 22-16</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -14672,11 +14640,11 @@
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 22-16 AWG</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -14687,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr"/>
@@ -14714,7 +14682,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 12-10</t>
+          <t>GENERIC RING M8 22-16</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14725,11 +14693,11 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 12-10 AWG</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 22-16 AWG</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -14740,7 +14708,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
@@ -14767,7 +14735,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 22-16</t>
+          <t>GENERIC SOLDER SPLICE</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -14778,11 +14746,11 @@
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 22-16 AWG</t>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
@@ -14793,7 +14761,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="K121" s="3" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr"/>
@@ -14820,7 +14788,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M8 22-16</t>
+          <t>GENERIC SPADE RECEPTACLE 12-10</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -14831,11 +14799,11 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 22-16 AWG</t>
+          <t>TERMINAL, QUICK CONNECT, RECEPTACLE, INSULATED, 6.3 MM (250) TAB, 12-10 AWG</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -14846,7 +14814,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
@@ -14873,22 +14841,22 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>GENERIC SOLDER SPLICE</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -14899,7 +14867,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr"/>
@@ -14908,7 +14876,7 @@
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr"/>
@@ -14926,7 +14894,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>GENERIC SPADE RECEPTACLE 12-10</t>
+          <t>Jump lugs 1/0</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -14937,11 +14905,11 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, QUICK CONNECT, RECEPTACLE, INSULATED, 6.3 MM (250) TAB, 12-10 AWG</t>
+          <t>LUG, RING, COPPER, 1/0 AWG</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -14952,7 +14920,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
@@ -14979,22 +14947,22 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>CNLINKO</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
+          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -15005,7 +14973,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
@@ -15014,7 +14982,7 @@
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q125" s="3" t="inlineStr"/>
@@ -15032,33 +15000,33 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Jump lugs 1/0</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>LUG, RING, COPPER, 1/0 AWG</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
@@ -15070,7 +15038,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="inlineStr"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>10.4 m drawn + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -15085,33 +15057,33 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>CNLINKO</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I127" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K127" s="3" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr"/>
@@ -15123,7 +15095,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q127" s="3" t="inlineStr"/>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>0.3 m drawn + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -15138,7 +15114,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -15149,11 +15125,11 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -15164,7 +15140,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
@@ -15178,7 +15154,7 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>10.4 m drawn + 15% margin</t>
+          <t>0.3 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15171,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -15206,11 +15182,11 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -15221,7 +15197,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
@@ -15235,7 +15211,7 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>0.3 m drawn + 15% margin</t>
+          <t>0.7 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15228,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -15263,7 +15239,7 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
@@ -15292,7 +15268,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>0.3 m drawn + 15% margin</t>
+          <t>0.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15285,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -15320,11 +15296,11 @@
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -15335,21 +15311,33 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K131" s="3" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr"/>
-      <c r="M131" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-14</t>
+        </is>
+      </c>
       <c r="N131" s="3" t="inlineStr"/>
-      <c r="O131" s="3" t="inlineStr"/>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>0.7 m drawn + 15% margin</t>
+          <t>21.1 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15366,7 +15354,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -15377,11 +15365,11 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -15392,7 +15380,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
@@ -15406,7 +15394,7 @@
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>0.4 m drawn + 15% margin</t>
+          <t>1.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15411,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -15434,11 +15422,11 @@
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -15449,33 +15437,21 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="K133" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="M133" s="5" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-14</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr"/>
       <c r="N133" s="3" t="inlineStr"/>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O133" s="3" t="inlineStr"/>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>21.1 m drawn + 15% margin</t>
+          <t>5.2 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15492,7 +15468,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -15503,11 +15479,11 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -15518,21 +15494,33 @@
         <v>0</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-16</t>
+        </is>
+      </c>
       <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>1.4 m drawn + 15% margin</t>
+          <t>19.5 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15549,7 +15537,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -15560,11 +15548,11 @@
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -15575,7 +15563,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
@@ -15589,7 +15577,7 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>5.2 m drawn + 15% margin</t>
+          <t>3.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15606,7 +15594,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -15617,11 +15605,11 @@
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -15632,17 +15620,17 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-16</t>
+          <t>https://www.awcwire.com/product/m22759_16-18</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr"/>
@@ -15658,7 +15646,7 @@
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>19.5 m drawn + 15% margin</t>
+          <t>21.6 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15675,7 +15663,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -15686,7 +15674,7 @@
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
@@ -15732,7 +15720,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -15743,11 +15731,11 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -15758,33 +15746,21 @@
         <v>0</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K138" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="M138" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-18</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
       <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O138" s="2" t="inlineStr"/>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>21.6 m drawn + 15% margin</t>
+          <t>7.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15777,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -15812,11 +15788,11 @@
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
@@ -15827,7 +15803,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K139" s="3" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr"/>
@@ -15841,7 +15817,7 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>3.0 m drawn + 15% margin</t>
+          <t>4.7 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15834,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -15869,11 +15845,11 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -15884,21 +15860,33 @@
         <v>0</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K140" s="2" t="inlineStr"/>
-      <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-20</t>
+        </is>
+      </c>
       <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>7.4 m drawn + 15% margin</t>
+          <t>5.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15903,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -15926,11 +15914,11 @@
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -15941,7 +15929,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K141" s="3" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr"/>
@@ -15955,7 +15943,7 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>4.7 m drawn + 15% margin</t>
+          <t>7.3 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15960,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -15983,11 +15971,11 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -15998,33 +15986,21 @@
         <v>0</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K142" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="M142" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-20</t>
-        </is>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O142" s="2" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>5.9 m drawn + 15% margin</t>
+          <t>6.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16041,7 +16017,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -16052,11 +16028,11 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -16067,7 +16043,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
@@ -16081,7 +16057,7 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>7.3 m drawn + 15% margin</t>
+          <t>3.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16074,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -16109,11 +16085,11 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -16124,21 +16100,29 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr"/>
-      <c r="N144" s="2" t="inlineStr"/>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
+        </is>
+      </c>
       <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>6.9 m drawn + 15% margin</t>
+          <t>35.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16139,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -16166,11 +16150,11 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 6 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -16181,7 +16165,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K145" s="3" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
@@ -16195,7 +16179,7 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>3.9 m drawn + 15% margin</t>
+          <t>2.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16196,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -16223,11 +16207,11 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -16238,29 +16222,21 @@
         <v>0</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="4" t="inlineStr">
-        <is>
-          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
-        </is>
-      </c>
-      <c r="N146" s="4" t="inlineStr">
-        <is>
-          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
-        </is>
-      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
       <c r="O146" s="2" t="inlineStr"/>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>35.4 m drawn + 15% margin</t>
+          <t>3.2 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16277,7 +16253,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -16288,11 +16264,11 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 6 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
@@ -16303,7 +16279,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="K147" s="3" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr"/>
@@ -16317,7 +16293,7 @@
       </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
-          <t>2.0 m drawn + 15% margin</t>
+          <t>9.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16334,33 +16310,33 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Toyota / Sumitomo</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR SET, TOYOTA, 3 HOUSINGS: 90980-12068 2 POS, 90980-10897 6 POS, 90980-10942 2 POS</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr"/>
@@ -16372,11 +16348,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q148" s="2" t="inlineStr">
-        <is>
-          <t>3.2 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="Q148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -16391,33 +16363,29 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>Micro ISO relays x4</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>RELAY, PLUG-IN, MICRO ISO, 1 FORM A, 12 VDC COIL</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I149" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
@@ -16429,11 +16397,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q149" s="3" t="inlineStr">
-        <is>
-          <t>9.9 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="Q149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -16448,22 +16412,22 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Toyota / Sumitomo</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR SET, TOYOTA, 3 HOUSINGS: 90980-12068 2 POS, 90980-10897 6 POS, 90980-10942 2 POS</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -16474,7 +16438,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -16501,18 +16465,22 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Micro ISO relays x4</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr"/>
+          <t>RL00801-50RE</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Amphenol</t>
+        </is>
+      </c>
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>RELAY, PLUG-IN, MICRO ISO, 1 FORM A, 12 VDC COIL</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -16520,10 +16488,10 @@
         </is>
       </c>
       <c r="I151" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -16550,7 +16518,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>RL9080-301-F1</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -16561,11 +16529,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
+          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, BLACK, MATES RL00801-50BK</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -16576,16 +16544,28 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K152" s="2" t="inlineStr"/>
-      <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL9080-301-F1/16271602</t>
+        </is>
+      </c>
       <c r="N152" s="2" t="inlineStr"/>
-      <c r="O152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr"/>
@@ -16603,7 +16583,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -16614,11 +16594,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
+          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, RED, MATES RL00801-50RE</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -16629,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -16656,18 +16636,18 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>RL9080-301-F1</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, BLACK, MATES RL00801-50BK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
@@ -16675,7 +16655,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
@@ -16685,25 +16665,21 @@
         <v>1</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>13.43</v>
+        <v>0</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="M154" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL9080-301-F1/16271602</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
       <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr"/>
@@ -16721,18 +16697,18 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, RED, MATES RL00801-50RE</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
@@ -16740,7 +16716,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I155" s="3" t="n">
@@ -16749,14 +16725,22 @@
       <c r="J155" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K155" s="3" t="inlineStr"/>
-      <c r="L155" s="3" t="inlineStr"/>
+      <c r="K155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M155" s="3" t="inlineStr"/>
       <c r="N155" s="3" t="inlineStr"/>
-      <c r="O155" s="3" t="inlineStr"/>
+      <c r="O155" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P155" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q155" s="3" t="inlineStr"/>
@@ -16774,7 +16758,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -16785,7 +16769,7 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
@@ -16835,7 +16819,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -16846,11 +16830,11 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -16861,7 +16845,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K157" s="3" t="n">
         <v>0</v>
@@ -16896,7 +16880,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -16907,11 +16891,11 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -16922,7 +16906,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>0</v>
@@ -16957,7 +16941,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -16968,11 +16952,11 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -16983,7 +16967,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K159" s="3" t="n">
         <v>0</v>
@@ -17018,7 +17002,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
+          <t>RNF-100-3/8-4-STK</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -17029,11 +17013,11 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -17044,7 +17028,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>0</v>
@@ -17079,7 +17063,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
+          <t>RNF-100-3/8-6-STK</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -17090,11 +17074,11 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
@@ -17105,7 +17089,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K161" s="3" t="n">
         <v>0</v>
@@ -17140,50 +17124,42 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-4-STK</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Sumitomo / Subaru</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
+          <t>CONNECTOR, PLUG, SUMITOMO TS 025, 6 POS, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr"/>
       <c r="M162" s="2" t="inlineStr"/>
       <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O162" s="2" t="inlineStr"/>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr"/>
@@ -17201,7 +17177,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-6-STK</t>
+          <t>TMS-SCE-1/2-2.0-9</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -17212,22 +17188,22 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K163" s="3" t="n">
         <v>0</v>
@@ -17262,22 +17238,22 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo TS 025 6-way</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo / Subaru</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, SUMITOMO TS 025, 6 POS, SOCKET CONTACTS</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -17288,16 +17264,24 @@
         <v>0</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K164" s="2" t="inlineStr"/>
-      <c r="L164" s="2" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M164" s="2" t="inlineStr"/>
       <c r="N164" s="2" t="inlineStr"/>
-      <c r="O164" s="2" t="inlineStr"/>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr"/>
@@ -17315,7 +17299,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -17326,11 +17310,11 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
@@ -17341,7 +17325,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="K165" s="3" t="n">
         <v>0</v>
@@ -17376,22 +17360,22 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
+          <t>V23132-A2001-B200</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>RELAY, HIGH CURRENT, TE HCR 150, IP67, 1 FORM A, 130 A AT 85 C, 12 VDC COIL 37 OHM 3.9 W, PARALLEL RESISTOR, STUD LOAD TERMINALS</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -17402,21 +17386,13 @@
         <v>0</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L166" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr"/>
       <c r="M166" s="2" t="inlineStr"/>
       <c r="N166" s="2" t="inlineStr"/>
-      <c r="O166" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O166" s="2" t="inlineStr"/>
       <c r="P166" s="2" t="inlineStr">
         <is>
           <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
@@ -17437,22 +17413,18 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>W12P</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr"/>
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>WEDGELOCK, DT, 12-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
@@ -17460,27 +17432,19 @@
         </is>
       </c>
       <c r="I167" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="K167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K167" s="3" t="inlineStr"/>
+      <c r="L167" s="3" t="inlineStr"/>
       <c r="M167" s="3" t="inlineStr"/>
       <c r="N167" s="3" t="inlineStr"/>
-      <c r="O167" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O167" s="3" t="inlineStr"/>
       <c r="P167" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q167" s="3" t="inlineStr"/>
@@ -17498,18 +17462,14 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>V23132-A2001-B200</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity</t>
-        </is>
-      </c>
+          <t>W12S</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr"/>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>RELAY, HIGH CURRENT, TE HCR 150, IP67, 1 FORM A, 130 A AT 85 C, 12 VDC COIL 37 OHM 3.9 W, PARALLEL RESISTOR, STUD LOAD TERMINALS</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -17521,10 +17481,10 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
@@ -17533,7 +17493,7 @@
       <c r="O168" s="2" t="inlineStr"/>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr"/>
@@ -17551,18 +17511,26 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>W12P</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" s="3" t="inlineStr"/>
+          <t>W2P</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
@@ -17570,19 +17538,31 @@
         </is>
       </c>
       <c r="I169" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K169" s="3" t="inlineStr"/>
-      <c r="L169" s="3" t="inlineStr"/>
-      <c r="M169" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K169" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L169" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M169" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+        </is>
+      </c>
       <c r="N169" s="3" t="inlineStr"/>
-      <c r="O169" s="3" t="inlineStr"/>
+      <c r="O169" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P169" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="3" t="inlineStr"/>
@@ -17600,18 +17580,26 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>W12S</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr"/>
-      <c r="E170" s="2" t="inlineStr"/>
+          <t>W2S</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -17619,19 +17607,31 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K170" s="2" t="inlineStr"/>
-      <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W2S.html</t>
+        </is>
+      </c>
       <c r="N170" s="2" t="inlineStr"/>
-      <c r="O170" s="2" t="inlineStr"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>W2P</t>
+          <t>W3P</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -17664,11 +17664,11 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 3-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -17679,28 +17679,28 @@
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K171" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="L171" s="3" t="n">
-        <v>0.65</v>
+        <v>0.13</v>
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+          <t>https://www.te.com/en/product-W3P.html</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr"/>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P171" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="3" t="inlineStr"/>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -17733,11 +17733,11 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -17748,17 +17748,17 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1.43</v>
+        <v>0.26</v>
       </c>
       <c r="M172" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr"/>
@@ -17787,7 +17787,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>W3P</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -17802,11 +17802,11 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -17817,28 +17817,20 @@
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K173" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L173" s="3" t="n">
-        <v>0.13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K173" s="3" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr"/>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3P.html</t>
+          <t>https://www.te.com/en/product-W6P.html</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr"/>
-      <c r="O173" s="3" t="inlineStr">
-        <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
+      <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q173" s="3" t="inlineStr"/>
@@ -17856,12 +17848,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -17871,7 +17863,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
@@ -17888,23 +17880,15 @@
       <c r="J174" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K174" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L174" s="2" t="n">
-        <v>0.26</v>
-      </c>
+      <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.te.com/en/product-W6S.html</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr"/>
-      <c r="O174" s="2" t="inlineStr">
-        <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
+      <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -17925,7 +17909,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -17940,11 +17924,11 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -17955,13 +17939,13 @@
         <v>0</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K175" s="3" t="inlineStr"/>
       <c r="L175" s="3" t="inlineStr"/>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W6P.html</t>
+          <t>https://www.te.com/en/product-W8S.html</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr"/>
@@ -17986,7 +17970,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>WB-51PAL</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -18001,11 +17985,11 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, LEFT</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -18016,20 +18000,20 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W6S.html</t>
+          <t>https://www.te.com/en/product-WB-51PAL.html</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr"/>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr"/>
@@ -18047,7 +18031,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>WB-51PAR</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -18062,11 +18046,11 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
+          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, RIGHT</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -18077,13 +18061,13 @@
         <v>0</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K177" s="3" t="inlineStr"/>
       <c r="L177" s="3" t="inlineStr"/>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W8S.html</t>
+          <t>https://www.te.com/en/product-WB-51PAR.html</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr"/>
@@ -18108,7 +18092,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>WB-51PAL</t>
+          <t>WB-51SAL</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -18116,14 +18100,10 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, LEFT</t>
+          <t>WEDGELOCK, DRB 102/128, PLUG, LEFT</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
@@ -18144,14 +18124,14 @@
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51PAL.html</t>
+          <t>https://www.te.com/en/product-WB-51SAL.html</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr"/>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr"/>
@@ -18169,7 +18149,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>WB-51PAR</t>
+          <t>WB-51SAR</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -18184,7 +18164,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, RIGHT</t>
+          <t>WEDGELOCK, DRB 102/128, PLUG, RIGHT</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
@@ -18205,14 +18185,14 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51PAR.html</t>
+          <t>https://www.te.com/en/product-WB-51SAR.html</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr"/>
       <c r="O179" s="3" t="inlineStr"/>
       <c r="P179" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="3" t="inlineStr"/>
@@ -18230,7 +18210,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>WB-51SAL</t>
+          <t>WM-4S</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -18238,10 +18218,14 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, PLUG, LEFT</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
@@ -18262,14 +18246,14 @@
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51SAL.html</t>
+          <t>https://www.te.com/en/product-WM-4S.html</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr"/>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr"/>
@@ -18287,12 +18271,12 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>WB-51SAR</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -18302,7 +18286,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, PLUG, RIGHT</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
@@ -18323,14 +18307,14 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51SAR.html</t>
+          <t>https://www.te.com/en/product-WM-6S.html</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr"/>
       <c r="O181" s="3" t="inlineStr"/>
       <c r="P181" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q181" s="3" t="inlineStr"/>
@@ -18348,22 +18332,14 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>WM-4S</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E182" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+          <t>CABLE, SHIELDED, 1 CONDUCTOR, 22 AWG, WHITE, ETFE (TEFZEL), TINNED COPPER BRAID</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
@@ -18375,23 +18351,19 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WM-4S.html</t>
-        </is>
-      </c>
+      <c r="M182" s="2" t="inlineStr"/>
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr"/>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr"/>
@@ -18409,22 +18381,18 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>jump-post-M8</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
+          <t>POST, JUMP START, M8, INSULATED</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -18443,124 +18411,18 @@
       </c>
       <c r="K183" s="3" t="inlineStr"/>
       <c r="L183" s="3" t="inlineStr"/>
-      <c r="M183" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-WM-6S.html</t>
-        </is>
-      </c>
+      <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="inlineStr"/>
       <c r="O183" s="3" t="inlineStr"/>
       <c r="P183" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q183" s="3" t="inlineStr"/>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>generic</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr"/>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>CABLE, SHIELDED, 1 CONDUCTOR, 22 AWG, WHITE, ETFE (TEFZEL), TINNED COPPER BRAID</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="2" t="inlineStr"/>
-      <c r="M184" s="2" t="inlineStr"/>
-      <c r="N184" s="2" t="inlineStr"/>
-      <c r="O184" s="2" t="inlineStr"/>
-      <c r="P184" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q184" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>All 15 looms</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>jump-post-M8</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr"/>
-      <c r="F185" s="3" t="inlineStr">
-        <is>
-          <t>POST, JUMP START, M8, INSULATED</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K185" s="3" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr"/>
-      <c r="M185" s="3" t="inlineStr"/>
-      <c r="N185" s="3" t="inlineStr"/>
-      <c r="O185" s="3" t="inlineStr"/>
-      <c r="P185" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q185" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q185"/>
+  <autoFilter ref="A1:Q183"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -18598,20 +18460,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId53"/>
@@ -18623,8 +18485,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>355.91</v>
+        <v>352.1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>11</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>122</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>664.98</v>
+        <v>661.17</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>25</v>
@@ -7974,7 +7974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q183"/>
+  <dimension ref="A1:Q185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>12</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
@@ -13463,7 +13463,7 @@
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -13474,13 +13474,13 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>3.81</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>7.62</v>
+        <v>3.81</v>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
@@ -13516,7 +13516,11 @@
           <t>DT06-12SA</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -13524,7 +13528,7 @@
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
@@ -13535,16 +13539,20 @@
         <v>2</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr"/>
-      <c r="M99" s="3" t="inlineStr"/>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-DT06-12SA.html</t>
+        </is>
+      </c>
       <c r="N99" s="3" t="inlineStr"/>
       <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -14591,7 +14599,7 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -14602,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
@@ -14644,7 +14652,7 @@
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -14655,7 +14663,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr"/>
@@ -14682,7 +14690,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M8 22-16</t>
+          <t>GENERIC RING M8 12-10</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14693,11 +14701,11 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 22-16 AWG</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 12-10 AWG</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -14708,7 +14716,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
@@ -14735,7 +14743,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>GENERIC SOLDER SPLICE</t>
+          <t>GENERIC RING M8 22-16</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -14746,11 +14754,11 @@
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 22-16 AWG</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
@@ -14761,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="K121" s="3" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr"/>
@@ -14788,7 +14796,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>GENERIC SPADE RECEPTACLE 12-10</t>
+          <t>GENERIC SOLDER SPLICE</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -14799,11 +14807,11 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, QUICK CONNECT, RECEPTACLE, INSULATED, 6.3 MM (250) TAB, 12-10 AWG</t>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -14814,7 +14822,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
@@ -14841,18 +14849,18 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>GENERIC SPADE RECEPTACLE 12-10</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
+          <t>TERMINAL, QUICK CONNECT, RECEPTACLE, INSULATED, 6.3 MM (250) TAB, 12-10 AWG</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
@@ -14876,7 +14884,7 @@
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr"/>
@@ -14894,22 +14902,22 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Jump lugs 1/0</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>LUG, RING, COPPER, 1/0 AWG</t>
+          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -14920,7 +14928,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
@@ -14929,7 +14937,7 @@
       <c r="O124" s="2" t="inlineStr"/>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr"/>
@@ -14947,22 +14955,22 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>Jump lugs 1/0</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>CNLINKO</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
+          <t>LUG, RING, COPPER, 1/0 AWG</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -14973,7 +14981,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
@@ -15000,33 +15008,33 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>CNLINKO</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
@@ -15038,11 +15046,7 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="inlineStr">
-        <is>
-          <t>10.4 m drawn + 15% margin</t>
-        </is>
-      </c>
+      <c r="Q126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -15057,7 +15061,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -15068,11 +15072,11 @@
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
@@ -15083,7 +15087,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K127" s="3" t="inlineStr"/>
       <c r="L127" s="3" t="inlineStr"/>
@@ -15097,7 +15101,7 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>0.3 m drawn + 15% margin</t>
+          <t>0.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15118,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -15125,11 +15129,11 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -15140,7 +15144,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
@@ -15154,7 +15158,7 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>0.3 m drawn + 15% margin</t>
+          <t>10.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15171,7 +15175,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -15182,11 +15186,11 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -15197,7 +15201,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
@@ -15211,7 +15215,7 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>0.7 m drawn + 15% margin</t>
+          <t>0.3 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15232,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -15239,7 +15243,7 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
@@ -15268,7 +15272,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>0.4 m drawn + 15% margin</t>
+          <t>0.3 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15285,7 +15289,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -15296,11 +15300,11 @@
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -15311,33 +15315,21 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="K131" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="M131" s="5" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-14</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="3" t="inlineStr"/>
-      <c r="O131" s="3" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O131" s="3" t="inlineStr"/>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>21.1 m drawn + 15% margin</t>
+          <t>0.7 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15346,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -15365,11 +15357,11 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -15380,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
@@ -15394,7 +15386,7 @@
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>1.4 m drawn + 15% margin</t>
+          <t>0.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15403,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -15422,11 +15414,11 @@
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -15437,21 +15429,33 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="K133" s="3" t="inlineStr"/>
-      <c r="L133" s="3" t="inlineStr"/>
-      <c r="M133" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-14</t>
+        </is>
+      </c>
       <c r="N133" s="3" t="inlineStr"/>
-      <c r="O133" s="3" t="inlineStr"/>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>5.2 m drawn + 15% margin</t>
+          <t>21.1 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15468,7 +15472,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -15479,11 +15483,11 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
@@ -15494,33 +15498,21 @@
         <v>0</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="M134" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-16</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
       <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
         <is>
-          <t>19.5 m drawn + 15% margin</t>
+          <t>1.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15529,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -15548,11 +15540,11 @@
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -15563,7 +15555,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
@@ -15577,7 +15569,7 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>3.0 m drawn + 15% margin</t>
+          <t>5.8 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15586,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -15605,11 +15597,11 @@
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -15620,17 +15612,17 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-18</t>
+          <t>https://www.awcwire.com/product/m22759_16-16</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr"/>
@@ -15646,7 +15638,7 @@
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>21.6 m drawn + 15% margin</t>
+          <t>19.5 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15663,7 +15655,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -15674,7 +15666,7 @@
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
@@ -15720,7 +15712,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -15731,11 +15723,11 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -15746,21 +15738,33 @@
         <v>0</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K138" s="2" t="inlineStr"/>
-      <c r="L138" s="2" t="inlineStr"/>
-      <c r="M138" s="2" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="M138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-18</t>
+        </is>
+      </c>
       <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>7.4 m drawn + 15% margin</t>
+          <t>21.6 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15781,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -15788,11 +15792,11 @@
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
@@ -15803,7 +15807,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K139" s="3" t="inlineStr"/>
       <c r="L139" s="3" t="inlineStr"/>
@@ -15817,7 +15821,7 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>4.7 m drawn + 15% margin</t>
+          <t>3.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15834,7 +15838,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -15845,11 +15849,11 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -15860,33 +15864,21 @@
         <v>0</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="M140" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-20</t>
-        </is>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
       <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O140" s="2" t="inlineStr"/>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>5.9 m drawn + 15% margin</t>
+          <t>7.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15895,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -15914,11 +15906,11 @@
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -15929,7 +15921,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K141" s="3" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr"/>
@@ -15943,7 +15935,7 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>7.3 m drawn + 15% margin</t>
+          <t>5.6 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15960,7 +15952,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -15971,11 +15963,11 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -15986,21 +15978,33 @@
         <v>0</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="K142" s="2" t="inlineStr"/>
-      <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="M142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-20</t>
+        </is>
+      </c>
       <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>6.9 m drawn + 15% margin</t>
+          <t>5.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16017,7 +16021,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
@@ -16028,11 +16032,11 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -16043,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
@@ -16057,7 +16061,7 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>3.9 m drawn + 15% margin</t>
+          <t>8.8 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16078,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -16085,11 +16089,11 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -16100,29 +16104,21 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="4" t="inlineStr">
-        <is>
-          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
-        </is>
-      </c>
-      <c r="N144" s="4" t="inlineStr">
-        <is>
-          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
-        </is>
-      </c>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
       <c r="O144" s="2" t="inlineStr"/>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
         <is>
-          <t>35.4 m drawn + 15% margin</t>
+          <t>6.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16139,7 +16135,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
@@ -16150,11 +16146,11 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 6 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -16165,7 +16161,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K145" s="3" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
@@ -16179,7 +16175,7 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>2.0 m drawn + 15% margin</t>
+          <t>6.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16192,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -16207,11 +16203,11 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -16222,21 +16218,29 @@
         <v>0</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="2" t="inlineStr"/>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
+        </is>
+      </c>
       <c r="O146" s="2" t="inlineStr"/>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
         <is>
-          <t>3.2 m drawn + 15% margin</t>
+          <t>35.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16253,7 +16257,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
@@ -16264,11 +16268,11 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 6 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
@@ -16279,7 +16283,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="3" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="K147" s="3" t="inlineStr"/>
       <c r="L147" s="3" t="inlineStr"/>
@@ -16293,7 +16297,7 @@
       </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
-          <t>9.9 m drawn + 15% margin</t>
+          <t>2.0 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16310,33 +16314,33 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Toyota / Sumitomo</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR SET, TOYOTA, 3 HOUSINGS: 90980-12068 2 POS, 90980-10897 6 POS, 90980-10942 2 POS</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr"/>
@@ -16348,7 +16352,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
+          <t>3.2 m drawn + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -16363,29 +16371,33 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Micro ISO relays x4</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr"/>
+          <t>M22759/16-8-2</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>M22759</t>
+        </is>
+      </c>
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>RELAY, PLUG-IN, MICRO ISO, 1 FORM A, 12 VDC COIL</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I149" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
@@ -16397,7 +16409,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q149" s="3" t="inlineStr"/>
+      <c r="Q149" s="3" t="inlineStr">
+        <is>
+          <t>9.9 m drawn + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -16412,22 +16428,22 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Toyota / Sumitomo</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
+          <t>CONNECTOR SET, TOYOTA, 3 HOUSINGS: 90980-12068 2 POS, 90980-10897 6 POS, 90980-10942 2 POS</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -16438,7 +16454,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -16465,22 +16481,18 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>Amphenol</t>
-        </is>
-      </c>
+          <t>Micro ISO relays x4</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
+          <t>RELAY, PLUG-IN, MICRO ISO, 1 FORM A, 12 VDC COIL</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -16488,10 +16500,10 @@
         </is>
       </c>
       <c r="I151" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -16518,7 +16530,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>RL9080-301-F1</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -16529,11 +16541,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, BLACK, MATES RL00801-50BK</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -16544,28 +16556,16 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K152" s="2" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="L152" s="2" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="M152" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL9080-301-F1/16271602</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
       <c r="N152" s="2" t="inlineStr"/>
-      <c r="O152" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O152" s="2" t="inlineStr"/>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr"/>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -16594,11 +16594,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, RED, MATES RL00801-50RE</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -16636,18 +16636,18 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
+          <t>RL9080-301-F1</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, BLACK, MATES RL00801-50BK</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
@@ -16665,21 +16665,25 @@
         <v>1</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0</v>
+        <v>13.43</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M154" s="2" t="inlineStr"/>
+        <v>13.43</v>
+      </c>
+      <c r="M154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL9080-301-F1/16271602</t>
+        </is>
+      </c>
       <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>not priced (Dan)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr"/>
@@ -16697,18 +16701,18 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>RECEPTACLE, FEED-THROUGH, RADLOK 8.0, PANEL MOUNT, 200 A, 1 KV, RED, MATES RL00801-50RE</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
@@ -16716,7 +16720,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I155" s="3" t="n">
@@ -16725,22 +16729,14 @@
       <c r="J155" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr"/>
       <c r="M155" s="3" t="inlineStr"/>
       <c r="N155" s="3" t="inlineStr"/>
-      <c r="O155" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O155" s="3" t="inlineStr"/>
       <c r="P155" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q155" s="3" t="inlineStr"/>
@@ -16758,7 +16754,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -16769,7 +16765,7 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
@@ -16819,7 +16815,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
@@ -16830,11 +16826,11 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -16845,7 +16841,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K157" s="3" t="n">
         <v>0</v>
@@ -16880,7 +16876,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -16891,11 +16887,11 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -16906,7 +16902,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>0</v>
@@ -16941,7 +16937,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
@@ -16952,11 +16948,11 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -16967,7 +16963,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K159" s="3" t="n">
         <v>0</v>
@@ -17002,7 +16998,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-4-STK</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -17013,11 +17009,11 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -17028,7 +17024,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>0</v>
@@ -17063,7 +17059,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/8-6-STK</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
@@ -17074,11 +17070,11 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
@@ -17089,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K161" s="3" t="n">
         <v>0</v>
@@ -17124,42 +17120,50 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo TS 025 6-way</t>
+          <t>RNF-100-3/8-4-STK</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo / Subaru</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, SUMITOMO TS 025, 6 POS, SOCKET CONTACTS</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K162" s="2" t="inlineStr"/>
-      <c r="L162" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M162" s="2" t="inlineStr"/>
       <c r="N162" s="2" t="inlineStr"/>
-      <c r="O162" s="2" t="inlineStr"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr"/>
@@ -17177,7 +17181,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
+          <t>RNF-100-3/8-6-STK</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
@@ -17188,22 +17192,22 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 9.5 MM EXPANDED ID, 4.8 MM RECOVERED ID, CUT 25 MM</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I163" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J163" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K163" s="3" t="n">
         <v>0</v>
@@ -17238,22 +17242,22 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Sumitomo / Subaru</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>CONNECTOR, PLUG, SUMITOMO TS 025, 6 POS, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -17264,24 +17268,16 @@
         <v>0</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
       <c r="M164" s="2" t="inlineStr"/>
       <c r="N164" s="2" t="inlineStr"/>
-      <c r="O164" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O164" s="2" t="inlineStr"/>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr"/>
@@ -17299,7 +17295,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>TMS-SCE-1/2-2.0-9</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -17310,11 +17306,11 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
@@ -17325,7 +17321,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="3" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="K165" s="3" t="n">
         <v>0</v>
@@ -17360,22 +17356,22 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>V23132-A2001-B200</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>RELAY, HIGH CURRENT, TE HCR 150, IP67, 1 FORM A, 130 A AT 85 C, 12 VDC COIL 37 OHM 3.9 W, PARALLEL RESISTOR, STUD LOAD TERMINALS</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -17386,13 +17382,21 @@
         <v>0</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K166" s="2" t="inlineStr"/>
-      <c r="L166" s="2" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M166" s="2" t="inlineStr"/>
       <c r="N166" s="2" t="inlineStr"/>
-      <c r="O166" s="2" t="inlineStr"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
           <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
@@ -17413,18 +17417,22 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>W12P</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr"/>
+          <t>TMS-SCE-3/8-2.0-9</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12-WAY RECEPTACLE</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
@@ -17432,19 +17440,27 @@
         </is>
       </c>
       <c r="I167" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" s="3" t="inlineStr"/>
-      <c r="L167" s="3" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="K167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M167" s="3" t="inlineStr"/>
       <c r="N167" s="3" t="inlineStr"/>
-      <c r="O167" s="3" t="inlineStr"/>
+      <c r="O167" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P167" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q167" s="3" t="inlineStr"/>
@@ -17462,14 +17478,18 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>W12S</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr"/>
+          <t>V23132-A2001-B200</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>TE Connectivity</t>
+        </is>
+      </c>
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>RELAY, HIGH CURRENT, TE HCR 150, IP67, 1 FORM A, 130 A AT 85 C, 12 VDC COIL 37 OHM 3.9 W, PARALLEL RESISTOR, STUD LOAD TERMINALS</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -17481,10 +17501,10 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
@@ -17493,7 +17513,7 @@
       <c r="O168" s="2" t="inlineStr"/>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr"/>
@@ -17511,26 +17531,18 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>W2P</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>W12P</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr"/>
+      <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 12-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
@@ -17538,31 +17550,19 @@
         </is>
       </c>
       <c r="I169" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J169" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K169" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L169" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="M169" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K169" s="3" t="inlineStr"/>
+      <c r="L169" s="3" t="inlineStr"/>
+      <c r="M169" s="3" t="inlineStr"/>
       <c r="N169" s="3" t="inlineStr"/>
-      <c r="O169" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O169" s="3" t="inlineStr"/>
       <c r="P169" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q169" s="3" t="inlineStr"/>
@@ -17580,26 +17580,22 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Deutsch (TE Connectivity)</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -17607,31 +17603,23 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K170" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L170" s="2" t="n">
-        <v>1.43</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.te.com/en/product-W12S.html</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr"/>
-      <c r="O170" s="2" t="inlineStr">
-        <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
+      <c r="O170" s="2" t="inlineStr"/>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr"/>
@@ -17649,7 +17637,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>W3P</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
@@ -17664,11 +17652,11 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -17679,28 +17667,28 @@
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K171" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="L171" s="3" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="M171" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3P.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr"/>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P171" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="3" t="inlineStr"/>
@@ -17718,12 +17706,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W2S</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -17733,11 +17721,11 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -17748,17 +17736,17 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="L172" s="2" t="n">
-        <v>0.26</v>
+        <v>1.43</v>
       </c>
       <c r="M172" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.te.com/en/product-W2S.html</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr"/>
@@ -17769,7 +17757,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr"/>
@@ -17787,7 +17775,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>W3P</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
@@ -17802,11 +17790,11 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 3-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -17817,20 +17805,28 @@
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K173" s="3" t="inlineStr"/>
-      <c r="L173" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K173" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L173" s="3" t="n">
+        <v>0.13</v>
+      </c>
       <c r="M173" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W6P.html</t>
+          <t>https://www.te.com/en/product-W3P.html</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr"/>
-      <c r="O173" s="3" t="inlineStr"/>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="P173" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="3" t="inlineStr"/>
@@ -17848,12 +17844,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -17863,7 +17859,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
@@ -17880,15 +17876,23 @@
       <c r="J174" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0.26</v>
+      </c>
       <c r="M174" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W6S.html</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr"/>
-      <c r="O174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
           <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
@@ -17909,7 +17913,7 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
@@ -17924,7 +17928,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
@@ -17945,7 +17949,7 @@
       <c r="L175" s="3" t="inlineStr"/>
       <c r="M175" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W8S.html</t>
+          <t>https://www.te.com/en/product-W6P.html</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr"/>
@@ -17970,7 +17974,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>WB-51PAL</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -17985,11 +17989,11 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, LEFT</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -18000,20 +18004,20 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51PAL.html</t>
+          <t>https://www.te.com/en/product-W6S.html</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr"/>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr"/>
@@ -18031,7 +18035,7 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>WB-51PAR</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
@@ -18046,7 +18050,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, RIGHT</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
@@ -18067,7 +18071,7 @@
       <c r="L177" s="3" t="inlineStr"/>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51PAR.html</t>
+          <t>https://www.te.com/en/product-W8S.html</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr"/>
@@ -18092,7 +18096,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>WB-51SAL</t>
+          <t>WB-51PAL</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -18100,10 +18104,14 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, PLUG, LEFT</t>
+          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, LEFT</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
@@ -18124,14 +18132,14 @@
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51SAL.html</t>
+          <t>https://www.te.com/en/product-WB-51PAL.html</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr"/>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr"/>
@@ -18149,7 +18157,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>WB-51SAR</t>
+          <t>WB-51PAR</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -18164,7 +18172,7 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DRB 102/128, PLUG, RIGHT</t>
+          <t>WEDGELOCK, DRB 102/128, RECEPTACLE, RIGHT</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
@@ -18185,14 +18193,14 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WB-51SAR.html</t>
+          <t>https://www.te.com/en/product-WB-51PAR.html</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr"/>
       <c r="O179" s="3" t="inlineStr"/>
       <c r="P179" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q179" s="3" t="inlineStr"/>
@@ -18210,7 +18218,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>WB-51SAL</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -18218,14 +18226,10 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+          <t>WEDGELOCK, DRB 102/128, PLUG, LEFT</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
@@ -18246,14 +18250,14 @@
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WM-4S.html</t>
+          <t>https://www.te.com/en/product-WB-51SAL.html</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr"/>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr"/>
@@ -18271,12 +18275,12 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>WB-51SAR</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -18286,7 +18290,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
+          <t>WEDGELOCK, DRB 102/128, PLUG, RIGHT</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
@@ -18307,14 +18311,14 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WM-6S.html</t>
+          <t>https://www.te.com/en/product-WB-51SAR.html</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr"/>
       <c r="O181" s="3" t="inlineStr"/>
       <c r="P181" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="3" t="inlineStr"/>
@@ -18332,14 +18336,22 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="2" t="inlineStr"/>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 1 CONDUCTOR, 22 AWG, WHITE, ETFE (TEFZEL), TINNED COPPER BRAID</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
@@ -18351,19 +18363,23 @@
         </is>
       </c>
       <c r="I182" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="2" t="inlineStr"/>
+      <c r="M182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-WM-4S.html</t>
+        </is>
+      </c>
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr"/>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr"/>
@@ -18381,18 +18397,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>jump-post-M8</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr"/>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>POST, JUMP START, M8, INSULATED</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -18411,18 +18431,124 @@
       </c>
       <c r="K183" s="3" t="inlineStr"/>
       <c r="L183" s="3" t="inlineStr"/>
-      <c r="M183" s="3" t="inlineStr"/>
+      <c r="M183" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-WM-6S.html</t>
+        </is>
+      </c>
       <c r="N183" s="3" t="inlineStr"/>
       <c r="O183" s="3" t="inlineStr"/>
       <c r="P183" s="3" t="inlineStr">
         <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>All 15 looms</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>CABLE, SHIELDED, 1 CONDUCTOR, 22 AWG, WHITE, ETFE (TEFZEL), TINNED COPPER BRAID</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr"/>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q183" s="3" t="inlineStr"/>
+      <c r="Q184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>All 15 looms</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>jump-post-M8</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr"/>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>POST, JUMP START, M8, INSULATED</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" s="3" t="inlineStr"/>
+      <c r="L185" s="3" t="inlineStr"/>
+      <c r="M185" s="3" t="inlineStr"/>
+      <c r="N185" s="3" t="inlineStr"/>
+      <c r="O185" s="3" t="inlineStr"/>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q185" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q183"/>
+  <autoFilter ref="A1:Q185"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -18460,19 +18586,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M140" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M144" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N144" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M152" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M169" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId52"/>
@@ -18485,6 +18611,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -18497,7 +18625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20384,17 +20512,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>GENERIC CRIMP SPLICE 14-10</t>
+          <t>DT06-12SA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20406,7 +20534,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>GENERIC FLYING LEAD</t>
+          <t>GENERIC CRIMP SPLICE 14-10</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -20428,7 +20556,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
+          <t>GENERIC FLYING LEAD</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -20450,7 +20578,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 2AWG</t>
+          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -20472,7 +20600,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 4AWG</t>
+          <t>GENERIC LUG M10 2AWG</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -20494,7 +20622,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 50MM2</t>
+          <t>GENERIC LUG M10 4AWG</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -20516,7 +20644,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 8AWG</t>
+          <t>GENERIC LUG M10 50MM2</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -20538,7 +20666,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 2AWG</t>
+          <t>GENERIC LUG M10 8AWG</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -20560,7 +20688,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 4AWG</t>
+          <t>GENERIC LUG M8 2AWG</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -20582,7 +20710,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 8AWG</t>
+          <t>GENERIC LUG M8 4AWG</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -20604,7 +20732,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 12-10</t>
+          <t>GENERIC LUG M8 8AWG</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -20626,7 +20754,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 22-16</t>
+          <t>GENERIC RING M6 12-10</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -20648,7 +20776,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M8 22-16</t>
+          <t>GENERIC RING M6 22-16</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -20670,7 +20798,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>GENERIC SOLDER SPLICE</t>
+          <t>GENERIC RING M8 12-10</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -20692,7 +20820,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GENERIC SPADE RECEPTACLE 12-10</t>
+          <t>GENERIC RING M8 22-16</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -20714,17 +20842,17 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>GENERIC SOLDER SPLICE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20736,7 +20864,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Jump lugs 1/0</t>
+          <t>GENERIC SPADE RECEPTACLE 12-10</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -20758,12 +20886,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -20780,7 +20908,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>Jump lugs 1/0</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -20790,7 +20918,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20802,7 +20930,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -20812,7 +20940,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20824,7 +20952,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -20846,7 +20974,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -20868,7 +20996,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -20890,7 +21018,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -20912,7 +21040,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -20934,7 +21062,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -20956,7 +21084,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -20978,7 +21106,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -21000,7 +21128,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -21022,7 +21150,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -21044,7 +21172,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -21066,7 +21194,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -21088,12 +21216,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -21110,7 +21238,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -21132,7 +21260,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -21154,12 +21282,12 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -21176,7 +21304,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -21186,7 +21314,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21198,7 +21326,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -21208,7 +21336,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21220,7 +21348,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -21230,7 +21358,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21242,7 +21370,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -21252,7 +21380,7 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21392,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo TS 025 6-way</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -21286,12 +21414,12 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>V23132-A2001-B200</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -21308,12 +21436,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -21330,12 +21458,12 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -21352,12 +21480,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>V23132-A2001-B200</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -21374,12 +21502,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>WB-51PAL</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -21396,7 +21524,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>WB-51PAR</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -21418,7 +21546,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>WB-51SAL</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -21440,12 +21568,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>WB-51SAR</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -21462,7 +21590,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>WB-51PAL</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -21484,7 +21612,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>WB-51PAR</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -21506,22 +21634,110 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
+          <t>WB-51SAL</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>WB-51SAR</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>WM-6S</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
           <t>jump-post-M8</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D137"/>
+  <autoFilter ref="A1:D141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$185</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,13 +543,13 @@
         <v>184</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>360.93</v>
+        <v>352.1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>11</v>
@@ -565,13 +565,13 @@
         <v>298</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>670</v>
+        <v>661.17</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>25</v>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>12</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" s="3" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
@@ -13089,7 +13089,7 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>DT04-6P-CE03</t>
+          <t>DT06-08SA</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 6 POS, PIN CONTACTS, E SEAL, INSUL 1.35-3.05 MM, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
@@ -13477,25 +13477,25 @@
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.34</v>
+        <v>3.81</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2.34</v>
+        <v>3.81</v>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-6P-CE03.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>family price (DT04-6P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -13513,58 +13513,46 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>DT06-08SA</t>
+          <t>DT06-12SA</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J99" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="L99" s="3" t="n">
-        <v>7.62</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
+          <t>https://www.te.com/en/product-DT06-12SA.html</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr"/>
-      <c r="O99" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O99" s="3" t="inlineStr"/>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -13582,18 +13570,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>DT06-12SA</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr"/>
+          <t>DT06-2S</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -13604,16 +13596,28 @@
         <v>2</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -13631,7 +13635,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>DT06-2S</t>
+          <t>DT06-2S-CE05</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -13639,14 +13643,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr"/>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
@@ -13654,31 +13662,31 @@
         </is>
       </c>
       <c r="I101" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0.77</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0.77</v>
+        <v>6.16</v>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
+          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr"/>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr"/>
@@ -13696,26 +13704,18 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>DT06-2S-CE05</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DT06-3S</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -13723,31 +13723,19 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="M102" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
+      <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr"/>
@@ -13765,14 +13753,22 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>DT06-3S</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr"/>
-      <c r="E103" s="3" t="inlineStr"/>
+          <t>DT06-3S-CE05</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
@@ -13784,19 +13780,31 @@
         </is>
       </c>
       <c r="I103" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
+        </is>
+      </c>
       <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="3" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr"/>
@@ -13814,26 +13822,22 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>DT06-3S-CE05</t>
+          <t>DT06-6S</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -13844,17 +13848,17 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>2.06</v>
+        <v>5.04</v>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
@@ -13883,7 +13887,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>DT06-6S</t>
+          <t>DTHD06-1-8S</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -13891,14 +13895,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr"/>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -13909,17 +13917,17 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K105" s="3" t="n">
-        <v>2.52</v>
+        <v>3.48</v>
       </c>
       <c r="L105" s="3" t="n">
-        <v>5.04</v>
+        <v>13.92</v>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
         </is>
       </c>
       <c r="N105" s="3" t="inlineStr"/>
@@ -13948,22 +13956,14 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>DT06-6S-CE05</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DTM06-4S</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
@@ -13975,31 +13975,19 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" s="2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="M106" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/wee/DT06-6S-CE05/29360522</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
       <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key listing opened 2026-10-19 (reseller "wee", not TE direct)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr"/>
@@ -14017,26 +14005,18 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>DTHD06-1-8S</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>DTM06-6S</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
+          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -14044,31 +14024,19 @@
         </is>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K107" s="3" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="L107" s="3" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K107" s="3" t="inlineStr"/>
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
+      <c r="O107" s="3" t="inlineStr"/>
       <c r="P107" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q107" s="3" t="inlineStr"/>
@@ -14086,18 +14054,22 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>DTM06-4S</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr"/>
+          <t>GENERIC CRIMP SPLICE 14-10</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
+          <t>SPLICE, CRIMP, UNINSULATED, COPPER, TINNED, COMBINED 14-10 AWG, ADHESIVE HEATSHRINK OVER</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -14105,10 +14077,10 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
@@ -14135,18 +14107,22 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>DTM06-6S</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr"/>
+          <t>GENERIC FLYING LEAD</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
+          <t>TERMINAL, FLYING LEAD</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -14154,10 +14130,10 @@
         </is>
       </c>
       <c r="I109" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="K109" s="3" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr"/>
@@ -14184,7 +14160,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>GENERIC CRIMP SPLICE 14-10</t>
+          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -14195,7 +14171,7 @@
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>SPLICE, CRIMP, UNINSULATED, COPPER, TINNED, COMBINED 14-10 AWG, ADHESIVE HEATSHRINK OVER</t>
+          <t>TERMINAL, FLYING LEAD, HEAVY</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -14237,7 +14213,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>GENERIC FLYING LEAD</t>
+          <t>GENERIC LUG M10 2AWG</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -14248,11 +14224,11 @@
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, FLYING LEAD</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -14263,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="K111" s="3" t="inlineStr"/>
       <c r="L111" s="3" t="inlineStr"/>
@@ -14290,7 +14266,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
+          <t>GENERIC LUG M10 4AWG</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -14301,11 +14277,11 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, FLYING LEAD, HEAVY</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -14316,7 +14292,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
@@ -14343,7 +14319,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 2AWG</t>
+          <t>GENERIC LUG M10 50MM2</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -14354,11 +14330,11 @@
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 50 MM2 (1/0) BARREL, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -14369,7 +14345,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr"/>
@@ -14396,7 +14372,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 4AWG</t>
+          <t>GENERIC LUG M10 8AWG</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -14407,7 +14383,7 @@
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
@@ -14449,7 +14425,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 50MM2</t>
+          <t>GENERIC LUG M8 2AWG</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -14460,11 +14436,11 @@
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 50 MM2 (1/0) BARREL, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -14475,7 +14451,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K115" s="3" t="inlineStr"/>
       <c r="L115" s="3" t="inlineStr"/>
@@ -14502,7 +14478,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 8AWG</t>
+          <t>GENERIC LUG M8 4AWG</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -14513,7 +14489,7 @@
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M10 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
@@ -14555,7 +14531,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 2AWG</t>
+          <t>GENERIC LUG M8 8AWG</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -14566,11 +14542,11 @@
       <c r="E117" s="3" t="inlineStr"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 2 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -14581,7 +14557,7 @@
         <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K117" s="3" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr"/>
@@ -14608,7 +14584,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 4AWG</t>
+          <t>GENERIC RING M6 12-10</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -14619,11 +14595,11 @@
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 4 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 12-10 AWG</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -14634,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
@@ -14661,7 +14637,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 8AWG</t>
+          <t>GENERIC RING M6 22-16</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -14672,11 +14648,11 @@
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, LUG, RING, COPPER, TINNED, 8 AWG, M8 STUD, ADHESIVE HEATSHRINK</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 22-16 AWG</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -14687,7 +14663,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr"/>
@@ -14714,7 +14690,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 12-10</t>
+          <t>GENERIC RING M8 12-10</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -14725,11 +14701,11 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 12-10 AWG</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 12-10 AWG</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -14740,7 +14716,7 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
@@ -14767,7 +14743,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 22-16</t>
+          <t>GENERIC RING M8 22-16</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -14778,7 +14754,7 @@
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M6 STUD, 22-16 AWG</t>
+          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 22-16 AWG</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
@@ -14820,7 +14796,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M8 22-16</t>
+          <t>GENERIC SOLDER SPLICE</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -14831,11 +14807,11 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, RING, INSULATED, NYLON, M8 STUD, 22-16 AWG</t>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -14846,7 +14822,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
@@ -14873,7 +14849,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>GENERIC SOLDER SPLICE</t>
+          <t>GENERIC SPADE RECEPTACLE 12-10</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -14884,11 +14860,11 @@
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+          <t>TERMINAL, QUICK CONNECT, RECEPTACLE, INSULATED, 6.3 MM (250) TAB, 12-10 AWG</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -14899,7 +14875,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr"/>
@@ -14926,18 +14902,18 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>GENERIC SPADE RECEPTACLE 12-10</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>TERMINAL, QUICK CONNECT, RECEPTACLE, INSULATED, 6.3 MM (250) TAB, 12-10 AWG</t>
+          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
@@ -14961,7 +14937,7 @@
       <c r="O124" s="2" t="inlineStr"/>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr"/>
@@ -14979,22 +14955,22 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>Jump lugs 1/0</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
+          <t>LUG, RING, COPPER, 1/0 AWG</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -15005,7 +14981,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
       <c r="L125" s="3" t="inlineStr"/>
@@ -15014,7 +14990,7 @@
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q125" s="3" t="inlineStr"/>
@@ -15032,22 +15008,22 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Jump lugs 1/0</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>CNLINKO</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>LUG, RING, COPPER, 1/0 AWG</t>
+          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -15058,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
@@ -15085,18 +15061,18 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>CNLINKO</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
@@ -15104,7 +15080,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I127" s="3" t="n">
@@ -15123,7 +15099,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q127" s="3" t="inlineStr"/>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>0.9 m drawn + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -15381,7 +15361,7 @@
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -15392,7 +15372,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
@@ -15406,7 +15386,7 @@
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>0.4 m drawn + 15% margin</t>
+          <t>0.9 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15564,7 +15544,7 @@
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -15575,7 +15555,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
@@ -15589,7 +15569,7 @@
       </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
-          <t>5.2 m drawn + 15% margin</t>
+          <t>5.8 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15910,7 @@
         </is>
       </c>
       <c r="G141" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -15941,7 +15921,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K141" s="3" t="inlineStr"/>
       <c r="L141" s="3" t="inlineStr"/>
@@ -15955,7 +15935,7 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>4.7 m drawn + 15% margin</t>
+          <t>5.6 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16036,7 @@
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -16067,7 +16047,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
@@ -16081,7 +16061,7 @@
       </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
-          <t>7.3 m drawn + 15% margin</t>
+          <t>8.8 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16150,7 @@
         </is>
       </c>
       <c r="G145" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -16181,7 +16161,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K145" s="3" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
@@ -16195,7 +16175,7 @@
       </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
-          <t>3.9 m drawn + 15% margin</t>
+          <t>6.4 m drawn + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16972,7 +16952,7 @@
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -16983,7 +16963,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K159" s="3" t="n">
         <v>0</v>
@@ -17391,7 +17371,7 @@
         </is>
       </c>
       <c r="G166" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -17402,7 +17382,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>0</v>
@@ -17452,7 +17432,7 @@
         </is>
       </c>
       <c r="G167" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
@@ -17463,7 +17443,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K167" s="3" t="n">
         <v>0</v>
@@ -17603,7 +17583,11 @@
           <t>W12S</t>
         </is>
       </c>
-      <c r="D170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch (TE Connectivity)</t>
+        </is>
+      </c>
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -17611,7 +17595,7 @@
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -17622,16 +17606,20 @@
         <v>2</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
+      <c r="M170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W12S.html</t>
+        </is>
+      </c>
       <c r="N170" s="2" t="inlineStr"/>
       <c r="O170" s="2" t="inlineStr"/>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr"/>
@@ -17944,7 +17932,7 @@
         </is>
       </c>
       <c r="G175" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -17955,7 +17943,7 @@
         <v>0</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K175" s="3" t="inlineStr"/>
       <c r="L175" s="3" t="inlineStr"/>
@@ -18005,7 +17993,7 @@
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -18016,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
@@ -18066,7 +18054,7 @@
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -18077,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K177" s="3" t="inlineStr"/>
       <c r="L177" s="3" t="inlineStr"/>
@@ -18599,19 +18587,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M138" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M142" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M146" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N146" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M154" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M170" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M171" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M172" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M173" r:id="rId53"/>
@@ -18637,7 +18625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20524,17 +20512,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>GENERIC CRIMP SPLICE 14-10</t>
+          <t>DT06-12SA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20546,7 +20534,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>GENERIC FLYING LEAD</t>
+          <t>GENERIC CRIMP SPLICE 14-10</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -20568,7 +20556,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
+          <t>GENERIC FLYING LEAD</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -20590,7 +20578,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 2AWG</t>
+          <t>GENERIC HEAVY FLYING LEAD 10-6</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -20612,7 +20600,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 4AWG</t>
+          <t>GENERIC LUG M10 2AWG</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -20634,7 +20622,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 50MM2</t>
+          <t>GENERIC LUG M10 4AWG</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -20656,7 +20644,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M10 8AWG</t>
+          <t>GENERIC LUG M10 50MM2</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -20678,7 +20666,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 2AWG</t>
+          <t>GENERIC LUG M10 8AWG</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -20700,7 +20688,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 4AWG</t>
+          <t>GENERIC LUG M8 2AWG</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -20722,7 +20710,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>GENERIC LUG M8 8AWG</t>
+          <t>GENERIC LUG M8 4AWG</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -20744,7 +20732,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 12-10</t>
+          <t>GENERIC LUG M8 8AWG</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -20766,7 +20754,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>GENERIC RING M6 22-16</t>
+          <t>GENERIC RING M6 12-10</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -20788,7 +20776,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>GENERIC RING M8 22-16</t>
+          <t>GENERIC RING M6 22-16</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -20810,7 +20798,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>GENERIC SOLDER SPLICE</t>
+          <t>GENERIC RING M8 12-10</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -20832,7 +20820,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GENERIC SPADE RECEPTACLE 12-10</t>
+          <t>GENERIC RING M8 22-16</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -20854,17 +20842,17 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>GENERIC SOLDER SPLICE</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20876,7 +20864,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Jump lugs 1/0</t>
+          <t>GENERIC SPADE RECEPTACLE 12-10</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -20898,12 +20886,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -20920,7 +20908,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>Jump lugs 1/0</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -20930,7 +20918,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20942,7 +20930,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -20952,7 +20940,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20952,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -20986,7 +20974,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -21008,7 +20996,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -21030,7 +21018,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -21052,7 +21040,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -21074,7 +21062,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -21096,7 +21084,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -21118,7 +21106,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -21140,7 +21128,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -21162,7 +21150,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -21184,7 +21172,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -21206,7 +21194,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -21228,12 +21216,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -21250,7 +21238,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -21272,7 +21260,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -21294,12 +21282,12 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -21316,7 +21304,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -21326,7 +21314,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21338,7 +21326,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -21348,7 +21336,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21348,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -21370,7 +21358,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21382,7 +21370,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>RL9080-301-F1RE</t>
+          <t>MR-S ZZW30 EHPS pump - A 90980-12068 / B 90980-10897 / C 90980-10942</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -21392,7 +21380,7 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -21404,7 +21392,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Sumitomo TS 025 6-way</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -21426,12 +21414,12 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>V23132-A2001-B200</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -21448,12 +21436,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>RL9080-301-F1RE</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -21470,12 +21458,12 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>Sumitomo TS 025 6-way</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -21492,12 +21480,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>V23132-A2001-B200</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -21514,12 +21502,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>WB-51PAL</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -21536,7 +21524,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>WB-51PAR</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -21558,7 +21546,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>WB-51SAL</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -21580,12 +21568,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>WB-51SAR</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -21602,7 +21590,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>WB-51PAL</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -21624,7 +21612,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>WB-51PAR</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -21646,22 +21634,110 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
+          <t>WB-51SAL</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>WB-51SAR</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>WM-6S</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
           <t>jump-post-M8</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D137"/>
+  <autoFilter ref="A1:D141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$205</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,10 +524,10 @@
         <v>103</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>309.07</v>
+        <v>411.54</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>14</v>
@@ -546,10 +546,10 @@
         <v>193</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>140.27</v>
+        <v>3252.25</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -568,10 +568,10 @@
         <v>296</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>449.34</v>
+        <v>3663.79</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23</v>
@@ -604,7 +604,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
@@ -642,7 +642,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TE sample</t>
+          <t>Free sample</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -751,18 +751,24 @@
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>48.46</v>
+      </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-1416010-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-potter-brumfield-relays/1416010-1/8635411</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 475 in stock</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -790,7 +796,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -812,18 +818,24 @@
       <c r="J3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-281934-2.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/281934-2/2054300</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 197174 in stock</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -851,7 +863,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -873,18 +885,24 @@
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
+        <v>0.89</v>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-282080-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/282080-1/1860704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 6040 in stock</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -912,7 +930,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -934,18 +952,24 @@
       <c r="J5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="n">
+        <v>0.19</v>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-282110-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/282110-1/2054305</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Cut Tape (CT)), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 10029 in stock</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -2062,7 +2086,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -2084,18 +2108,26 @@
       <c r="J23" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>22.88</v>
+      </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0460-202-2031.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0460-202-2031/7200808</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 26 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 29580 in stock</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -2123,7 +2155,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2145,18 +2177,26 @@
       <c r="J24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>6.03</v>
+      </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-112263-90.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/112263-90/6566683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 6773 in stock</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -2184,7 +2224,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -2206,18 +2246,26 @@
       <c r="J25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>1.62</v>
+      </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-112264-ZZ.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/112264-ZZ/9923093</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 34528 in stock</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -2263,14 +2311,26 @@
       <c r="J26" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/essentra-components/50M060100P030/11641017</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 1581 in stock</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -2693,7 +2753,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2762,7 +2822,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2831,7 +2891,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2853,18 +2913,26 @@
       <c r="J36" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-280919-2.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/280919-2/2279662</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 16 (Cut Tape (CT)), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 25533 in stock</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -2911,25 +2979,25 @@
         <v>13</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-320554.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/320554/299303</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 13 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 3221 in stock</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -2957,7 +3025,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2979,18 +3047,24 @@
       <c r="J38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
+        <v>5.05</v>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-4-1904124-2.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1904124-2/22871639</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 463 in stock</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -3018,7 +3092,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -3040,18 +3114,24 @@
       <c r="J39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="n">
+        <v>4.54</v>
+      </c>
       <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-4-1904124-3.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1904124-3/5342812</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 1781 in stock</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -3079,7 +3159,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3102,25 +3182,25 @@
         <v>15</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-42281-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/42281-1/288367</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 31 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 59892 in stock</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -3148,7 +3228,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -3170,18 +3250,24 @@
       <c r="J41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="n">
+        <v>3.66</v>
+      </c>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-5-1393292-8.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-potter-brumfield-relays/5-1393292-8/5437855</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 260 in stock</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -3209,7 +3295,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3232,25 +3318,25 @@
         <v>10</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.37</v>
+        <v>0.79</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-53941-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/53941-1/297881</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>seen</t>
+          <t>Digi-Key qty 10 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 3924 in stock</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -3278,7 +3364,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -3300,18 +3386,26 @@
       <c r="J43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>4.49</v>
+      </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-6-1419137-4.html</t>
+          <t>https://www.digikey.com/en/products/detail/wee/6-1419137-4/25564049</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 40 (Retail Package), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 200 in stock</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr"/>
@@ -3423,25 +3517,25 @@
         <v>2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.55</v>
+        <v>2.62</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1.1</v>
+        <v>5.24</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>https://stanion.com/Product/atm10bus</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-10/264842</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20; listed as BK/ATM-10</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 1817 in stock</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr"/>
@@ -3488,25 +3582,25 @@
         <v>7</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.55</v>
+        <v>2.55</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3.85</v>
+        <v>17.85</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>https://www.vanmeterinc.com/catalog/electrical/fuses/automotive-fuses/eaton-atm-15</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-15/264843</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 7 (Bulk), 2026-10-20; listed as BK/ATM-15</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 6692 in stock</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
@@ -3553,25 +3647,25 @@
         <v>4</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.55</v>
+        <v>2.95</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>2.2</v>
+        <v>11.8</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://www.standardelectricsupply.com/Bussmann-ATM-2-Automotive-Fuse</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-2/264844</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20; listed as BK/ATM-2</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 844 in stock</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr"/>
@@ -3618,25 +3712,25 @@
         <v>1</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.55</v>
+        <v>2.56</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0.55</v>
+        <v>2.56</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanion.com/Product/atm20bus</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-20/264845</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20; listed as BK/ATM-20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 369 in stock</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
@@ -3683,25 +3777,25 @@
         <v>3</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.55</v>
+        <v>2.61</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>1.65</v>
+        <v>7.83</v>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>https://www.stanion.com/Product/atm5bus</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-5/264850</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20; listed as BK/ATM-5</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 1104 in stock</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr"/>
@@ -3748,25 +3842,25 @@
         <v>4</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.55</v>
+        <v>2.91</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2.2</v>
+        <v>11.64</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>https://www.stanion.com/Product/atm71-2bus</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-7-1-2/264851</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20; listed as BK/ATM-7-1/2</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 3014 in stock</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -4581,21 +4675,25 @@
         <v>1</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>2.55</v>
+        <v>3.81</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M63" s="3" t="inlineStr"/>
+        <v>3.81</v>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-8-0-STK/26583058</t>
+        </is>
+      </c>
       <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>seen</t>
+          <t>Digi-Key qty 2 (Bag), 2026-10-20</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr"/>
@@ -4642,21 +4740,25 @@
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+        <v>1.91</v>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-3-32-0-STK/26583372</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 2 (Bag), 2026-10-20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 1599 in stock</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr"/>
@@ -4944,7 +5046,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -4966,18 +5068,24 @@
       <c r="J69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="n">
+        <v>10.29</v>
+      </c>
       <c r="L69" s="3" t="inlineStr"/>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-1-1393304-0.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/1-1393304-0/5338684</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr"/>
-      <c r="O69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 140 in stock</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr"/>
@@ -5005,7 +5113,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -5027,18 +5135,24 @@
       <c r="J70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
+        <v>8.220000000000001</v>
+      </c>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-1-1414147-0.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/1-1414147-0/5338726</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 501 in stock</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr"/>
@@ -5085,25 +5199,25 @@
         <v>1</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>9</v>
+        <v>9.57</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>9</v>
+        <v>9.57</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-1-1414687-0.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-potter-brumfield-relays/1-1414687-0/5592432</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 250 in stock</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr"/>
@@ -5131,7 +5245,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -5200,7 +5314,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -5269,7 +5383,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5292,25 +5406,25 @@
         <v>6</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>4.38</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-280755-4.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/280755-4/2055537</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 6 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 20132 in stock</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -5338,7 +5452,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -5361,25 +5475,25 @@
         <v>8</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>3.2</v>
+        <v>5.84</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-280756-4.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/280756-4/1014749</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 8 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 9736 in stock</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr"/>
@@ -5426,25 +5540,25 @@
         <v>4</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>2.04</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-36161.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/36161/287829</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 52618 in stock</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -5472,7 +5586,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -5495,23 +5609,23 @@
         <v>0</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-42281-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/42281-1/288367</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 31 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 59892 in stock</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr"/>
@@ -5539,7 +5653,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5562,23 +5676,23 @@
         <v>0</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-42281-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/42281-1/288367</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 31 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 59892 in stock</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -5606,7 +5720,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -5629,25 +5743,25 @@
         <v>4</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-62998-2.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/62998-2/665822</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 4 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 33613 in stock</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr"/>
@@ -6019,25 +6133,25 @@
         <v>1</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.55</v>
+        <v>2.62</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.55</v>
+        <v>2.62</v>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>https://stanion.com/Product/atm10bus</t>
+          <t>https://www.digikey.com/en/products/detail/eaton-bussmann-electrical-division/BK-ATM-10/264842</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr"/>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20; listed as BK/ATM-10</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 1817 in stock</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr"/>
@@ -6782,14 +6896,26 @@
       <c r="J97" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K97" s="3" t="inlineStr"/>
-      <c r="L97" s="3" t="inlineStr"/>
-      <c r="M97" s="3" t="inlineStr"/>
+      <c r="K97" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-4-0-STK/26583229</t>
+        </is>
+      </c>
       <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="inlineStr"/>
+      <c r="O97" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bag), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr"/>
@@ -6836,21 +6962,25 @@
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.55</v>
+        <v>3.81</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+        <v>3.81</v>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-8-0-STK/26583058</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>seen</t>
+          <t>Digi-Key qty 2 (Bag), 2026-10-20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr"/>
@@ -6897,21 +7027,25 @@
         <v>1</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="M99" s="3" t="inlineStr"/>
+        <v>1.91</v>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-3-32-0-STK/26583372</t>
+        </is>
+      </c>
       <c r="N99" s="3" t="inlineStr"/>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 2 (Bag), 2026-10-20</t>
         </is>
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 1599 in stock</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -7477,14 +7611,26 @@
       <c r="J108" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/essentra-components/50M060100P030/11641017</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 1581 in stock</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr"/>
@@ -7899,69 +8045,76 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -7981,7 +8134,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
@@ -8019,7 +8172,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TE sample</t>
+          <t>Free sample</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -8106,7 +8259,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -8128,18 +8281,26 @@
       <c r="J2" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2.4</v>
+      </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0413-204-2005.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0413-204-2005/7387531</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 24 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 156196 in stock</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -8167,7 +8328,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -8189,18 +8350,26 @@
       <c r="J3" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>10.64</v>
+      </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0413-214-1205.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0413-214-1205/18110389</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 14 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 7641 in stock</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr"/>
@@ -8246,18 +8415,24 @@
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
+        <v>1.09</v>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0460-202-1631.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0460-202-1631/7200928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 74 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 45820 in stock</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -8303,18 +8478,24 @@
       <c r="J5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="n">
+        <v>2.17</v>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0460-220-1231.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0460-220-1231/7201149</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 6 in stock</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr"/>
@@ -8342,7 +8523,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -8364,18 +8545,26 @@
       <c r="J6" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>25.01</v>
+      </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0462-201-16141.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0462-201-16141/7200924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 61 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -8421,18 +8610,24 @@
       <c r="J7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="n">
+        <v>1.33</v>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0462-201-1631.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0462-201-1631/7200925</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 91 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
@@ -8460,7 +8655,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -8482,18 +8677,26 @@
       <c r="J8" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>16.91</v>
+      </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0462-201-2031.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0462-201-2031/7200804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 19 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
@@ -8539,18 +8742,24 @@
       <c r="J9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="n">
+        <v>6.84</v>
+      </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0462-203-08141.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0462-203-08141/7201144</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr"/>
@@ -8596,18 +8805,24 @@
       <c r="J10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
+        <v>3.19</v>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-0462-210-1231.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0462-210-1231/7201148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 7632 in stock</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -8706,14 +8921,26 @@
       <c r="J12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K80/1741255</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K80</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 17051 in stock</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -8759,14 +8986,26 @@
       <c r="J13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT10K0/1741265</t>
+        </is>
+      </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT10K0</t>
+        </is>
+      </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 568040 in stock</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
@@ -8812,14 +9051,26 @@
       <c r="J14" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114017-ZZ/6566679</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 58 (Box), 2026-10-20; listed as 114017-ZZ</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 267877 in stock</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -8865,18 +9116,24 @@
       <c r="J15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="n">
+        <v>0.75</v>
+      </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-114018-ZZ.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114018-ZZ/9923101</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 8 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 6856 in stock</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -8922,18 +9179,24 @@
       <c r="J16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="n">
+        <v>1.82</v>
+      </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-114019-ZZ.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114019-ZZ/6566680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 4 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 2935 in stock</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -9097,14 +9360,26 @@
       <c r="J19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RNMF14FTC120R/2617285</t>
+        </is>
+      </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Cut Tape (CT)), 2026-10-20; listed as RNMF14FTC120R</t>
+        </is>
+      </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 124869 in stock</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -9415,14 +9690,26 @@
       <c r="J25" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
+        </is>
+      </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -9468,14 +9755,26 @@
       <c r="J26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -9574,18 +9873,24 @@
       <c r="J28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="n">
+        <v>0.41</v>
+      </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-3-1447221-3.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -9631,18 +9936,24 @@
       <c r="J29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="n">
+        <v>0.28</v>
+      </c>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-3-1447221-4.html</t>
+          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+        </is>
+      </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -9688,14 +9999,26 @@
       <c r="J30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -9741,14 +10064,26 @@
       <c r="J31" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
+        </is>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 236 in stock</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -9794,14 +10129,26 @@
       <c r="J32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>81.54000000000001</v>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 151 in stock</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -9847,14 +10194,26 @@
       <c r="J33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="n">
+        <v>37.65</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
+        </is>
+      </c>
       <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 94 in stock</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -9900,14 +10259,26 @@
       <c r="J34" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="n">
+        <v>35.59</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>427.08</v>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -9953,14 +10324,26 @@
       <c r="J35" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>557.26</v>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
+        </is>
+      </c>
       <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 140 in stock</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10006,14 +10389,26 @@
       <c r="J36" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>75.67</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>605.36</v>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 57 in stock</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -10059,14 +10454,26 @@
       <c r="J37" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
+      <c r="K37" s="3" t="n">
+        <v>117.77</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>235.54</v>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 46 in stock</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -10112,14 +10519,26 @@
       <c r="J38" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A012-25-0/2394192</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 380 in stock</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -10165,14 +10584,26 @@
       <c r="J39" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
+      <c r="K39" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A023-25-0/2394201</t>
+        </is>
+      </c>
       <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 152 in stock</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -10218,14 +10649,26 @@
       <c r="J40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A034-25-0/2394193</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 34 in stock</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -10271,18 +10714,24 @@
       <c r="J41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="n">
+        <v>10.82</v>
+      </c>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-4-1437290-0.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-0/2054331</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 1305 in stock</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -10328,18 +10777,24 @@
       <c r="J42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="n">
+        <v>11.92</v>
+      </c>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-4-1437290-1.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-1/2329261</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Tube), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 506 in stock</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -10385,14 +10840,26 @@
       <c r="J43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/462A023-25-0/2394175</t>
+        </is>
+      </c>
       <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 33 in stock</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr"/>
@@ -10438,14 +10905,26 @@
       <c r="J44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT470R/1741440</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT470R</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 327849 in stock</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
@@ -11960,7 +12439,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -11982,18 +12461,26 @@
       <c r="J72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>55.13</v>
+      </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DRB12-102PAE-L018.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB12-102PAE-L018/10461602</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 61 in stock</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -12039,18 +12526,26 @@
       <c r="J73" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K73" s="3" t="inlineStr"/>
-      <c r="L73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="n">
+        <v>46.89</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>46.89</v>
+      </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DRB16-102SAE-L018.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB16-102SAE-L018/10461459</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr"/>
-      <c r="O73" s="3" t="inlineStr"/>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 45 in stock</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr"/>
@@ -12078,7 +12573,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -12100,18 +12595,26 @@
       <c r="J74" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="n">
+        <v>179.14</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>179.14</v>
+      </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DRBF-1A.html</t>
+          <t>https://www.digikey.com/en/products/detail/powell-electronics/DRBF-1A/29580951</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 10 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 37 in stock</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -12157,18 +12660,26 @@
       <c r="J75" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K75" s="3" t="inlineStr"/>
-      <c r="L75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="n">
+        <v>144.42</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>144.42</v>
+      </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-08PA-P021.html</t>
+          <t>https://www.digikey.com/en/products/detail/powell-electronics/DT04-08PA-P021/29660378</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr"/>
-      <c r="O75" s="3" t="inlineStr"/>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 10 (Tray), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 30 in stock</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr"/>
@@ -12214,18 +12725,26 @@
       <c r="J76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>49.4</v>
+      </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT04-12PA-P021.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-12PA-P021/9923072</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 1418 in stock</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -12253,7 +12772,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -12322,7 +12841,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -12391,7 +12910,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -12478,18 +12997,26 @@
       <c r="J80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>12.66</v>
+      </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-12SA.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-12SA/6566568</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 14204 in stock</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -12549,12 +13076,12 @@
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 41242 in stock</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr"/>
@@ -12582,7 +13109,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -12669,18 +13196,26 @@
       <c r="J83" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K83" s="3" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-3S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S/6566573</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr"/>
-      <c r="O83" s="3" t="inlineStr"/>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr"/>
@@ -12708,7 +13243,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -12842,7 +13377,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -12929,18 +13464,26 @@
       <c r="J87" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K87" s="3" t="inlineStr"/>
-      <c r="L87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>2.05</v>
+      </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DTM06-4S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTM06-4S/6566635</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="3" t="inlineStr"/>
+      <c r="O87" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 15700 in stock</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr"/>
@@ -15713,14 +16256,26 @@
       <c r="J135" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K135" s="3" t="inlineStr"/>
-      <c r="L135" s="3" t="inlineStr"/>
-      <c r="M135" s="3" t="inlineStr"/>
+      <c r="K135" s="3" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
+        </is>
+      </c>
       <c r="N135" s="3" t="inlineStr"/>
-      <c r="O135" s="3" t="inlineStr"/>
+      <c r="O135" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 65 in stock</t>
         </is>
       </c>
       <c r="Q135" s="3" t="inlineStr"/>
@@ -15766,14 +16321,26 @@
       <c r="J136" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K136" s="2" t="inlineStr"/>
-      <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
+        </is>
+      </c>
       <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 72 in stock</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr"/>
@@ -19095,18 +19662,26 @@
       <c r="J197" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K197" s="3" t="inlineStr"/>
-      <c r="L197" s="3" t="inlineStr"/>
+      <c r="K197" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L197" s="3" t="n">
+        <v>1.26</v>
+      </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W12S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr"/>
-      <c r="O197" s="3" t="inlineStr"/>
+      <c r="O197" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P197" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
         </is>
       </c>
       <c r="Q197" s="3" t="inlineStr"/>
@@ -19134,7 +19709,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F198" s="2" t="inlineStr">
@@ -19203,7 +19778,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -19272,7 +19847,7 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
@@ -19341,7 +19916,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -19363,18 +19938,26 @@
       <c r="J201" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K201" s="3" t="inlineStr"/>
-      <c r="L201" s="3" t="inlineStr"/>
+      <c r="K201" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L201" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W6P.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr"/>
-      <c r="O201" s="3" t="inlineStr"/>
+      <c r="O201" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P201" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
         </is>
       </c>
       <c r="Q201" s="3" t="inlineStr"/>
@@ -19402,7 +19985,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -19424,18 +20007,26 @@
       <c r="J202" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L202" s="2" t="n">
+        <v>0.42</v>
+      </c>
       <c r="M202" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W6S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr"/>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr"/>
@@ -19463,7 +20054,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -19485,18 +20076,26 @@
       <c r="J203" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K203" s="3" t="inlineStr"/>
-      <c r="L203" s="3" t="inlineStr"/>
+      <c r="K203" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L203" s="3" t="n">
+        <v>0.35</v>
+      </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W8S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
         </is>
       </c>
       <c r="N203" s="3" t="inlineStr"/>
-      <c r="O203" s="3" t="inlineStr"/>
+      <c r="O203" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P203" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
         </is>
       </c>
       <c r="Q203" s="3" t="inlineStr"/>
@@ -19524,7 +20123,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -19546,18 +20145,26 @@
       <c r="J204" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K204" s="2" t="inlineStr"/>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L204" s="2" t="n">
+        <v>0.28</v>
+      </c>
       <c r="M204" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WM-4S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr"/>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr"/>
@@ -19585,7 +20192,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>✓ TE</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -19607,18 +20214,26 @@
       <c r="J205" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K205" s="3" t="inlineStr"/>
-      <c r="L205" s="3" t="inlineStr"/>
+      <c r="K205" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L205" s="3" t="n">
+        <v>0.31</v>
+      </c>
       <c r="M205" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-WM-6S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr"/>
-      <c r="O205" s="3" t="inlineStr"/>
+      <c r="O205" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P205" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
       <c r="Q205" s="3" t="inlineStr"/>
@@ -19635,50 +20250,71 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -19691,7 +20327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:D142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19752,12 +20388,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0460-202-2031</t>
+          <t>8847 L=10</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -19774,7 +20410,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>112263-90</t>
+          <t>HD34-24-33PE</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -19796,17 +20432,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>112264-ZZ</t>
+          <t>ISO 10642 M3 x 12 A2</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19818,7 +20454,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>50M060100P030</t>
+          <t>ISO 4026 M8 x 6 A2</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -19840,7 +20476,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>8847 L=10</t>
+          <t>N0674-70 2-039</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -19862,17 +20498,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>HD34-24-33PE</t>
+          <t>ISO 10642 M3 x 12 A2</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19884,7 +20520,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>ISO 10642 M3 x 12 A2</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -19894,7 +20530,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19906,7 +20542,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ISO 4026 M8 x 6 A2</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -19928,7 +20564,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N0674-70 2-039</t>
+          <t>Lemu 2990806014</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -19950,12 +20586,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>280919-2</t>
+          <t>N0674-70 2-039</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -19967,17 +20603,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>6-1419137-4</t>
+          <t>1 928 403 874</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -19989,17 +20625,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-1/8-0-STK</t>
+          <t>12052641</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -20011,17 +20647,17 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-0-STK</t>
+          <t>12084200</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Waytek listing seen 2026-10-19 (100 pc min, 0 stock; Aptiv sheet not checked)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -20033,17 +20669,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-1/4-0-STK</t>
+          <t>12110293</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -20055,17 +20691,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-1/8-0-STK</t>
+          <t>12191819</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -20077,17 +20713,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-0-STK</t>
+          <t>13519047</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -20099,12 +20735,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>50M060100P030</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -20121,12 +20757,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ISO 10642 M3 x 12 A2</t>
+          <t>15419715</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -20136,19 +20772,19 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>2.2k 1/4W 1%</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -20158,19 +20794,19 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -20187,17 +20823,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Lemu 2990806014</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -20209,17 +20845,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Mechanical assemblies</t>
+          <t>Wire harness</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N0674-70 2-039</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -20236,12 +20872,12 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>0413-204-2005</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -20258,12 +20894,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>0413-214-1205</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -20280,12 +20916,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>0462-201-16141</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -20302,17 +20938,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>0462-201-2031</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20324,7 +20960,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>1 928 403 874</t>
+          <t>90980-10897</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20334,7 +20970,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20346,7 +20982,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>1.8k 1/4W</t>
+          <t>90980-10942</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -20356,7 +20992,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20368,7 +21004,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>10k 1/4W</t>
+          <t>90980-11062</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -20378,7 +21014,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20390,17 +21026,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>90980-11143</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20412,7 +21048,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>12052641</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -20422,7 +21058,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20434,17 +21070,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Waytek listing seen 2026-10-19 (100 pc min, 0 stock; Aptiv sheet not checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20456,7 +21092,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>120R 1/4W</t>
+          <t>90980-12068</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -20466,7 +21102,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20478,7 +21114,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>12110293</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -20488,7 +21124,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20500,7 +21136,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -20510,7 +21146,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20522,7 +21158,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>13519047</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -20532,7 +21168,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20544,7 +21180,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -20554,7 +21190,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20566,7 +21202,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>D 261 205 358-01</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -20588,12 +21224,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>1N5822</t>
+          <t>DR-25-1-0-SP</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -20610,17 +21246,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1k 1/4W</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20632,17 +21268,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>DR-25-1/2-0-SP</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20654,17 +21290,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>3.9k 1/4W</t>
+          <t>DR-25-1/4-0-SP</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20676,7 +21312,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>301A011-25-0</t>
+          <t>DR-25-2-0-SP</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -20698,7 +21334,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>301A022-25-0</t>
+          <t>DR-25-3/16-0-SP</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -20720,7 +21356,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>301A028-25-0</t>
+          <t>DR-25-3/4-0-SP</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -20742,7 +21378,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>342A012-25-0</t>
+          <t>DR-25-3/8-0-SP</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -20764,12 +21400,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>342A024-25-0</t>
+          <t>DTM06-6S</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -20786,7 +21422,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>342A034-25-0</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -20808,12 +21444,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>342A048-25-0</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -20830,17 +21466,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>382A012-25-0</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20852,17 +21488,17 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>382A023-25-0</t>
+          <t>M22759/16-10-1</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20874,17 +21510,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>382A034-25-0</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20896,17 +21532,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>462A023-25-0</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20918,7 +21554,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>470R 1/4W</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -20928,7 +21564,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20940,7 +21576,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -20950,7 +21586,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20962,17 +21598,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>M22759/16-14-6</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20984,17 +21620,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>M22759/16-14-60</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21006,17 +21642,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>M22759/16-14-62</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21028,17 +21664,17 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>M22759/16-14-63</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21050,7 +21686,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>M22759/16-14-69</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -21060,7 +21696,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21708,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -21082,7 +21718,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21094,7 +21730,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>90980-10897</t>
+          <t>M22759/16-16-20</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -21104,7 +21740,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21116,7 +21752,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>90980-10942</t>
+          <t>M22759/16-16-26</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -21126,7 +21762,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21138,7 +21774,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>90980-11062</t>
+          <t>M22759/16-16-50</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -21148,7 +21784,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21160,7 +21796,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>M22759/16-16-53</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -21170,7 +21806,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21818,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>M22759/16-16-59</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -21192,7 +21828,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21204,7 +21840,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>M22759/16-16-90</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -21214,7 +21850,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21226,7 +21862,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>90980-12068</t>
+          <t>M22759/16-18-0</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -21236,7 +21872,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21884,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>M22759/16-18-29</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -21258,7 +21894,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21270,7 +21906,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>M22759/16-18-50</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -21280,7 +21916,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21928,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>M22759/16-18-54</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -21302,7 +21938,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21950,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>M22759/16-18-7</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -21324,7 +21960,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21336,7 +21972,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>D 261 205 358-01</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -21346,7 +21982,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21358,17 +21994,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-0-SP</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21380,17 +22016,17 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>M22759/16-20-06</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21402,17 +22038,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1/2-0-SP</t>
+          <t>M22759/16-20-09</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21424,17 +22060,17 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1/4-0-SP</t>
+          <t>M22759/16-20-1</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21446,17 +22082,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>DR-25-2-0-SP</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21468,17 +22104,17 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/16-0-SP</t>
+          <t>M22759/16-20-39</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21490,17 +22126,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/4-0-SP</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21512,17 +22148,17 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/8-0-SP</t>
+          <t>M22759/16-20-5</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21534,17 +22170,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>DRB12-102PAE-L018</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21556,17 +22192,17 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>DRB16-102SAE-L018</t>
+          <t>M22759/16-20-7</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21578,17 +22214,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>DRBF-1A</t>
+          <t>M22759/16-20-8</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21600,17 +22236,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>DT04-08PA-P021</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>seller page seen 2026-10-19 (per foot)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21622,17 +22258,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>DT04-12PA-P021</t>
+          <t>M22759/16-6-9</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21644,17 +22280,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>DT06-12SA</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21666,17 +22302,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>DT06-3S</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21688,17 +22324,17 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>DTM06-4S</t>
+          <t>M22759/16-8-9</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21710,12 +22346,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>DTM06-6S</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -21732,12 +22368,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -21754,7 +22390,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -21776,7 +22412,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -21786,7 +22422,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21798,7 +22434,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -21808,7 +22444,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21820,7 +22456,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -21830,7 +22466,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21842,7 +22478,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -21852,7 +22488,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21864,7 +22500,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -21874,7 +22510,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21886,7 +22522,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -21896,7 +22532,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21908,7 +22544,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -21918,7 +22554,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21930,7 +22566,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -21940,7 +22576,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21952,7 +22588,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -21962,7 +22598,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21974,7 +22610,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -21984,7 +22620,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21996,7 +22632,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -22006,7 +22642,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22018,7 +22654,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -22028,7 +22664,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22676,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -22050,7 +22686,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22698,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -22072,7 +22708,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22084,7 +22720,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -22094,7 +22730,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22106,7 +22742,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -22116,7 +22752,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22128,7 +22764,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -22138,7 +22774,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22150,7 +22786,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -22160,7 +22796,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22172,7 +22808,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -22182,7 +22818,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22830,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -22204,7 +22840,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22852,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -22226,7 +22862,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22238,7 +22874,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -22248,7 +22884,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22896,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -22270,7 +22906,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22282,7 +22918,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -22292,7 +22928,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22940,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -22314,7 +22950,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22326,7 +22962,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -22336,7 +22972,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22348,7 +22984,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -22358,7 +22994,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22370,7 +23006,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -22380,7 +23016,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22392,7 +23028,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -22402,7 +23038,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22414,7 +23050,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -22424,7 +23060,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22436,7 +23072,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -22446,7 +23082,7 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22458,7 +23094,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -22468,7 +23104,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22480,7 +23116,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -22490,7 +23126,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22502,7 +23138,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -22512,7 +23148,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22524,7 +23160,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -22534,7 +23170,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22546,17 +23182,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22568,7 +23204,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -22578,7 +23214,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22590,7 +23226,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -22600,7 +23236,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22612,7 +23248,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -22622,7 +23258,7 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22634,7 +23270,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -22644,7 +23280,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22656,7 +23292,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -22678,7 +23314,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -22824,1130 +23460,8 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>W12S</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>W6P</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>W6S</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>W8S</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>WM-4S</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D193"/>
+  <autoFilter ref="A1:D142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$205</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,10 +546,10 @@
         <v>193</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>3252.25</v>
+        <v>4749.29</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -568,10 +568,10 @@
         <v>296</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>155</v>
+        <v>197</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3663.79</v>
+        <v>5160.83</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23</v>
@@ -9242,14 +9242,26 @@
       <c r="J17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/12052641?variant=45536631554366</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr"/>
@@ -9295,11 +9307,15 @@
       <c r="J18" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>2.24</v>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://waytekwire.com/product/aptiv-12084200-metri-pack-150-series-female</t>
+          <t>https://www.customconnectorkits.com/products/12084200-l?variant=45536283525438</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -9307,10 +9323,14 @@
           <t>https://www.ebay.de/itm/145990327082</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Waytek listing seen 2026-10-19 (100 pc min, 0 stock; Aptiv sheet not checked)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9425,14 +9445,26 @@
       <c r="J20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/12110293?variant=45536279953726</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -9478,14 +9510,26 @@
       <c r="J21" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
@@ -9531,14 +9575,26 @@
       <c r="J22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
@@ -9584,14 +9640,26 @@
       <c r="J23" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
+        </is>
+      </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -9637,14 +9705,26 @@
       <c r="J24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -11267,14 +11347,26 @@
       <c r="J50" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.customconnectorkits.com/products/8100-0461-l?variant=46049028800830</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -11365,14 +11457,26 @@
       <c r="J52" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/toyota-lexus-90980-10897-8-pin-connector-kit?variant=29504109805610</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr"/>
@@ -11463,14 +11567,26 @@
       <c r="J54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/2-way-connector-kit-for-toyota-lexus-90980-11062-water-temperature-sensor-22-18-awg?variant=11482559741994</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -11948,14 +12064,26 @@
       <c r="J63" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="3" t="inlineStr"/>
+      <c r="K63" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/6-way-connector-kit-same-as-bosch-d261-205-358-01-23-20-awg?variant=40430818852899</t>
+        </is>
+      </c>
       <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr"/>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr"/>
@@ -12001,14 +12129,26 @@
       <c r="J64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>60.24</v>
+      </c>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/1-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737243683</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $6.12 per ft</t>
+        </is>
+      </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -12115,14 +12255,26 @@
       <c r="J66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/1-2-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735736355</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $4.34 per ft</t>
+        </is>
+      </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -12172,14 +12324,26 @@
       <c r="J67" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K67" s="3" t="inlineStr"/>
-      <c r="L67" s="3" t="inlineStr"/>
-      <c r="M67" s="3" t="inlineStr"/>
+      <c r="K67" s="3" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>78.54000000000001</v>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/1-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735113763</t>
+        </is>
+      </c>
       <c r="N67" s="3" t="inlineStr"/>
-      <c r="O67" s="3" t="inlineStr"/>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $1.71 per ft</t>
+        </is>
+      </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -12286,14 +12450,26 @@
       <c r="J69" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="K69" s="3" t="inlineStr"/>
-      <c r="L69" s="3" t="inlineStr"/>
-      <c r="M69" s="3" t="inlineStr"/>
+      <c r="K69" s="3" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
+        </is>
+      </c>
       <c r="N69" s="3" t="inlineStr"/>
-      <c r="O69" s="3" t="inlineStr"/>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
+        </is>
+      </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -12343,14 +12519,26 @@
       <c r="J70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/3-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737112611</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $4.57 per ft</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -12400,14 +12588,26 @@
       <c r="J71" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="K71" s="3" t="inlineStr"/>
-      <c r="L71" s="3" t="inlineStr"/>
-      <c r="M71" s="3" t="inlineStr"/>
+      <c r="K71" s="3" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>129.96</v>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/3-8-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735343139</t>
+        </is>
+      </c>
       <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $3.30 per ft</t>
+        </is>
+      </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -13529,18 +13729,26 @@
       <c r="J88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>2.48</v>
+      </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DTM06-6S.html</t>
+          <t>https://www.ksvlooms.com/products/dtm06-6s-deutsch-dtm-housing?variant=43643315290147</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -13692,14 +13900,26 @@
       <c r="J91" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K91" s="3" t="inlineStr"/>
-      <c r="L91" s="3" t="inlineStr"/>
-      <c r="M91" s="3" t="inlineStr"/>
+      <c r="K91" s="3" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/10-awg-black-tefzel-wire-m22759-16-10-0-cut-length?variant=40451551199267</t>
+        </is>
+      </c>
       <c r="N91" s="3" t="inlineStr"/>
-      <c r="O91" s="3" t="inlineStr"/>
+      <c r="O91" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P91" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q91" s="3" t="inlineStr">
@@ -13749,14 +13969,26 @@
       <c r="J92" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="M92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/10-awg-brown-tefzel-wire-m22759-16-10-1-spool?variant=40423436288035</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -13806,14 +14038,26 @@
       <c r="J93" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="K93" s="3" t="inlineStr"/>
-      <c r="L93" s="3" t="inlineStr"/>
-      <c r="M93" s="3" t="inlineStr"/>
+      <c r="K93" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
+        </is>
+      </c>
       <c r="N93" s="3" t="inlineStr"/>
-      <c r="O93" s="3" t="inlineStr"/>
+      <c r="O93" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P93" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q93" s="3" t="inlineStr">
@@ -13863,14 +14107,26 @@
       <c r="J94" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K94" s="2" t="inlineStr"/>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="M94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/12-awg-black-tefzel-wire-m22759-16-12-0-spool?variant=40415052726307</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -13920,14 +14176,26 @@
       <c r="J95" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K95" s="3" t="inlineStr"/>
-      <c r="L95" s="3" t="inlineStr"/>
-      <c r="M95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/12-awg-red-tefzel-wire-m22759-16-12-2-spool?variant=40415053152291</t>
+        </is>
+      </c>
       <c r="N95" s="3" t="inlineStr"/>
-      <c r="O95" s="3" t="inlineStr"/>
+      <c r="O95" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P95" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q95" s="3" t="inlineStr">
@@ -13977,14 +14245,26 @@
       <c r="J96" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K96" s="2" t="inlineStr"/>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/14-awg-black-tefzel-wire-m22759-16-14-0-spool?variant=40415048695843</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -14103,14 +14383,26 @@
       <c r="J98" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>87.36</v>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/14-awg-blue-tefzel-wire-m22759-16-14-6-spool?variant=40423417708579</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -14388,14 +14680,26 @@
       <c r="J103" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K103" s="3" t="inlineStr"/>
-      <c r="L103" s="3" t="inlineStr"/>
-      <c r="M103" s="3" t="inlineStr"/>
+      <c r="K103" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L103" s="3" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
+        </is>
+      </c>
       <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="3" t="inlineStr"/>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
@@ -14856,14 +15160,26 @@
       <c r="J111" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K111" s="3" t="inlineStr"/>
-      <c r="L111" s="3" t="inlineStr"/>
-      <c r="M111" s="3" t="inlineStr"/>
+      <c r="K111" s="3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L111" s="3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-black-tefzel-wire-m22759-16-18-0-spool?variant=40415044370467</t>
+        </is>
+      </c>
       <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="3" t="inlineStr"/>
+      <c r="O111" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
@@ -15153,14 +15469,26 @@
       <c r="J116" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
-      <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="M116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-purple-tefzel-wire-m22759-16-18-7-spool?variant=40423402700835</t>
+        </is>
+      </c>
       <c r="N116" s="2" t="inlineStr"/>
-      <c r="O116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15210,14 +15538,26 @@
       <c r="J117" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="K117" s="3" t="inlineStr"/>
-      <c r="L117" s="3" t="inlineStr"/>
-      <c r="M117" s="3" t="inlineStr"/>
+      <c r="K117" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L117" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
+        </is>
+      </c>
       <c r="N117" s="3" t="inlineStr"/>
-      <c r="O117" s="3" t="inlineStr"/>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q117" s="3" t="inlineStr">
@@ -15267,14 +15607,26 @@
       <c r="J118" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
+        </is>
+      </c>
       <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15438,14 +15790,26 @@
       <c r="J121" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="K121" s="3" t="inlineStr"/>
-      <c r="L121" s="3" t="inlineStr"/>
-      <c r="M121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-brown-tefzel-wire-m22759-16-20-1-spool?variant=40415026708515</t>
+        </is>
+      </c>
       <c r="N121" s="3" t="inlineStr"/>
-      <c r="O121" s="3" t="inlineStr"/>
+      <c r="O121" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
@@ -15564,14 +15928,26 @@
       <c r="J123" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr"/>
-      <c r="M123" s="3" t="inlineStr"/>
+      <c r="K123" s="3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
+        </is>
+      </c>
       <c r="N123" s="3" t="inlineStr"/>
-      <c r="O123" s="3" t="inlineStr"/>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr">
@@ -15678,14 +16054,26 @@
       <c r="J125" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="K125" s="3" t="inlineStr"/>
-      <c r="L125" s="3" t="inlineStr"/>
-      <c r="M125" s="3" t="inlineStr"/>
+      <c r="K125" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L125" s="3" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
+        </is>
+      </c>
       <c r="N125" s="3" t="inlineStr"/>
-      <c r="O125" s="3" t="inlineStr"/>
+      <c r="O125" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q125" s="3" t="inlineStr">
@@ -15735,14 +16123,26 @@
       <c r="J126" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
-      <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-green-tefzel-wire-m22759-16-20-5-spool?variant=40415028838435</t>
+        </is>
+      </c>
       <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -15792,14 +16192,26 @@
       <c r="J127" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K127" s="3" t="inlineStr"/>
-      <c r="L127" s="3" t="inlineStr"/>
-      <c r="M127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L127" s="3" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
+        </is>
+      </c>
       <c r="N127" s="3" t="inlineStr"/>
-      <c r="O127" s="3" t="inlineStr"/>
+      <c r="O127" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P127" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q127" s="3" t="inlineStr">
@@ -15849,14 +16261,26 @@
       <c r="J128" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
-      <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="M128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-purple-tefzel-wire-m22759-16-20-7-spool?variant=40415029198883</t>
+        </is>
+      </c>
       <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -15906,14 +16330,26 @@
       <c r="J129" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K129" s="3" t="inlineStr"/>
-      <c r="L129" s="3" t="inlineStr"/>
-      <c r="M129" s="3" t="inlineStr"/>
+      <c r="K129" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-gray-tefzel-wire-m22759-16-20-8-spool?variant=40415029264419</t>
+        </is>
+      </c>
       <c r="N129" s="3" t="inlineStr"/>
-      <c r="O129" s="3" t="inlineStr"/>
+      <c r="O129" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q129" s="3" t="inlineStr">
@@ -15963,11 +16399,15 @@
       <c r="J130" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
-      <c r="L130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>31.68</v>
+      </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>https://wingsandwheels.com/tefzel-wire-20-gauge-new.html</t>
+          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
         </is>
       </c>
       <c r="N130" s="4" t="inlineStr">
@@ -15975,10 +16415,14 @@
           <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
         </is>
       </c>
-      <c r="O130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16028,14 +16472,26 @@
       <c r="J131" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K131" s="3" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr"/>
-      <c r="M131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/6-awg-white-tefzel-wire-m22759-16-6-9-spool?variant=40415058198563</t>
+        </is>
+      </c>
       <c r="N131" s="3" t="inlineStr"/>
-      <c r="O131" s="3" t="inlineStr"/>
+      <c r="O131" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q131" s="3" t="inlineStr">
@@ -16085,14 +16541,26 @@
       <c r="J132" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K132" s="2" t="inlineStr"/>
-      <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
+        </is>
+      </c>
       <c r="N132" s="2" t="inlineStr"/>
-      <c r="O132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16142,14 +16610,26 @@
       <c r="J133" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K133" s="3" t="inlineStr"/>
-      <c r="L133" s="3" t="inlineStr"/>
-      <c r="M133" s="3" t="inlineStr"/>
+      <c r="K133" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
+        </is>
+      </c>
       <c r="N133" s="3" t="inlineStr"/>
-      <c r="O133" s="3" t="inlineStr"/>
+      <c r="O133" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q133" s="3" t="inlineStr">
@@ -16199,14 +16679,26 @@
       <c r="J134" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="K134" s="2" t="inlineStr"/>
-      <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="M134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/8-awg-white-tefzel-wire-m22759-16-8-9-spool?variant=40415055740963</t>
+        </is>
+      </c>
       <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -20255,66 +20747,105 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -20327,7 +20858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D142"/>
+  <dimension ref="A1:D100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20630,7 +21161,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12052641</t>
+          <t>2.2k 1/4W 1%</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -20640,7 +21171,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -20652,12 +21183,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Waytek listing seen 2026-10-19 (100 pc min, 0 stock; Aptiv sheet not checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -20674,12 +21205,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>12110293</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -20696,12 +21227,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -20718,12 +21249,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>13519047</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -20740,12 +21271,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -20762,7 +21293,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -20772,7 +21303,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20784,7 +21315,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>90980-10942</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -20794,7 +21325,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20806,7 +21337,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>90980-11143</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -20816,7 +21347,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20828,17 +21359,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20850,17 +21381,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20872,17 +21403,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>90980-12068</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20894,17 +21425,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20916,7 +21447,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>8100-0461</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20926,7 +21457,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20938,7 +21469,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -20948,7 +21479,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20960,7 +21491,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>90980-10897</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20970,7 +21501,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20982,17 +21513,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>90980-10942</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21004,17 +21535,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>90980-11062</t>
+          <t>DR-25-2-0-SP</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21026,17 +21557,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21579,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -21058,7 +21589,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21070,7 +21601,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>M22759/16-14-60</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -21080,7 +21611,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21092,7 +21623,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>90980-12068</t>
+          <t>M22759/16-14-62</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -21102,7 +21633,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21645,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>M22759/16-14-63</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -21124,7 +21655,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21667,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>M22759/16-14-69</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -21146,7 +21677,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21158,7 +21689,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>M22759/16-16-20</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -21168,7 +21699,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21180,7 +21711,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>M22759/16-16-26</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -21190,7 +21721,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21202,7 +21733,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>D 261 205 358-01</t>
+          <t>M22759/16-16-50</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -21212,7 +21743,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21224,17 +21755,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1-0-SP</t>
+          <t>M22759/16-16-53</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21246,17 +21777,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>M22759/16-16-59</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21268,17 +21799,17 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1/2-0-SP</t>
+          <t>M22759/16-16-90</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21290,17 +21821,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1/4-0-SP</t>
+          <t>M22759/16-18-29</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21312,17 +21843,17 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>DR-25-2-0-SP</t>
+          <t>M22759/16-18-50</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21334,17 +21865,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/16-0-SP</t>
+          <t>M22759/16-18-54</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21356,17 +21887,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/4-0-SP</t>
+          <t>M22759/16-20-06</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21378,17 +21909,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/8-0-SP</t>
+          <t>M22759/16-20-09</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21400,17 +21931,17 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTM06-6S</t>
+          <t>M22759/16-20-39</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21422,12 +21953,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -21444,7 +21975,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -21466,7 +21997,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -21476,7 +22007,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21488,7 +22019,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -21498,7 +22029,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21510,7 +22041,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -21520,7 +22051,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21532,7 +22063,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -21542,7 +22073,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21554,7 +22085,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -21564,7 +22095,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21576,7 +22107,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -21586,7 +22117,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21598,7 +22129,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -21608,7 +22139,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21620,7 +22151,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -21630,7 +22161,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21642,7 +22173,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -21652,7 +22183,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21664,7 +22195,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -21674,7 +22205,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21686,7 +22217,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -21696,7 +22227,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21708,7 +22239,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -21718,7 +22249,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21730,7 +22261,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -21740,7 +22271,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21752,7 +22283,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -21762,7 +22293,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21774,7 +22305,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -21784,7 +22315,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21796,7 +22327,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -21806,7 +22337,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21818,7 +22349,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -21828,7 +22359,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21840,7 +22371,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -21850,7 +22381,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21862,7 +22393,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -21872,7 +22403,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21884,7 +22415,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -21894,7 +22425,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21906,7 +22437,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -21916,7 +22447,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21928,7 +22459,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -21938,7 +22469,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21950,7 +22481,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -21960,7 +22491,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21972,7 +22503,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -21982,7 +22513,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21994,7 +22525,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -22004,7 +22535,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22016,7 +22547,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -22026,7 +22557,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22038,7 +22569,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -22048,7 +22579,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22591,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -22070,7 +22601,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22082,7 +22613,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -22092,7 +22623,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22635,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -22114,7 +22645,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22657,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -22136,7 +22667,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22148,7 +22679,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -22158,7 +22689,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22170,7 +22701,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -22180,7 +22711,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22192,7 +22723,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -22202,7 +22733,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22214,7 +22745,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -22224,7 +22755,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22236,17 +22767,17 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>seller page seen 2026-10-19 (per foot)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22789,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -22268,7 +22799,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22280,7 +22811,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -22290,7 +22821,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22833,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -22312,7 +22843,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22324,7 +22855,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -22334,7 +22865,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22536,932 +23067,8 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D142"/>
+  <autoFilter ref="A1:D100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$205</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>105</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4749.29</v>
+        <v>4757.91</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>197</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5160.83</v>
+        <v>5169.45</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23</v>
@@ -8127,7 +8127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q205"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12116,7 +12116,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -12127,13 +12127,13 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>20.08</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>60.24</v>
+        <v>20.08</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2.3 m of bundle + 10 % cut / recovery margin</t>
+          <t>0.8 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K65" s="3" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr"/>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>6.3 m of bundle + 10 % cut / recovery margin</t>
+          <t>1.3 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -12253,13 +12253,13 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>14.24</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>71.2</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>3.7 m of bundle + 10 % cut / recovery margin</t>
+          <t>5.6 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12311,7 +12311,7 @@
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -12322,13 +12322,13 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>5.61</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>78.54000000000001</v>
+        <v>28.05</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>11.9 m of bundle + 10 % cut / recovery margin</t>
+          <t>3.9 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12365,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>DR-25-2-0-SP</t>
+          <t>DR-25-3/16-0-SP</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -12376,11 +12376,11 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 51.0 MM EXPANDED ID, 25.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -12391,21 +12391,33 @@
         <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
+        </is>
+      </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>0.4 m of bundle + 10 % cut / recovery margin</t>
+          <t>11.6 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12434,7 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/16-0-SP</t>
+          <t>DR-25-3/4-0-SP</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -12433,11 +12445,11 @@
       <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 19.0 MM EXPANDED ID, 9.5 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
@@ -12448,23 +12460,23 @@
         <v>0</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>5.54</v>
+        <v>14.99</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>72.02</v>
+        <v>119.92</v>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
+          <t>https://www.ksvlooms.com/products/3-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737112611</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
+          <t>KSV Looms, 2026-10-20; $4.57 per ft</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -12474,7 +12486,7 @@
       </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
-          <t>11.2 m of bundle + 10 % cut / recovery margin</t>
+          <t>6.8 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12503,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/4-0-SP</t>
+          <t>DR-25-3/8-0-SP</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -12502,11 +12514,11 @@
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 19.0 MM EXPANDED ID, 9.5 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 9.53 MM EXPANDED ID, 4.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -12517,23 +12529,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>14.99</v>
+        <v>10.83</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>59.96</v>
+        <v>140.79</v>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737112611</t>
+          <t>https://www.ksvlooms.com/products/3-8-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735343139</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $4.57 per ft</t>
+          <t>KSV Looms, 2026-10-20; $3.30 per ft</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -12543,7 +12555,7 @@
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>2.9 m of bundle + 10 % cut / recovery margin</t>
+          <t>11.2 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12560,61 +12572,61 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/8-0-SP</t>
+          <t>DRB12-102PAE-L018</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 9.53 MM EXPANDED ID, 4.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, DRB, 102 POS, PIN CONTACTS, E SEAL, A KEY, WIRE ROUTER, FLANGE MOUNT</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>10.83</v>
+        <v>55.13</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>129.96</v>
+        <v>55.13</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-8-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735343139</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB12-102PAE-L018/10461602</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $3.30 per ft</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q71" s="3" t="inlineStr">
-        <is>
-          <t>10.7 m of bundle + 10 % cut / recovery margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 61 in stock</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12629,7 +12641,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>DRB12-102PAE-L018</t>
+          <t>DRB16-102SAE-L018</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -12637,14 +12649,10 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DRB, 102 POS, PIN CONTACTS, E SEAL, A KEY, WIRE ROUTER, FLANGE MOUNT</t>
+          <t>CONNECTOR, PLUG, DRB, 102 POS, SOCKET CONTACTS, E SEAL, A KEY, WIRE ROUTER</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -12662,14 +12670,14 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>55.13</v>
+        <v>46.89</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>55.13</v>
+        <v>46.89</v>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB12-102PAE-L018/10461602</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB16-102SAE-L018/10461459</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr"/>
@@ -12680,7 +12688,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 61 in stock</t>
+          <t>Digi-Key API 2026-10-20: 45 in stock</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -12698,7 +12706,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>DRB16-102SAE-L018</t>
+          <t>DRBF-1A</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -12706,10 +12714,14 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr"/>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DRB, 102 POS, SOCKET CONTACTS, E SEAL, A KEY, WIRE ROUTER</t>
+          <t>FLANGE, MOUNTING, DRB 102/128 SERIES</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
@@ -12727,25 +12739,25 @@
         <v>1</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>46.89</v>
+        <v>179.14</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>46.89</v>
+        <v>179.14</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB16-102SAE-L018/10461459</t>
+          <t>https://www.digikey.com/en/products/detail/powell-electronics/DRBF-1A/29580951</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 10 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 45 in stock</t>
+          <t>Digi-Key API 2026-10-20: 37 in stock</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr"/>
@@ -12763,7 +12775,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>DRBF-1A</t>
+          <t>DT04-08PA-P021</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -12771,14 +12783,10 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+      <c r="E74" s="2" t="inlineStr"/>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>FLANGE, MOUNTING, DRB 102/128 SERIES</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 8 POS, BUSSED 1 X 8, NICKEL PINS MOULDED IN, 13 A PER PIN, 52 A BUS, WEDGELOCK INCLUDED, GRAY</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
@@ -12796,25 +12804,25 @@
         <v>1</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>179.14</v>
+        <v>144.42</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>179.14</v>
+        <v>144.42</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/powell-electronics/DRBF-1A/29580951</t>
+          <t>https://www.digikey.com/en/products/detail/powell-electronics/DT04-08PA-P021/29660378</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 10 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 10 (Tray), 2026-10-20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 37 in stock</t>
+          <t>Digi-Key API 2026-10-20: 30 in stock</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -12832,7 +12840,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>DT04-08PA-P021</t>
+          <t>DT04-12PA-P021</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -12843,11 +12851,11 @@
       <c r="E75" s="3" t="inlineStr"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 8 POS, BUSSED 1 X 8, NICKEL PINS MOULDED IN, 13 A PER PIN, 52 A BUS, WEDGELOCK INCLUDED, GRAY</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 12 POS, BUSSED 1 X 12, NICKEL PINS MOULDED IN, 13 A PER PIN, 78 A BUS, WEDGELOCK INCLUDED, GRAY</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
@@ -12858,28 +12866,28 @@
         <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>144.42</v>
+        <v>12.35</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>144.42</v>
+        <v>49.4</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/powell-electronics/DT04-08PA-P021/29660378</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-12PA-P021/9923072</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 10 (Tray), 2026-10-20</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 30 in stock</t>
+          <t>Digi-Key API 2026-10-20: 1418 in stock</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr"/>
@@ -12897,7 +12905,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>DT04-12PA-P021</t>
+          <t>DT04-2P</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -12905,14 +12913,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 12 POS, BUSSED 1 X 12, NICKEL PINS MOULDED IN, 13 A PER PIN, 78 A BUS, WEDGELOCK INCLUDED, GRAY</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 2 POS, PIN CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -12923,28 +12935,28 @@
         <v>0</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>12.35</v>
+        <v>0.67</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>49.4</v>
+        <v>1.34</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-12PA-P021/9923072</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-2P/6566582</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 1418 in stock</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr"/>
@@ -12962,7 +12974,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>DT04-2P</t>
+          <t>DT04-6P</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -12977,7 +12989,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 2 POS, PIN CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 6 POS, PIN CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
@@ -12995,14 +13007,14 @@
         <v>2</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.67</v>
+        <v>2.34</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>1.34</v>
+        <v>4.68</v>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-2P/6566582</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-6P/6566585</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr"/>
@@ -13031,7 +13043,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>DT04-6P</t>
+          <t>DT06-08SA</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -13046,11 +13058,11 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 6 POS, PIN CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -13061,17 +13073,17 @@
         <v>0</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2.34</v>
+        <v>3.81</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>4.68</v>
+        <v>3.81</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-6P/6566585</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
@@ -13100,26 +13112,22 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>DT06-08SA</t>
+          <t>DT06-12SA</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
@@ -13127,31 +13135,31 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>3.81</v>
+        <v>4.22</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>3.81</v>
+        <v>12.66</v>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-12SA/6566568</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 14204 in stock</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr"/>
@@ -13169,22 +13177,22 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>DT06-12SA</t>
+          <t>DT06-2S</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -13192,20 +13200,20 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>4.22</v>
+        <v>0.77</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>12.66</v>
+        <v>2.31</v>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-12SA/6566568</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
@@ -13216,7 +13224,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 14204 in stock</t>
+          <t>Digi-Key API 2026-10-20: 41242 in stock</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -13234,7 +13242,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>DT06-2S</t>
+          <t>DT06-2S-CE05</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -13242,14 +13250,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr"/>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
@@ -13260,28 +13272,28 @@
         <v>0</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K81" s="3" t="n">
         <v>0.77</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>2.31</v>
+        <v>6.16</v>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
+          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 41242 in stock</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr"/>
@@ -13299,26 +13311,22 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>DT06-2S-CE05</t>
+          <t>DT06-3S</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -13329,28 +13337,28 @@
         <v>0</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>6.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S/6566573</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -13368,7 +13376,7 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>DT06-3S</t>
+          <t>DT06-3S-CE05</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -13376,10 +13384,14 @@
           <t>TE Connectivity DEUTSCH</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr"/>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
@@ -13397,25 +13409,25 @@
         <v>1</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S/6566573</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="3" t="inlineStr"/>
@@ -13433,26 +13445,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>DT06-3S-CE05</t>
+          <t>DT06-6S</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -13463,17 +13471,17 @@
         <v>0</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2.06</v>
+        <v>5.04</v>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
@@ -13502,7 +13510,7 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>DT06-6S</t>
+          <t>DTHD06-1-8S</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -13510,14 +13518,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
@@ -13528,17 +13540,17 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>2.52</v>
+        <v>3.48</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>5.04</v>
+        <v>13.92</v>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr"/>
@@ -13567,26 +13579,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>DTHD06-1-8S</t>
+          <t>DTM06-4S</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
+          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -13597,28 +13605,28 @@
         <v>0</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3.48</v>
+        <v>2.05</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>13.92</v>
+        <v>2.05</v>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTM06-4S/6566635</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 15700 in stock</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -13636,7 +13644,7 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>DTM06-4S</t>
+          <t>DTM06-6S</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -13647,7 +13655,7 @@
       <c r="E87" s="3" t="inlineStr"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
+          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
@@ -13665,25 +13673,25 @@
         <v>1</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTM06-4S/6566635</t>
+          <t>https://www.ksvlooms.com/products/dtm06-6s-deutsch-dtm-housing?variant=43643315290147</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 15700 in stock</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr"/>
@@ -13701,18 +13709,18 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>DTM06-6S</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
+          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
@@ -13729,26 +13737,14 @@
       <c r="J88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K88" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="M88" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/dtm06-6s-deutsch-dtm-housing?variant=43643315290147</t>
-        </is>
-      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr"/>
@@ -13766,22 +13762,22 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>CNLINKO</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
+          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
@@ -13792,7 +13788,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K89" s="3" t="inlineStr"/>
       <c r="L89" s="3" t="inlineStr"/>
@@ -13801,7 +13797,7 @@
       <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q89" s="3" t="inlineStr"/>
@@ -13819,18 +13815,18 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>CNLINKO</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
@@ -13838,7 +13834,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
@@ -13847,17 +13843,33 @@
       <c r="J90" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
-      <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="M90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/10-awg-black-tefzel-wire-m22759-16-10-0-cut-length?variant=40451551199267</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q90" s="2" t="inlineStr"/>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>0.9 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -13872,7 +13884,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>M22759/16-10-1</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -13883,11 +13895,11 @@
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
@@ -13898,17 +13910,17 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>4.08</v>
+        <v>2.72</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>16.32</v>
+        <v>21.76</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-black-tefzel-wire-m22759-16-10-0-cut-length?variant=40451551199267</t>
+          <t>https://www.ksvlooms.com/products/10-awg-brown-tefzel-wire-m22759-16-10-1-spool?variant=40423436288035</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr"/>
@@ -13924,7 +13936,7 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>0.9 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -13941,7 +13953,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -13952,11 +13964,11 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13967,17 +13979,17 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>21.76</v>
+        <v>115.5</v>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-brown-tefzel-wire-m22759-16-10-1-spool?variant=40423436288035</t>
+          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr"/>
@@ -13993,7 +14005,7 @@
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>8.7 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14022,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -14021,11 +14033,11 @@
       <c r="E93" s="3" t="inlineStr"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
@@ -14036,17 +14048,17 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>115.5</v>
+        <v>7.12</v>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
+          <t>https://www.ksvlooms.com/products/12-awg-black-tefzel-wire-m22759-16-12-0-spool?variant=40415052726307</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr"/>
@@ -14062,7 +14074,7 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>8.7 m in the master + 15% margin</t>
+          <t>0.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14091,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -14090,11 +14102,11 @@
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -14105,17 +14117,17 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>3.56</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>7.12</v>
+        <v>10.68</v>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/12-awg-black-tefzel-wire-m22759-16-12-0-spool?variant=40415052726307</t>
+          <t>https://www.ksvlooms.com/products/12-awg-red-tefzel-wire-m22759-16-12-2-spool?variant=40415053152291</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr"/>
@@ -14131,7 +14143,7 @@
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>0.3 m in the master + 15% margin</t>
+          <t>0.7 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14160,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -14159,11 +14171,11 @@
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
@@ -14174,17 +14186,17 @@
         <v>0</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>3.56</v>
+        <v>2.56</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>10.68</v>
+        <v>10.24</v>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/12-awg-red-tefzel-wire-m22759-16-12-2-spool?variant=40415053152291</t>
+          <t>https://www.ksvlooms.com/products/14-awg-black-tefzel-wire-m22759-16-14-0-spool?variant=40415048695843</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr"/>
@@ -14200,7 +14212,7 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>0.7 m in the master + 15% margin</t>
+          <t>0.9 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14229,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -14228,11 +14240,11 @@
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -14243,33 +14255,33 @@
         <v>0</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2.56</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>10.24</v>
+        <v>31</v>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/14-awg-black-tefzel-wire-m22759-16-14-0-spool?variant=40415048695843</t>
+          <t>https://www.awcwire.com/product/m22759_16-14</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>0.9 m in the master + 15% margin</t>
+          <t>8.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14298,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-14-6</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -14297,11 +14309,11 @@
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
@@ -14312,33 +14324,33 @@
         <v>0</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>1</v>
+        <v>3.12</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>31</v>
+        <v>87.36</v>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-14</t>
+          <t>https://www.ksvlooms.com/products/14-awg-blue-tefzel-wire-m22759-16-14-6-spool?variant=40423417708579</t>
         </is>
       </c>
       <c r="N97" s="3" t="inlineStr"/>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>7.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14367,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>M22759/16-14-60</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -14366,11 +14378,11 @@
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -14381,33 +14393,21 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K98" s="2" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>87.36</v>
-      </c>
-      <c r="M98" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/14-awg-blue-tefzel-wire-m22759-16-14-6-spool?variant=40423417708579</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O98" s="2" t="inlineStr"/>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>7.3 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-14-62</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -14435,11 +14435,11 @@
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr"/>
@@ -14464,7 +14464,7 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>2.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-14-63</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -14492,11 +14492,11 @@
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
@@ -14521,7 +14521,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>2.8 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-14-69</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -14549,7 +14549,7 @@
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -14606,11 +14606,11 @@
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14621,21 +14621,33 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K102" s="2" t="inlineStr"/>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>3.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14664,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -14663,11 +14675,11 @@
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
@@ -14678,33 +14690,33 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>1.88</v>
+        <v>1</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>26.32</v>
+        <v>32</v>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
+          <t>https://www.awcwire.com/product/m22759_16-16</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr"/>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>3.5 m in the master + 15% margin</t>
+          <t>8.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14733,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-20</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -14732,11 +14744,11 @@
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -14747,33 +14759,21 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M104" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-16</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O104" s="2" t="inlineStr"/>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>8.4 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14790,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-16-26</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -14801,11 +14801,11 @@
       <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K105" s="3" t="inlineStr"/>
       <c r="L105" s="3" t="inlineStr"/>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>2.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>M22759/16-16-50</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -14858,11 +14858,11 @@
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>2.4 m in the master + 15% margin</t>
+          <t>4.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>M22759/16-16-53</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -14915,7 +14915,7 @@
       <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>4.2 m in the master + 15% margin</t>
+          <t>4.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>M22759/16-16-59</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -14972,11 +14972,11 @@
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
@@ -15001,7 +15001,7 @@
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>4.1 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>M22759/16-16-90</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -15029,11 +15029,11 @@
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, WHITE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K109" s="3" t="inlineStr"/>
       <c r="L109" s="3" t="inlineStr"/>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>2.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>M22759/16-18-0</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -15086,11 +15086,11 @@
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, WHITE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -15101,21 +15101,33 @@
         <v>0</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K110" s="2" t="inlineStr"/>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-black-tefzel-wire-m22759-16-18-0-spool?variant=40415044370467</t>
+        </is>
+      </c>
       <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>2.3 m in the master + 15% margin</t>
+          <t>0.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15132,7 +15144,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -15143,11 +15155,11 @@
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -15158,33 +15170,33 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>1.52</v>
+        <v>1</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>3.04</v>
+        <v>22</v>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/18-awg-black-tefzel-wire-m22759-16-18-0-spool?variant=40415044370467</t>
+          <t>https://www.awcwire.com/product/m22759_16-18</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr"/>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>0.4 m in the master + 15% margin</t>
+          <t>5.7 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15201,7 +15213,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-18-29</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -15212,11 +15224,11 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -15227,33 +15239,21 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="M112" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-18</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
       <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O112" s="2" t="inlineStr"/>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>5.7 m in the master + 15% margin</t>
+          <t>0.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>M22759/16-18-50</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -15281,11 +15281,11 @@
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr"/>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>0.4 m in the master + 15% margin</t>
+          <t>7.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>M22759/16-18-54</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -15338,11 +15338,11 @@
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>7.2 m in the master + 15% margin</t>
+          <t>8.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>M22759/16-18-7</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -15395,11 +15395,11 @@
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -15410,21 +15410,33 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K115" s="3" t="inlineStr"/>
-      <c r="L115" s="3" t="inlineStr"/>
-      <c r="M115" s="3" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L115" s="3" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-purple-tefzel-wire-m22759-16-18-7-spool?variant=40423402700835</t>
+        </is>
+      </c>
       <c r="N115" s="3" t="inlineStr"/>
-      <c r="O115" s="3" t="inlineStr"/>
+      <c r="O115" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>8.3 m in the master + 15% margin</t>
+          <t>7.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15441,7 +15453,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -15452,11 +15464,11 @@
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -15467,17 +15479,17 @@
         <v>0</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>38.08</v>
+        <v>16</v>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/18-awg-purple-tefzel-wire-m22759-16-18-7-spool?variant=40423402700835</t>
+          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr"/>
@@ -15493,7 +15505,7 @@
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>7.4 m in the master + 15% margin</t>
+          <t>2.6 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15522,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -15521,11 +15533,11 @@
       <c r="E117" s="3" t="inlineStr"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -15536,17 +15548,17 @@
         <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="L117" s="3" t="n">
-        <v>16</v>
+        <v>27.72</v>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
+          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr"/>
@@ -15562,7 +15574,7 @@
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>2.6 m in the master + 15% margin</t>
+          <t>5.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15579,7 +15591,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-20-06</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -15590,11 +15602,11 @@
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -15605,33 +15617,21 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="M118" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K118" s="2" t="inlineStr"/>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O118" s="2" t="inlineStr"/>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>5.4 m in the master + 15% margin</t>
+          <t>0.6 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>M22759/16-20-09</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -15659,11 +15659,11 @@
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
       <c r="L119" s="3" t="inlineStr"/>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>0.6 m in the master + 15% margin</t>
+          <t>6.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>M22759/16-20-1</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -15716,11 +15716,11 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -15731,21 +15731,33 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K120" s="2" t="inlineStr"/>
-      <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="M120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-brown-tefzel-wire-m22759-16-20-1-spool?variant=40415026708515</t>
+        </is>
+      </c>
       <c r="N120" s="2" t="inlineStr"/>
-      <c r="O120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>6.4 m in the master + 15% margin</t>
+          <t>6.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15762,7 +15774,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -15773,11 +15785,11 @@
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
@@ -15788,33 +15800,33 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>23.52</v>
+        <v>14</v>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-brown-tefzel-wire-m22759-16-20-1-spool?variant=40415026708515</t>
+          <t>https://www.awcwire.com/product/m22759_16-20</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr"/>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>6.3 m in the master + 15% margin</t>
+          <t>3.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15831,7 +15843,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -15842,11 +15854,11 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -15857,33 +15869,33 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>14</v>
+        <v>32.24</v>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-20</t>
+          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr"/>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>3.5 m in the master + 15% margin</t>
+          <t>8.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15900,7 +15912,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-20-39</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -15911,11 +15923,11 @@
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -15926,33 +15938,21 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="K123" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L123" s="3" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="M123" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K123" s="3" t="inlineStr"/>
+      <c r="L123" s="3" t="inlineStr"/>
+      <c r="M123" s="3" t="inlineStr"/>
       <c r="N123" s="3" t="inlineStr"/>
-      <c r="O123" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>1.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15969,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -15980,11 +15980,11 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -15995,21 +15995,33 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K124" s="2" t="inlineStr"/>
-      <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="M124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
+        </is>
+      </c>
       <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>1.1 m in the master + 15% margin</t>
+          <t>8.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16026,7 +16038,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-5</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -16037,11 +16049,11 @@
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, GREEN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -16052,17 +16064,17 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>36.96</v>
+        <v>32.24</v>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
+          <t>https://www.ksvlooms.com/products/20-awg-green-tefzel-wire-m22759-16-20-5-spool?variant=40415028838435</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr"/>
@@ -16078,7 +16090,7 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>8.5 m in the master + 15% margin</t>
+          <t>8.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16107,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -16106,11 +16118,11 @@
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GREEN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -16121,17 +16133,17 @@
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>32.24</v>
+        <v>6.48</v>
       </c>
       <c r="M126" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-green-tefzel-wire-m22759-16-20-5-spool?variant=40415028838435</t>
+          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr"/>
@@ -16147,7 +16159,7 @@
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>1.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16176,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-7</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -16175,11 +16187,11 @@
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
@@ -16190,17 +16202,17 @@
         <v>0</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K127" s="3" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>6.48</v>
+        <v>24.36</v>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
+          <t>https://www.ksvlooms.com/products/20-awg-purple-tefzel-wire-m22759-16-20-7-spool?variant=40415029198883</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr"/>
@@ -16216,7 +16228,7 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>1.5 m in the master + 15% margin</t>
+          <t>5.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16233,7 +16245,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
+          <t>M22759/16-20-8</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -16244,7 +16256,7 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, GRAY, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
@@ -16262,14 +16274,14 @@
         <v>21</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>24.36</v>
+        <v>25.2</v>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-purple-tefzel-wire-m22759-16-20-7-spool?variant=40415029198883</t>
+          <t>https://www.ksvlooms.com/products/20-awg-gray-tefzel-wire-m22759-16-20-8-spool?variant=40415029264419</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr"/>
@@ -16285,7 +16297,7 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>5.5 m in the master + 15% margin</t>
+          <t>5.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16302,7 +16314,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -16313,11 +16325,11 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GRAY, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -16328,20 +16340,24 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="L129" s="3" t="n">
-        <v>25.2</v>
+        <v>31.68</v>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-gray-tefzel-wire-m22759-16-20-8-spool?variant=40415029264419</t>
-        </is>
-      </c>
-      <c r="N129" s="3" t="inlineStr"/>
+          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
+        </is>
+      </c>
+      <c r="N129" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
+        </is>
+      </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
           <t>KSV Looms, 2026-10-20</t>
@@ -16354,7 +16370,7 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>5.3 m in the master + 15% margin</t>
+          <t>8.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16387,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-6-9</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -16382,11 +16398,11 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 6 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -16397,24 +16413,20 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.96</v>
+        <v>8.09</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>31.68</v>
+        <v>64.72</v>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
-        </is>
-      </c>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
-        </is>
-      </c>
+          <t>https://www.ksvlooms.com/products/6-awg-white-tefzel-wire-m22759-16-6-9-spool?variant=40415058198563</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr"/>
       <c r="O130" s="2" t="inlineStr">
         <is>
           <t>KSV Looms, 2026-10-20</t>
@@ -16427,7 +16439,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>8.5 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16444,7 +16456,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -16455,11 +16467,11 @@
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 6 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -16470,17 +16482,17 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>8.09</v>
+        <v>6.08</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>64.72</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/6-awg-white-tefzel-wire-m22759-16-6-9-spool?variant=40415058198563</t>
+          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr"/>
@@ -16496,7 +16508,7 @@
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>3.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16513,7 +16525,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -16524,11 +16536,11 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -16539,17 +16551,17 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>6.08</v>
+        <v>6.1</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>79.04000000000001</v>
+        <v>183</v>
       </c>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
+          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr"/>
@@ -16565,7 +16577,7 @@
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>3.2 m in the master + 15% margin</t>
+          <t>7.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16582,7 +16594,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>M22759/16-8-9</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
@@ -16593,11 +16605,11 @@
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -16608,17 +16620,17 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>6.1</v>
+        <v>6.44</v>
       </c>
       <c r="L133" s="3" t="n">
-        <v>183</v>
+        <v>51.52</v>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
+          <t>https://www.ksvlooms.com/products/8-awg-white-tefzel-wire-m22759-16-8-9-spool?variant=40415055740963</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr"/>
@@ -16634,7 +16646,7 @@
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>7.8 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16651,61 +16663,57 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>6.44</v>
+        <v>13.46</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>51.52</v>
+        <v>26.92</v>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/8-awg-white-tefzel-wire-m22759-16-8-9-spool?variant=40415055740963</t>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr"/>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr">
-        <is>
-          <t>2.0 m in the master + 15% margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 65 in stock</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -16720,7 +16728,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -16731,7 +16739,7 @@
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
@@ -16756,7 +16764,7 @@
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr"/>
@@ -16767,7 +16775,7 @@
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 65 in stock</t>
+          <t>Digi-Key API 2026-10-20: 72 in stock</t>
         </is>
       </c>
       <c r="Q135" s="3" t="inlineStr"/>
@@ -16785,57 +16793,57 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>13.46</v>
+        <v>0</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="M136" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr"/>
       <c r="N136" s="2" t="inlineStr"/>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 72 in stock</t>
-        </is>
-      </c>
-      <c r="Q136" s="2" t="inlineStr"/>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>50 bands of 6 mm, both ends of each wire</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -16850,7 +16858,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -16861,7 +16869,7 @@
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
@@ -16898,7 +16906,7 @@
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>50 bands of 6 mm, both ends of each wire</t>
+          <t>60 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -16915,7 +16923,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -16926,7 +16934,7 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
@@ -16963,7 +16971,7 @@
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>60 bands of 6 mm, both ends of each wire</t>
+          <t>54 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -16980,7 +16988,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -16991,11 +16999,11 @@
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
@@ -17006,7 +17014,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K139" s="3" t="n">
         <v>0</v>
@@ -17028,7 +17036,7 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>54 bands of 6 mm, both ends of each wire</t>
+          <t>590 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17045,7 +17053,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -17056,11 +17064,11 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -17071,7 +17079,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -17093,7 +17101,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>590 bands of 6 mm, both ends of each wire</t>
+          <t>840 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17118,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
@@ -17121,11 +17129,11 @@
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
@@ -17136,7 +17144,7 @@
         <v>0</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K141" s="3" t="n">
         <v>0</v>
@@ -17158,7 +17166,7 @@
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>840 bands of 6 mm, both ends of each wire</t>
+          <t>408 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17175,18 +17183,14 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: contact / plug (ALT-PLUG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
@@ -17194,7 +17198,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
@@ -17203,27 +17207,19 @@
       <c r="J142" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K142" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr"/>
       <c r="M142" s="2" t="inlineStr"/>
       <c r="N142" s="2" t="inlineStr"/>
-      <c r="O142" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O142" s="2" t="inlineStr"/>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
         <is>
-          <t>408 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -17247,11 +17243,11 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ALT-PLUG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -17262,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
@@ -17300,11 +17296,11 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -17315,7 +17311,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
@@ -17353,11 +17349,11 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
@@ -17368,7 +17364,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K145" s="3" t="inlineStr"/>
       <c r="L145" s="3" t="inlineStr"/>
@@ -17406,7 +17402,7 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -17459,7 +17455,7 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
@@ -17512,7 +17508,7 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
@@ -17565,11 +17561,11 @@
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -17580,7 +17576,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
@@ -17618,11 +17614,11 @@
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -17633,7 +17629,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -17671,11 +17667,11 @@
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -17686,7 +17682,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -17724,11 +17720,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -17739,7 +17735,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
@@ -17777,11 +17773,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -17792,7 +17788,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -17830,11 +17826,11 @@
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -17845,7 +17841,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
@@ -17883,7 +17879,7 @@
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
@@ -17936,11 +17932,11 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -17951,7 +17947,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr"/>
@@ -17989,11 +17985,11 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -18004,7 +18000,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K157" s="3" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr"/>
@@ -18042,11 +18038,11 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -18057,7 +18053,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
@@ -18095,7 +18091,7 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
@@ -18148,7 +18144,7 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
@@ -18201,7 +18197,7 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
@@ -18254,7 +18250,7 @@
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -18307,7 +18303,7 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
@@ -18360,7 +18356,7 @@
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
@@ -18413,7 +18409,7 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
@@ -18466,7 +18462,7 @@
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
@@ -18519,7 +18515,7 @@
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
@@ -18572,7 +18568,7 @@
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -18625,7 +18621,7 @@
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
@@ -18678,7 +18674,7 @@
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -18731,11 +18727,11 @@
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -18746,7 +18742,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K171" s="3" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr"/>
@@ -18784,11 +18780,11 @@
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -18799,7 +18795,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
@@ -18837,11 +18833,11 @@
       <c r="E173" s="3" t="inlineStr"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -18852,7 +18848,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K173" s="3" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr"/>
@@ -18890,11 +18886,11 @@
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -18905,7 +18901,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
@@ -18943,7 +18939,7 @@
       <c r="E175" s="3" t="inlineStr"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
@@ -18996,7 +18992,7 @@
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
@@ -19049,7 +19045,7 @@
       <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
@@ -19102,11 +19098,11 @@
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -19117,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
@@ -19155,7 +19151,7 @@
       <c r="E179" s="3" t="inlineStr"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
@@ -19208,11 +19204,11 @@
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -19223,7 +19219,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
@@ -19261,7 +19257,7 @@
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
@@ -19314,7 +19310,7 @@
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
@@ -19367,7 +19363,7 @@
       <c r="E183" s="3" t="inlineStr"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -19420,7 +19416,7 @@
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G184" s="2" t="n">
@@ -19473,7 +19469,7 @@
       <c r="E185" s="3" t="inlineStr"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G185" s="3" t="n">
@@ -19526,7 +19522,7 @@
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G186" s="2" t="n">
@@ -19579,7 +19575,7 @@
       <c r="E187" s="3" t="inlineStr"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G187" s="3" t="n">
@@ -19632,7 +19628,7 @@
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G188" s="2" t="n">
@@ -19685,7 +19681,7 @@
       <c r="E189" s="3" t="inlineStr"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G189" s="3" t="n">
@@ -19738,7 +19734,7 @@
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G190" s="2" t="n">
@@ -19791,7 +19787,7 @@
       <c r="E191" s="3" t="inlineStr"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G191" s="3" t="n">
@@ -19844,22 +19840,22 @@
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
+          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
@@ -19873,7 +19869,7 @@
       </c>
       <c r="Q192" s="2" t="inlineStr">
         <is>
-          <t>no maker document in the repo yet; never guessed</t>
+          <t>OPEN-ITEMS row 140</t>
         </is>
       </c>
     </row>
@@ -19890,45 +19886,53 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr"/>
+          <t>TMS-SCE-1/2-2.0-9</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G193" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I193" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K193" s="3" t="inlineStr"/>
-      <c r="L193" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M193" s="3" t="inlineStr"/>
       <c r="N193" s="3" t="inlineStr"/>
-      <c r="O193" s="3" t="inlineStr"/>
+      <c r="O193" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P193" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q193" s="3" t="inlineStr">
-        <is>
-          <t>OPEN-ITEMS row 140</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -19943,7 +19947,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -19954,11 +19958,11 @@
       <c r="E194" s="2" t="inlineStr"/>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -19969,7 +19973,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -20004,7 +20008,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -20015,11 +20019,11 @@
       <c r="E195" s="3" t="inlineStr"/>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G195" s="3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
@@ -20030,7 +20034,7 @@
         <v>0</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K195" s="3" t="n">
         <v>0</v>
@@ -20065,22 +20069,22 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Deutsch (TE Connectivity)</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr"/>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -20088,27 +20092,31 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M196" s="2" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="M196" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+        </is>
+      </c>
       <c r="N196" s="2" t="inlineStr"/>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>not priced (Dan)</t>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr"/>
@@ -20126,22 +20134,26 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>W12S</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Deutsch (TE Connectivity)</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G197" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
@@ -20149,31 +20161,31 @@
         </is>
       </c>
       <c r="I197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J197" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="K197" s="3" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="L197" s="3" t="n">
-        <v>1.26</v>
+        <v>0.26</v>
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr"/>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P197" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="3" t="inlineStr"/>
@@ -20191,7 +20203,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>W2P</t>
+          <t>W2S</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -20206,11 +20218,11 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -20221,28 +20233,28 @@
         <v>0</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K198" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>0.26</v>
+        <v>1.43</v>
       </c>
       <c r="M198" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+          <t>https://www.te.com/en/product-W2S.html</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr"/>
@@ -20260,12 +20272,12 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -20275,11 +20287,11 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G199" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
@@ -20290,17 +20302,17 @@
         <v>0</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K199" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="L199" s="3" t="n">
-        <v>1.43</v>
+        <v>0.26</v>
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr"/>
@@ -20311,7 +20323,7 @@
       </c>
       <c r="P199" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q199" s="3" t="inlineStr"/>
@@ -20329,12 +20341,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -20344,7 +20356,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G200" s="2" t="n">
@@ -20362,25 +20374,25 @@
         <v>2</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="L200" s="2" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="M200" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr"/>
@@ -20398,7 +20410,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
@@ -20413,7 +20425,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G201" s="3" t="n">
@@ -20431,14 +20443,14 @@
         <v>2</v>
       </c>
       <c r="K201" s="3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="L201" s="3" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr"/>
@@ -20449,7 +20461,7 @@
       </c>
       <c r="P201" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
         </is>
       </c>
       <c r="Q201" s="3" t="inlineStr"/>
@@ -20467,7 +20479,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -20482,11 +20494,11 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
@@ -20497,28 +20509,28 @@
         <v>0</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="L202" s="2" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="M202" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr"/>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr"/>
@@ -20536,7 +20548,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>WM-4S</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
@@ -20551,7 +20563,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="G203" s="3" t="n">
@@ -20569,14 +20581,14 @@
         <v>1</v>
       </c>
       <c r="K203" s="3" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="L203" s="3" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="M203" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
         </is>
       </c>
       <c r="N203" s="3" t="inlineStr"/>
@@ -20587,7 +20599,7 @@
       </c>
       <c r="P203" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
         </is>
       </c>
       <c r="Q203" s="3" t="inlineStr"/>
@@ -20605,12 +20617,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -20620,7 +20632,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="G204" s="2" t="n">
@@ -20638,14 +20650,14 @@
         <v>1</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="L204" s="2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="M204" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr"/>
@@ -20656,82 +20668,13 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr"/>
     </row>
-    <row r="205">
-      <c r="A205" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="D205" s="3" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E205" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I205" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K205" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L205" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M205" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
-        </is>
-      </c>
-      <c r="N205" s="3" t="inlineStr"/>
-      <c r="O205" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P205" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
-        </is>
-      </c>
-      <c r="Q205" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q205"/>
+  <autoFilter ref="A1:Q204"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -20786,66 +20729,66 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M118" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M136" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M205" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -20858,7 +20801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21535,7 +21478,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>DR-25-2-0-SP</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -21557,12 +21500,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -21579,7 +21522,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>M22759/16-14-60</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -21589,7 +21532,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21601,7 +21544,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-14-62</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -21623,7 +21566,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-14-63</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -21645,7 +21588,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-14-69</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -21667,7 +21610,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-16-20</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -21689,7 +21632,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-16-26</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -21711,7 +21654,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>M22759/16-16-50</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -21733,7 +21676,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>M22759/16-16-53</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -21755,7 +21698,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>M22759/16-16-59</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -21777,7 +21720,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>M22759/16-16-90</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -21799,7 +21742,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>M22759/16-18-29</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -21821,7 +21764,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>M22759/16-18-50</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -21843,7 +21786,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>M22759/16-18-54</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -21865,7 +21808,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>M22759/16-20-06</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -21887,7 +21830,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>M22759/16-20-09</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -21909,7 +21852,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>M22759/16-20-39</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -21931,7 +21874,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -21941,7 +21884,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -23045,30 +22988,8 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D100"/>
+  <autoFilter ref="A1:D99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$204</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$183</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4757.91</v>
+        <v>4774.69</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5169.45</v>
+        <v>5186.23</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23</v>
@@ -8127,7 +8127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q204"/>
+  <dimension ref="A1:Q183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -13895,11 +13895,11 @@
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
@@ -13910,17 +13910,17 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>2.72</v>
+        <v>3.5</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>21.76</v>
+        <v>140</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-brown-tefzel-wire-m22759-16-10-1-spool?variant=40423436288035</t>
+          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr"/>
@@ -13936,7 +13936,7 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>10.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -13964,11 +13964,11 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13979,33 +13979,21 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="M92" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>8.7 m in the master + 15% margin</t>
+          <t>0.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14244,7 +14232,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -14255,13 +14243,13 @@
         <v>0</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="M96" s="4" t="inlineStr">
         <is>
@@ -14281,7 +14269,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>21.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14286,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -14309,11 +14297,11 @@
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
@@ -14324,33 +14312,21 @@
         <v>0</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>87.36</v>
-      </c>
-      <c r="M97" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/14-awg-blue-tefzel-wire-m22759-16-14-6-spool?variant=40423417708579</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
       <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>7.3 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14367,7 +14343,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -14378,11 +14354,11 @@
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
@@ -14393,21 +14369,33 @@
         <v>0</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K98" s="2" t="inlineStr"/>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
+        <v>22</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>5.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14412,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -14435,11 +14423,11 @@
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
@@ -14450,21 +14438,33 @@
         <v>0</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K99" s="3" t="inlineStr"/>
-      <c r="L99" s="3" t="inlineStr"/>
-      <c r="M99" s="3" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-16</t>
+        </is>
+      </c>
       <c r="N99" s="3" t="inlineStr"/>
-      <c r="O99" s="3" t="inlineStr"/>
+      <c r="O99" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>2.8 m in the master + 15% margin</t>
+          <t>19.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -14492,11 +14492,11 @@
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
@@ -14521,7 +14521,7 @@
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>3.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -14549,11 +14549,11 @@
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
@@ -14564,21 +14564,33 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr"/>
-      <c r="M101" s="3" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-18</t>
+        </is>
+      </c>
       <c r="N101" s="3" t="inlineStr"/>
-      <c r="O101" s="3" t="inlineStr"/>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>21.6 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14607,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -14606,11 +14618,11 @@
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14621,33 +14633,21 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="M102" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>3.5 m in the master + 15% margin</t>
+          <t>3.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -14675,11 +14675,11 @@
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
@@ -14690,33 +14690,33 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>32</v>
+        <v>44.8</v>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-16</t>
+          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr"/>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>8.4 m in the master + 15% margin</t>
+          <t>7.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -14744,11 +14744,11 @@
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -14759,21 +14759,33 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>5.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14802,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -14801,11 +14813,11 @@
       <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -14816,21 +14828,33 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K105" s="3" t="inlineStr"/>
-      <c r="L105" s="3" t="inlineStr"/>
-      <c r="M105" s="3" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L105" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-20</t>
+        </is>
+      </c>
       <c r="N105" s="3" t="inlineStr"/>
-      <c r="O105" s="3" t="inlineStr"/>
+      <c r="O105" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P105" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>2.4 m in the master + 15% margin</t>
+          <t>5.9 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14871,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -14858,11 +14882,11 @@
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -14873,21 +14897,33 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K106" s="2" t="inlineStr"/>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>35.36</v>
+      </c>
+      <c r="M106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>4.2 m in the master + 15% margin</t>
+          <t>8.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14940,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -14915,11 +14951,11 @@
       <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -14930,21 +14966,33 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K107" s="3" t="inlineStr"/>
-      <c r="L107" s="3" t="inlineStr"/>
-      <c r="M107" s="3" t="inlineStr"/>
+        <v>26</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>29.12</v>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
+        </is>
+      </c>
       <c r="N107" s="3" t="inlineStr"/>
-      <c r="O107" s="3" t="inlineStr"/>
+      <c r="O107" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P107" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>4.1 m in the master + 15% margin</t>
+          <t>6.9 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14961,7 +15009,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -14972,11 +15020,11 @@
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -14987,21 +15035,33 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>6.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15078,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -15029,11 +15089,11 @@
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, WHITE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -15044,21 +15104,37 @@
         <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr"/>
-      <c r="M109" s="3" t="inlineStr"/>
-      <c r="N109" s="3" t="inlineStr"/>
-      <c r="O109" s="3" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>128.64</v>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
+        </is>
+      </c>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P109" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>2.3 m in the master + 15% margin</t>
+          <t>35.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15151,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -15086,11 +15162,11 @@
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 6 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -15101,33 +15177,21 @@
         <v>0</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K110" s="2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="M110" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/18-awg-black-tefzel-wire-m22759-16-18-0-spool?variant=40415044370467</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>0.4 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15144,7 +15208,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -15155,11 +15219,11 @@
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -15170,33 +15234,33 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>1</v>
+        <v>6.08</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>22</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-18</t>
+          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr"/>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>5.7 m in the master + 15% margin</t>
+          <t>3.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15277,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -15224,11 +15288,11 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -15239,21 +15303,33 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K112" s="2" t="inlineStr"/>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>231.8</v>
+      </c>
+      <c r="M112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
+        </is>
+      </c>
       <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>0.4 m in the master + 15% margin</t>
+          <t>9.9 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15270,49 +15346,57 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="K113" s="3" t="inlineStr"/>
-      <c r="L113" s="3" t="inlineStr"/>
-      <c r="M113" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="L113" s="3" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
+        </is>
+      </c>
       <c r="N113" s="3" t="inlineStr"/>
-      <c r="O113" s="3" t="inlineStr"/>
+      <c r="O113" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P113" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q113" s="3" t="inlineStr">
-        <is>
-          <t>7.2 m in the master + 15% margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 65 in stock</t>
+        </is>
+      </c>
+      <c r="Q113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -15327,49 +15411,57 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>26.92</v>
+      </c>
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
+        </is>
+      </c>
       <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>8.3 m in the master + 15% margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 72 in stock</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -15384,59 +15476,55 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>38.08</v>
-      </c>
-      <c r="M115" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/18-awg-purple-tefzel-wire-m22759-16-18-7-spool?variant=40423402700835</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr"/>
       <c r="N115" s="3" t="inlineStr"/>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>7.4 m in the master + 15% margin</t>
+          <t>50 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -15453,59 +15541,55 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M116" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
       <c r="N116" s="2" t="inlineStr"/>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>2.6 m in the master + 15% margin</t>
+          <t>60 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -15522,59 +15606,55 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I117" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="L117" s="3" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="M117" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr"/>
       <c r="N117" s="3" t="inlineStr"/>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>5.4 m in the master + 15% margin</t>
+          <t>54 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -15591,47 +15671,55 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K118" s="2" t="inlineStr"/>
-      <c r="L118" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M118" s="2" t="inlineStr"/>
       <c r="N118" s="2" t="inlineStr"/>
-      <c r="O118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>0.6 m in the master + 15% margin</t>
+          <t>590 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -15648,47 +15736,55 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I119" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="inlineStr"/>
-      <c r="O119" s="3" t="inlineStr"/>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>6.4 m in the master + 15% margin</t>
+          <t>840 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -15705,59 +15801,55 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>23.52</v>
-      </c>
-      <c r="M120" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-brown-tefzel-wire-m22759-16-20-1-spool?variant=40415026708515</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr"/>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>6.3 m in the master + 15% margin</t>
+          <t>408 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -15774,59 +15866,43 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (ALT-PLUG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="M121" s="5" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-20</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K121" s="3" t="inlineStr"/>
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="inlineStr"/>
-      <c r="O121" s="3" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>3.5 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -15843,59 +15919,43 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="M122" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -15912,33 +15972,29 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr"/>
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
       <c r="L123" s="3" t="inlineStr"/>
@@ -15952,7 +16008,7 @@
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>1.1 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -15969,59 +16025,43 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>36.96</v>
-      </c>
-      <c r="M124" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
       <c r="N124" s="2" t="inlineStr"/>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O124" s="2" t="inlineStr"/>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>8.5 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16038,59 +16078,43 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GREEN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="K125" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L125" s="3" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="M125" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-green-tefzel-wire-m22759-16-20-5-spool?variant=40415028838435</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K125" s="3" t="inlineStr"/>
+      <c r="L125" s="3" t="inlineStr"/>
+      <c r="M125" s="3" t="inlineStr"/>
       <c r="N125" s="3" t="inlineStr"/>
-      <c r="O125" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16107,59 +16131,43 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="M126" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
       <c r="N126" s="2" t="inlineStr"/>
-      <c r="O126" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O126" s="2" t="inlineStr"/>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>1.5 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16176,59 +16184,43 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I127" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K127" s="3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="L127" s="3" t="n">
-        <v>24.36</v>
-      </c>
-      <c r="M127" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-purple-tefzel-wire-m22759-16-20-7-spool?variant=40415029198883</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
+      <c r="L127" s="3" t="inlineStr"/>
+      <c r="M127" s="3" t="inlineStr"/>
       <c r="N127" s="3" t="inlineStr"/>
-      <c r="O127" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O127" s="3" t="inlineStr"/>
       <c r="P127" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>5.5 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16245,59 +16237,43 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GRAY, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="K128" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="M128" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-gray-tefzel-wire-m22759-16-20-8-spool?variant=40415029264419</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
       <c r="N128" s="2" t="inlineStr"/>
-      <c r="O128" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>5.3 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16314,63 +16290,43 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr"/>
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I129" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="K129" s="3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L129" s="3" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="M129" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
-        </is>
-      </c>
-      <c r="N129" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
-        </is>
-      </c>
-      <c r="O129" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K129" s="3" t="inlineStr"/>
+      <c r="L129" s="3" t="inlineStr"/>
+      <c r="M129" s="3" t="inlineStr"/>
+      <c r="N129" s="3" t="inlineStr"/>
+      <c r="O129" s="3" t="inlineStr"/>
       <c r="P129" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>8.5 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16387,59 +16343,43 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 6 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K130" s="2" t="n">
-        <v>8.09</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>64.72</v>
-      </c>
-      <c r="M130" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/6-awg-white-tefzel-wire-m22759-16-6-9-spool?variant=40415058198563</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
       <c r="N130" s="2" t="inlineStr"/>
-      <c r="O130" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16456,59 +16396,43 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr"/>
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I131" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K131" s="3" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="L131" s="3" t="n">
-        <v>79.04000000000001</v>
-      </c>
-      <c r="M131" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
+      <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="3" t="inlineStr"/>
-      <c r="O131" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O131" s="3" t="inlineStr"/>
       <c r="P131" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>3.2 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16525,59 +16449,43 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>183</v>
-      </c>
-      <c r="M132" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
       <c r="N132" s="2" t="inlineStr"/>
-      <c r="O132" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O132" s="2" t="inlineStr"/>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>7.8 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16594,59 +16502,43 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>M22759</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="K133" s="3" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="L133" s="3" t="n">
-        <v>51.52</v>
-      </c>
-      <c r="M133" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/8-awg-white-tefzel-wire-m22759-16-8-9-spool?variant=40415055740963</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K133" s="3" t="inlineStr"/>
+      <c r="L133" s="3" t="inlineStr"/>
+      <c r="M133" s="3" t="inlineStr"/>
       <c r="N133" s="3" t="inlineStr"/>
-      <c r="O133" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O133" s="3" t="inlineStr"/>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16663,18 +16555,14 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Amphenol</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
+          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
@@ -16691,29 +16579,21 @@
       <c r="J134" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K134" s="2" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="M134" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
-        </is>
-      </c>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
       <c r="N134" s="2" t="inlineStr"/>
-      <c r="O134" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 65 in stock</t>
-        </is>
-      </c>
-      <c r="Q134" s="2" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>no maker document in the repo yet; never guessed</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -16728,22 +16608,18 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Amphenol</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
+          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -16754,31 +16630,23 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K135" s="3" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="L135" s="3" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="M135" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K135" s="3" t="inlineStr"/>
+      <c r="L135" s="3" t="inlineStr"/>
+      <c r="M135" s="3" t="inlineStr"/>
       <c r="N135" s="3" t="inlineStr"/>
-      <c r="O135" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O135" s="3" t="inlineStr"/>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 72 in stock</t>
-        </is>
-      </c>
-      <c r="Q135" s="3" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q135" s="3" t="inlineStr">
+        <is>
+          <t>no maker document in the repo yet; never guessed</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -16793,55 +16661,43 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
       <c r="M136" s="2" t="inlineStr"/>
       <c r="N136" s="2" t="inlineStr"/>
-      <c r="O136" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O136" s="2" t="inlineStr"/>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>50 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16858,18 +16714,14 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
@@ -16877,7 +16729,7 @@
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I137" s="3" t="n">
@@ -16886,27 +16738,19 @@
       <c r="J137" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr"/>
       <c r="M137" s="3" t="inlineStr"/>
       <c r="N137" s="3" t="inlineStr"/>
-      <c r="O137" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>60 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16923,18 +16767,14 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
@@ -16942,7 +16782,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
@@ -16951,27 +16791,19 @@
       <c r="J138" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
       <c r="M138" s="2" t="inlineStr"/>
       <c r="N138" s="2" t="inlineStr"/>
-      <c r="O138" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O138" s="2" t="inlineStr"/>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>54 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -16988,55 +16820,43 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I139" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K139" s="3" t="inlineStr"/>
+      <c r="L139" s="3" t="inlineStr"/>
       <c r="M139" s="3" t="inlineStr"/>
       <c r="N139" s="3" t="inlineStr"/>
-      <c r="O139" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O139" s="3" t="inlineStr"/>
       <c r="P139" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>590 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -17053,55 +16873,43 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr"/>
       <c r="M140" s="2" t="inlineStr"/>
       <c r="N140" s="2" t="inlineStr"/>
-      <c r="O140" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O140" s="2" t="inlineStr"/>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>840 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -17118,55 +16926,43 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I141" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J141" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr"/>
       <c r="M141" s="3" t="inlineStr"/>
       <c r="N141" s="3" t="inlineStr"/>
-      <c r="O141" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O141" s="3" t="inlineStr"/>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>408 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -17190,11 +16986,11 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ALT-PLUG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -17205,7 +17001,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
@@ -17243,11 +17039,11 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -17258,7 +17054,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
@@ -17296,11 +17092,11 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -17311,7 +17107,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
@@ -17349,7 +17145,7 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
@@ -17402,7 +17198,7 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -17455,7 +17251,7 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
@@ -17508,7 +17304,7 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
@@ -17561,11 +17357,11 @@
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17372,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
@@ -17614,11 +17410,11 @@
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -17629,7 +17425,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -17667,11 +17463,11 @@
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -17682,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -17720,11 +17516,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -17735,7 +17531,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
@@ -17773,11 +17569,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -17788,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -17826,11 +17622,11 @@
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -17841,7 +17637,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
@@ -17879,11 +17675,11 @@
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
@@ -17894,7 +17690,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K155" s="3" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr"/>
@@ -17932,11 +17728,11 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -17947,7 +17743,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr"/>
@@ -17985,7 +17781,7 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
@@ -18038,11 +17834,11 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -18053,7 +17849,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
@@ -18091,7 +17887,7 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
@@ -18144,7 +17940,7 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
@@ -18197,7 +17993,7 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
@@ -18250,7 +18046,7 @@
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -18303,7 +18099,7 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
@@ -18356,7 +18152,7 @@
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
@@ -18409,7 +18205,7 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
@@ -18462,7 +18258,7 @@
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
@@ -18515,7 +18311,7 @@
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
@@ -18568,7 +18364,7 @@
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -18621,7 +18417,7 @@
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
@@ -18674,7 +18470,7 @@
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -18727,22 +18523,22 @@
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
+          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I171" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K171" s="3" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr"/>
@@ -18756,7 +18552,7 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>no maker document in the repo yet; never guessed</t>
+          <t>OPEN-ITEMS row 140</t>
         </is>
       </c>
     </row>
@@ -18773,18 +18569,22 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr"/>
+          <t>TMS-SCE-1/2-2.0-9</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -18795,23 +18595,27 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K172" s="2" t="inlineStr"/>
-      <c r="L172" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M172" s="2" t="inlineStr"/>
       <c r="N172" s="2" t="inlineStr"/>
-      <c r="O172" s="2" t="inlineStr"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q172" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -18826,18 +18630,22 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr"/>
+          <t>TMS-SCE-3/16-2.0-9</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E173" s="3" t="inlineStr"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -18848,23 +18656,27 @@
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K173" s="3" t="inlineStr"/>
-      <c r="L173" s="3" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M173" s="3" t="inlineStr"/>
       <c r="N173" s="3" t="inlineStr"/>
-      <c r="O173" s="3" t="inlineStr"/>
+      <c r="O173" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P173" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q173" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -18879,18 +18691,22 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr"/>
+          <t>TMS-SCE-3/8-2.0-9</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -18901,23 +18717,27 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K174" s="2" t="inlineStr"/>
-      <c r="L174" s="2" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M174" s="2" t="inlineStr"/>
       <c r="N174" s="2" t="inlineStr"/>
-      <c r="O174" s="2" t="inlineStr"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q174" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -18932,18 +18752,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr"/>
+          <t>W12S</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Deutsch (TE Connectivity)</t>
+        </is>
+      </c>
       <c r="E175" s="3" t="inlineStr"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -18951,26 +18775,34 @@
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K175" s="3" t="inlineStr"/>
-      <c r="L175" s="3" t="inlineStr"/>
-      <c r="M175" s="3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="K175" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L175" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M175" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+        </is>
+      </c>
       <c r="N175" s="3" t="inlineStr"/>
-      <c r="O175" s="3" t="inlineStr"/>
+      <c r="O175" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P175" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q175" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
+        </is>
+      </c>
+      <c r="Q175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -18985,18 +18817,26 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr"/>
-      <c r="E176" s="2" t="inlineStr"/>
+          <t>W2P</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -19007,23 +18847,31 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K176" s="2" t="inlineStr"/>
-      <c r="L176" s="2" t="inlineStr"/>
-      <c r="M176" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+        </is>
+      </c>
       <c r="N176" s="2" t="inlineStr"/>
-      <c r="O176" s="2" t="inlineStr"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1, 2026-10-19</t>
+        </is>
+      </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q176" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>Digi-Key product page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -19038,18 +18886,26 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr"/>
-      <c r="E177" s="3" t="inlineStr"/>
+          <t>W2S</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -19060,23 +18916,31 @@
         <v>0</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K177" s="3" t="inlineStr"/>
-      <c r="L177" s="3" t="inlineStr"/>
-      <c r="M177" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="K177" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L177" s="3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M177" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W2S.html</t>
+        </is>
+      </c>
       <c r="N177" s="3" t="inlineStr"/>
-      <c r="O177" s="3" t="inlineStr"/>
+      <c r="O177" s="3" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="P177" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q177" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>te.com page opened 2026-10-19</t>
+        </is>
+      </c>
+      <c r="Q177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -19091,14 +18955,22 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr"/>
-      <c r="E178" s="2" t="inlineStr"/>
+          <t>W3S</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
@@ -19115,21 +18987,29 @@
       <c r="J178" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
-      <c r="L178" s="2" t="inlineStr"/>
-      <c r="M178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W3S.html</t>
+        </is>
+      </c>
       <c r="N178" s="2" t="inlineStr"/>
-      <c r="O178" s="2" t="inlineStr"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+        </is>
+      </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q178" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -19144,14 +19024,22 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr"/>
-      <c r="E179" s="3" t="inlineStr"/>
+          <t>W6P</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
@@ -19168,21 +19056,29 @@
       <c r="J179" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K179" s="3" t="inlineStr"/>
-      <c r="L179" s="3" t="inlineStr"/>
-      <c r="M179" s="3" t="inlineStr"/>
+      <c r="K179" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L179" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M179" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
+        </is>
+      </c>
       <c r="N179" s="3" t="inlineStr"/>
-      <c r="O179" s="3" t="inlineStr"/>
+      <c r="O179" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P179" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q179" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
+        </is>
+      </c>
+      <c r="Q179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -19197,18 +19093,26 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="2" t="inlineStr"/>
+          <t>W6S</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
@@ -19219,23 +19123,31 @@
         <v>0</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K180" s="2" t="inlineStr"/>
-      <c r="L180" s="2" t="inlineStr"/>
-      <c r="M180" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
+        </is>
+      </c>
       <c r="N180" s="2" t="inlineStr"/>
-      <c r="O180" s="2" t="inlineStr"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q180" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -19250,14 +19162,22 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr"/>
-      <c r="E181" s="3" t="inlineStr"/>
+          <t>W8S</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
@@ -19274,21 +19194,29 @@
       <c r="J181" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K181" s="3" t="inlineStr"/>
-      <c r="L181" s="3" t="inlineStr"/>
-      <c r="M181" s="3" t="inlineStr"/>
+      <c r="K181" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L181" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M181" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
+        </is>
+      </c>
       <c r="N181" s="3" t="inlineStr"/>
-      <c r="O181" s="3" t="inlineStr"/>
+      <c r="O181" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P181" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q181" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+        </is>
+      </c>
+      <c r="Q181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -19303,14 +19231,22 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="2" t="inlineStr"/>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
@@ -19327,21 +19263,29 @@
       <c r="J182" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
-      <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+        </is>
+      </c>
       <c r="N182" s="2" t="inlineStr"/>
-      <c r="O182" s="2" t="inlineStr"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q182" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -19356,14 +19300,22 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr"/>
-      <c r="E183" s="3" t="inlineStr"/>
+          <t>WM-6S</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -19380,1301 +19332,32 @@
       <c r="J183" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K183" s="3" t="inlineStr"/>
-      <c r="L183" s="3" t="inlineStr"/>
-      <c r="M183" s="3" t="inlineStr"/>
+      <c r="K183" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L183" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M183" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
+        </is>
+      </c>
       <c r="N183" s="3" t="inlineStr"/>
-      <c r="O183" s="3" t="inlineStr"/>
+      <c r="O183" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P183" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q183" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr"/>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H184" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K184" s="2" t="inlineStr"/>
-      <c r="L184" s="2" t="inlineStr"/>
-      <c r="M184" s="2" t="inlineStr"/>
-      <c r="N184" s="2" t="inlineStr"/>
-      <c r="O184" s="2" t="inlineStr"/>
-      <c r="P184" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q184" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr"/>
-      <c r="E185" s="3" t="inlineStr"/>
-      <c r="F185" s="3" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H185" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K185" s="3" t="inlineStr"/>
-      <c r="L185" s="3" t="inlineStr"/>
-      <c r="M185" s="3" t="inlineStr"/>
-      <c r="N185" s="3" t="inlineStr"/>
-      <c r="O185" s="3" t="inlineStr"/>
-      <c r="P185" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q185" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr"/>
-      <c r="E186" s="2" t="inlineStr"/>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G186" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H186" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K186" s="2" t="inlineStr"/>
-      <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="inlineStr"/>
-      <c r="N186" s="2" t="inlineStr"/>
-      <c r="O186" s="2" t="inlineStr"/>
-      <c r="P186" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q186" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr"/>
-      <c r="E187" s="3" t="inlineStr"/>
-      <c r="F187" s="3" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G187" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H187" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I187" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K187" s="3" t="inlineStr"/>
-      <c r="L187" s="3" t="inlineStr"/>
-      <c r="M187" s="3" t="inlineStr"/>
-      <c r="N187" s="3" t="inlineStr"/>
-      <c r="O187" s="3" t="inlineStr"/>
-      <c r="P187" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q187" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr"/>
-      <c r="E188" s="2" t="inlineStr"/>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K188" s="2" t="inlineStr"/>
-      <c r="L188" s="2" t="inlineStr"/>
-      <c r="M188" s="2" t="inlineStr"/>
-      <c r="N188" s="2" t="inlineStr"/>
-      <c r="O188" s="2" t="inlineStr"/>
-      <c r="P188" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q188" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr"/>
-      <c r="E189" s="3" t="inlineStr"/>
-      <c r="F189" s="3" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G189" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H189" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I189" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K189" s="3" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr"/>
-      <c r="M189" s="3" t="inlineStr"/>
-      <c r="N189" s="3" t="inlineStr"/>
-      <c r="O189" s="3" t="inlineStr"/>
-      <c r="P189" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q189" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B190" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr"/>
-      <c r="E190" s="2" t="inlineStr"/>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G190" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="inlineStr"/>
-      <c r="M190" s="2" t="inlineStr"/>
-      <c r="N190" s="2" t="inlineStr"/>
-      <c r="O190" s="2" t="inlineStr"/>
-      <c r="P190" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q190" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr"/>
-      <c r="E191" s="3" t="inlineStr"/>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
-        </is>
-      </c>
-      <c r="G191" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H191" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I191" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K191" s="3" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr"/>
-      <c r="M191" s="3" t="inlineStr"/>
-      <c r="N191" s="3" t="inlineStr"/>
-      <c r="O191" s="3" t="inlineStr"/>
-      <c r="P191" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q191" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr"/>
-      <c r="E192" s="2" t="inlineStr"/>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>ft</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="2" t="inlineStr"/>
-      <c r="N192" s="2" t="inlineStr"/>
-      <c r="O192" s="2" t="inlineStr"/>
-      <c r="P192" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q192" s="2" t="inlineStr">
-        <is>
-          <t>OPEN-ITEMS row 140</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr"/>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H193" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" s="3" t="inlineStr"/>
-      <c r="N193" s="3" t="inlineStr"/>
-      <c r="O193" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
-      <c r="P193" s="3" t="inlineStr">
-        <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q193" s="3" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr"/>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
-        </is>
-      </c>
-      <c r="G194" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="H194" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="K194" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" s="2" t="inlineStr"/>
-      <c r="N194" s="2" t="inlineStr"/>
-      <c r="O194" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
-      <c r="P194" s="2" t="inlineStr">
-        <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q194" s="2" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr"/>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H195" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="K195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" s="3" t="inlineStr"/>
-      <c r="N195" s="3" t="inlineStr"/>
-      <c r="O195" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
-      <c r="P195" s="3" t="inlineStr">
-        <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q195" s="3" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>W12S</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>Deutsch (TE Connectivity)</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr"/>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G196" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H196" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J196" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K196" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L196" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M196" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
-      <c r="O196" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P196" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
-        </is>
-      </c>
-      <c r="Q196" s="2" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="inlineStr">
-        <is>
-          <t>W2P</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H197" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I197" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K197" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L197" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M197" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
-        </is>
-      </c>
-      <c r="N197" s="3" t="inlineStr"/>
-      <c r="O197" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
-        </is>
-      </c>
-      <c r="P197" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q197" s="3" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>W2S</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
-        </is>
-      </c>
-      <c r="G198" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H198" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K198" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L198" s="2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M198" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
-      <c r="O198" s="2" t="inlineStr">
-        <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
-      <c r="P198" s="2" t="inlineStr">
-        <is>
-          <t>te.com page opened 2026-10-19</t>
-        </is>
-      </c>
-      <c r="Q198" s="2" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="inlineStr">
-        <is>
-          <t>W3S</t>
-        </is>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I199" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K199" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="L199" s="3" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M199" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
-        </is>
-      </c>
-      <c r="N199" s="3" t="inlineStr"/>
-      <c r="O199" s="3" t="inlineStr">
-        <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
-        </is>
-      </c>
-      <c r="P199" s="3" t="inlineStr">
-        <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="Q199" s="3" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>W6P</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K200" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L200" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M200" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
-      <c r="O200" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P200" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
-        </is>
-      </c>
-      <c r="Q200" s="2" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>W6S</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I201" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K201" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="L201" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M201" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
-        </is>
-      </c>
-      <c r="N201" s="3" t="inlineStr"/>
-      <c r="O201" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P201" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
-        </is>
-      </c>
-      <c r="Q201" s="3" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>W8S</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K202" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L202" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M202" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
-        </is>
-      </c>
-      <c r="N202" s="2" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P202" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
-        </is>
-      </c>
-      <c r="Q202" s="2" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>WM-4S</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K203" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L203" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M203" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
-        </is>
-      </c>
-      <c r="N203" s="3" t="inlineStr"/>
-      <c r="O203" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P203" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
-        </is>
-      </c>
-      <c r="Q203" s="3" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K204" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L204" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M204" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
-        </is>
-      </c>
-      <c r="N204" s="2" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P204" s="2" t="inlineStr">
-        <is>
           <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
-      <c r="Q204" s="2" t="inlineStr"/>
+      <c r="Q183" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q204"/>
+  <autoFilter ref="A1:Q183"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -20751,44 +19434,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -20801,7 +19474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21522,7 +20195,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -21544,7 +20217,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -21566,7 +20239,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -21588,7 +20261,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -21610,7 +20283,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -21632,7 +20305,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -21642,7 +20315,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21654,7 +20327,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -21664,7 +20337,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21676,7 +20349,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -21686,7 +20359,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21698,7 +20371,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -21708,7 +20381,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21720,7 +20393,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -21730,7 +20403,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21742,7 +20415,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -21752,7 +20425,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21764,7 +20437,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -21774,7 +20447,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21786,7 +20459,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -21796,7 +20469,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21808,7 +20481,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -21818,7 +20491,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21830,7 +20503,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -21840,7 +20513,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -21852,7 +20525,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -21862,7 +20535,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -22746,250 +21419,8 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D99"/>
+  <autoFilter ref="A1:D88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="To do" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To do" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$204</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4757.91</v>
+        <v>4787.24</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5169.45</v>
+        <v>5198.78</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23</v>
@@ -8127,7 +8127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q204"/>
+  <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -8279,13 +8279,13 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -8543,13 +8543,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.41</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>25.01</v>
+        <v>23.78</v>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -8675,13 +8675,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0.89</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>16.91</v>
+        <v>18.69</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
@@ -8958,22 +8958,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10k 1/4W</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 10 KOHM, 5 PCT, 1/4 W</t>
+          <t>PLUG, SEALING, CAVITY, SIZE 16, WHITE</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -8984,28 +8984,28 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.1</v>
+        <v>13.42</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT10K0/1741265</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114017-ZZ/6566679</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT10K0</t>
+          <t>Digi-Key qty 58 (Box), 2026-10-20; listed as 114017-ZZ</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 568040 in stock</t>
+          <t>Digi-Key API 2026-10-20: 267877 in stock</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9034,11 +9034,11 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PLUG, SEALING, CAVITY, SIZE 16, WHITE</t>
+          <t>PLUG, SEALING, CAVITY, SIZE 8, WHITE</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -9046,31 +9046,29 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>12.76</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114017-ZZ/6566679</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114018-ZZ/9923101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 58 (Box), 2026-10-20; listed as 114017-ZZ</t>
+          <t>Digi-Key qty 8 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 267877 in stock</t>
+          <t>Digi-Key API 2026-10-20: 6856 in stock</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -9088,7 +9086,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -9099,11 +9097,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>PLUG, SEALING, CAVITY, SIZE 8, WHITE</t>
+          <t>PLUG, SEALING, CAVITY, SIZE 4, WHITE</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -9111,29 +9109,29 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.75</v>
+        <v>1.82</v>
       </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114018-ZZ/9923101</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114019-ZZ/6566680</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 8 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 4 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 6856 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2935 in stock</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -9151,22 +9149,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>12052641</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Aptiv (Delphi) Metri-Pack 150</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>PLUG, SEALING, CAVITY, SIZE 4, WHITE</t>
+          <t>CONNECTOR, 2 POS, SEALED</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -9174,29 +9172,31 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+        <v>0.89</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0.89</v>
+      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114019-ZZ/6566680</t>
+          <t>https://www.customconnectorkits.com/products/12052641?variant=45536631554366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 4 (Box), 2026-10-20</t>
+          <t>Custom Connector Kits, 2026-10-20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2935 in stock</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -9214,22 +9214,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>12052641</t>
+          <t>12084200</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Aptiv (Delphi) Metri-Pack 150</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, 2 POS, SEALED</t>
+          <t>CONTACT, SOCKET, CRIMP, METRI-PACK 150.2, TIN, CABLE-SEALED, 0.35-0.5 MM2 (22-20 AWG)</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -9240,20 +9240,24 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.89</v>
+        <v>0.16</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.89</v>
+        <v>2.24</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12052641?variant=45536631554366</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+          <t>https://www.customconnectorkits.com/products/12084200-l?variant=45536283525438</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ebay.de/itm/145990327082</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Custom Connector Kits, 2026-10-20</t>
@@ -9264,7 +9268,11 @@
           <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>confirm 150 vs 150.2 against Aptiv drawing</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9279,22 +9287,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>120R 1/4W</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, METRI-PACK 150.2, TIN, CABLE-SEALED, 0.35-0.5 MM2 (22-20 AWG)</t>
+          <t>RESISTOR, FIXED, METAL FILM, 120 OHM, 1 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -9305,39 +9313,31 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.24</v>
+        <v>0.2</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12084200-l?variant=45536283525438</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ebay.de/itm/145990327082</t>
-        </is>
-      </c>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RNMF14FTC120R/2617285</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>Digi-Key qty 2 (Cut Tape (CT)), 2026-10-20; listed as RNMF14FTC120R</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>confirm 150 vs 150.2 against Aptiv drawing</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 124869 in stock</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -9352,22 +9352,22 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>120R 1/4W</t>
+          <t>12110293</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 120 OHM, 1 PCT, 1/4 W</t>
+          <t>CONNECTOR, PLUG, METRI-PACK 150.2, 3 POS, SEALED, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -9378,28 +9378,28 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.1</v>
+        <v>0.95</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RNMF14FTC120R/2617285</t>
+          <t>https://www.customconnectorkits.com/products/12110293?variant=45536279953726</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Cut Tape (CT)), 2026-10-20; listed as RNMF14FTC120R</t>
+          <t>Custom Connector Kits, 2026-10-20</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 124869 in stock</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12110293</t>
+          <t>12191819</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, METRI-PACK 150.2, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -9446,14 +9446,14 @@
         <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.95</v>
+        <v>0.18</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.8</v>
+        <v>0.72</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12110293?variant=45536279953726</t>
+          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>13519047</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -9493,11 +9493,11 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -9508,17 +9508,17 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.18</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
+          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>13519047</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -9558,11 +9558,11 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -9573,17 +9573,17 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.95</v>
+        <v>3.15</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
+          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>15419715</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -9623,11 +9623,11 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -9638,17 +9638,17 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.15</v>
+        <v>4.36</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
+          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
@@ -9677,22 +9677,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>1N5822</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
+          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -9703,28 +9703,28 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4.36</v>
+        <v>0.71</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
+          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -9742,18 +9742,18 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1N5822</t>
+          <t>1k 1/4W</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
+          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
@@ -9771,25 +9771,25 @@
         <v>1</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
+          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -9807,22 +9807,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1k 1/4W</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -9830,31 +9830,29 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
+          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
+          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -9872,22 +9870,22 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 2.2 KOHM, 1 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -9895,19 +9893,29 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.28</v>
+      </c>
       <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+        </is>
+      </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -9925,22 +9933,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3.9k 1/4W 1%</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
+          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 1 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -9948,29 +9956,19 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="2" t="n">
-        <v>0.41</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -9988,22 +9986,22 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>301A011-25-0</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -10011,29 +10009,31 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
+        <v>27.58</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>82.73999999999999</v>
+      </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
+          <t>Digi-Key API 2026-10-20: 236 in stock</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -10051,22 +10051,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3.9k 1/4W</t>
+          <t>301A022-25-0</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 5 PCT, 1/4 W</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -10077,28 +10077,28 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.1</v>
+        <v>40.77</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.1</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
+          <t>Digi-Key API 2026-10-20: 151 in stock</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>301A011-25-0</t>
+          <t>301A028-25-0</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -10127,11 +10127,11 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -10142,28 +10142,28 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>27.58</v>
+        <v>37.65</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 236 in stock</t>
+          <t>Digi-Key API 2026-10-20: 94 in stock</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>301A022-25-0</t>
+          <t>342A012-25-0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -10192,11 +10192,11 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -10207,28 +10207,28 @@
         <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>40.77</v>
+        <v>35.59</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>81.54000000000001</v>
+        <v>427.08</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 151 in stock</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>301A028-25-0</t>
+          <t>342A024-25-0</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -10257,11 +10257,11 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -10272,28 +10272,28 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>37.65</v>
+        <v>50.66</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>75.3</v>
+        <v>557.26</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 94 in stock</t>
+          <t>Digi-Key API 2026-10-20: 140 in stock</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>342A012-25-0</t>
+          <t>342A034-25-0</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -10322,11 +10322,11 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -10337,28 +10337,28 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>35.59</v>
+        <v>75.67</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>427.08</v>
+        <v>605.36</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>Digi-Key API 2026-10-20: 57 in stock</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>342A024-25-0</t>
+          <t>342A048-25-0</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -10387,11 +10387,11 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -10402,28 +10402,28 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>50.66</v>
+        <v>117.77</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>557.26</v>
+        <v>235.54</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 140 in stock</t>
+          <t>Digi-Key API 2026-10-20: 46 in stock</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>342A034-25-0</t>
+          <t>382A012-25-0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10452,11 +10452,11 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.1 X 6.6/3.3 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -10467,28 +10467,28 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>75.67</v>
+        <v>31</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>605.36</v>
+        <v>124</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A012-25-0/2394192</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 57 in stock</t>
+          <t>Digi-Key API 2026-10-20: 380 in stock</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>342A048-25-0</t>
+          <t>382A023-25-0</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -10517,11 +10517,11 @@
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.4 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -10532,28 +10532,28 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>117.77</v>
+        <v>46.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>235.54</v>
+        <v>140.7</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A023-25-0/2394201</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 46 in stock</t>
+          <t>Digi-Key API 2026-10-20: 152 in stock</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>382A012-25-0</t>
+          <t>382A034-25-0</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10582,11 +10582,11 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.1 X 6.6/3.3 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 38.6/18.0 X 26.9/12.4 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -10597,28 +10597,28 @@
         <v>0</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>31</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>124</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A012-25-0/2394192</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A034-25-0/2394193</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 380 in stock</t>
+          <t>Digi-Key API 2026-10-20: 34 in stock</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -10636,22 +10636,22 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>382A023-25-0</t>
+          <t>4-1437290-0</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.4 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 1, SOCKET CONTACTS, BLUE</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -10659,31 +10659,29 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>140.7</v>
-      </c>
+        <v>10.82</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A023-25-0/2394201</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-0/2054331</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 152 in stock</t>
+          <t>Digi-Key API 2026-10-20: 1305 in stock</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -10701,18 +10699,18 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>382A034-25-0</t>
+          <t>4-1437290-1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 38.6/18.0 X 26.9/12.4 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 2, SOCKET CONTACTS, BLUE</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -10724,31 +10722,29 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>93.31999999999999</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>93.31999999999999</v>
-      </c>
+        <v>11.92</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A034-25-0/2394193</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-1/2329261</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Tube), 2026-10-20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 34 in stock</t>
+          <t>Digi-Key API 2026-10-20: 506 in stock</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -10766,18 +10762,18 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4-1437290-0</t>
+          <t>462A023-25-0</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 1, SOCKET CONTACTS, BLUE</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 1 TO 3, 4 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.2 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
@@ -10789,18 +10785,20 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
+        <v>72.52</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>72.52</v>
+      </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-0/2054331</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/462A023-25-0/2394175</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
@@ -10811,7 +10809,7 @@
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 1305 in stock</t>
+          <t>Digi-Key API 2026-10-20: 33 in stock</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -10829,18 +10827,18 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4-1437290-1</t>
+          <t>470R 1/4W</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 2, SOCKET CONTACTS, BLUE</t>
+          <t>RESISTOR, FIXED, METAL FILM, 470 OHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -10852,29 +10850,31 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>11.92</v>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-1/2329261</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT470R/1741440</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Tube), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT470R</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 506 in stock</t>
+          <t>Digi-Key API 2026-10-20: 327849 in stock</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -10892,18 +10892,18 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>462A023-25-0</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Longacre</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 1 TO 3, 4 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.2 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>SWITCH, BATTERY DISCONNECT, 4 TERMINAL, 2 POLE, 175 A CONTINUOUS, 1000 A PEAK, 20 A AUXILIARY POLE, 6-36 V</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
@@ -10920,26 +10920,14 @@
       <c r="J43" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>72.52</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>72.52</v>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/462A023-25-0/2394175</t>
-        </is>
-      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 33 in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr"/>
@@ -10957,57 +10945,53 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>470R 1/4W</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 470 OHM, 5 PCT, 1/4 W</t>
+          <t>CABLE, SHIELDED, 1 CONDUCTOR, 20 AWG, WHITE, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT470R/1741440</t>
+          <t>https://www.te.com/en/product-55A1811-20-9-9CS2275.html</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT470R</t>
-        </is>
-      </c>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 327849 in stock</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr"/>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>3 cable runs, 3.0 m + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -11022,45 +11006,53 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Longacre</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>SWITCH, BATTERY DISCONNECT, 4 TERMINAL, 2 POLE, 175 A CONTINUOUS, 1000 A PEAK, 20 A AUXILIARY POLE, 6-36 V</t>
+          <t>CABLE, SHIELDED, 2 CONDUCTOR TWISTED PAIR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-55A1821-20-6-9-9.html</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr"/>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>5 cable runs, 3.1 m + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11075,7 +11067,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -11086,11 +11078,11 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 1 CONDUCTOR, 20 AWG, WHITE, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CABLE, SHIELDED, 3 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -11101,13 +11093,13 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-55A1811-20-9-9CS2275.html</t>
+          <t>https://www.te.com/en/product-55A1831-20-2-4-6-9.html</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
@@ -11119,7 +11111,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>3 cable runs, 3.0 m + 15% margin</t>
+          <t>6 cable runs, 5.9 m + 15% margin</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11128,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -11147,11 +11139,11 @@
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 2 CONDUCTOR TWISTED PAIR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CABLE, SHIELDED, 4 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
@@ -11162,13 +11154,13 @@
         <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K47" s="3" t="inlineStr"/>
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-55A1821-20-6-9-9.html</t>
+          <t>https://www.te.com/en/product-55A1841-20-2-4-5-6-9.html</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
@@ -11180,7 +11172,7 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>5 cable runs, 3.1 m + 15% margin</t>
+          <t>4 cable runs, 4.9 m + 15% margin</t>
         </is>
       </c>
     </row>
@@ -11197,53 +11189,57 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Sumitomo</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 3 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CONTACT, SOCKET, CRIMP, SUMITOMO TS 090 (2.3 MM), TIN, 0.5-1.25 MM2 (20-16 AWG)</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-55A1831-20-2-4-6-9.html</t>
+          <t>https://www.customconnectorkits.com/products/8100-0461-l?variant=46049028800830</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>6 cable runs, 5.9 m + 15% margin</t>
-        </is>
-      </c>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -11258,53 +11254,45 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 4 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CONNECTOR, PLUG, TOYOTA, ROUND, 3 POS</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K49" s="3" t="inlineStr"/>
       <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-55A1841-20-2-4-5-6-9.html</t>
-        </is>
-      </c>
+      <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="3" t="inlineStr"/>
       <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>4 cable runs, 4.9 m + 15% margin</t>
-        </is>
-      </c>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11319,22 +11307,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>8100-0461</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Sumitomo</t>
-        </is>
-      </c>
+          <t>90980-10897</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>CONTACT, SOCKET, CRIMP, SUMITOMO TS 090 (2.3 MM), TIN, 0.5-1.25 MM2 (20-16 AWG)</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -11345,23 +11325,23 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.2</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/8100-0461-l?variant=46049028800830</t>
+          <t>https://www.ksvlooms.com/products/toyota-lexus-90980-10897-8-pin-connector-kit?variant=29504109805610</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -11384,20 +11364,12 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>90980-10341</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
+          <t>90980-10942</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>CONNECTOR, PLUG, TOYOTA, ROUND, 3 POS</t>
-        </is>
-      </c>
+      <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="n">
         <v>1</v>
       </c>
@@ -11437,14 +11409,22 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>90980-10897</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>90980-11062</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -11455,17 +11435,17 @@
         <v>0</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>4.52</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>18.08</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/toyota-lexus-90980-10897-8-pin-connector-kit?variant=29504109805610</t>
+          <t>https://www.ksvlooms.com/products/2-way-connector-kit-for-toyota-lexus-90980-11062-water-temperature-sensor-22-18-awg?variant=11482559741994</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
@@ -11494,12 +11474,20 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>90980-10942</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr"/>
+          <t>90980-11143</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
       <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>CONNECTOR, PLUG, TOYOTA OVAL, 3 POS, SOCKET CONTACTS</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="n">
         <v>1</v>
       </c>
@@ -11539,7 +11527,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>90980-11062</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11550,11 +11538,11 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS</t>
+          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS (HOUSING CONNECTOR F), BACK-UP LIGHT SWITCH</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -11565,28 +11553,16 @@
         <v>0</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/2-way-connector-kit-for-toyota-lexus-90980-11062-water-temperature-sensor-22-18-awg?variant=11482559741994</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
-        </is>
-      </c>
+      <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -11604,7 +11580,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -11615,11 +11591,11 @@
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA OVAL, 3 POS, SOCKET CONTACTS</t>
+          <t>CONNECTOR, PLUG, TOYOTA, 4 POS</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
@@ -11630,7 +11606,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K55" s="3" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr"/>
@@ -11657,20 +11633,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>90980-11250</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
+          <t>90980-12068</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS (HOUSING CONNECTOR F), BACK-UP LIGHT SWITCH</t>
-        </is>
-      </c>
+      <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="n">
         <v>1</v>
       </c>
@@ -11710,33 +11678,33 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA, 4 POS</t>
+          <t>CABLE, BATTERY, 1/0 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
@@ -11748,7 +11716,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>7.2 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11763,25 +11735,33 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>90980-12068</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>BC-1/0-RED</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>CABLE, BATTERY, 1/0 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
@@ -11793,7 +11773,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>5.8 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -11808,7 +11792,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -11819,11 +11803,11 @@
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 1/0 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>CABLE, BATTERY, 2 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -11834,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
@@ -11848,7 +11832,7 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>7.2 m in the master + 15% margin</t>
+          <t>2.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11849,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -11876,11 +11860,11 @@
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 1/0 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>CABLE, BATTERY, 4 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11891,7 +11875,7 @@
         <v>0</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
@@ -11905,7 +11889,7 @@
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>5.8 m in the master + 15% margin</t>
+          <t>3.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -11922,49 +11906,57 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>D 261 205 358-01</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 2 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>CONNECTOR, PLUG, BOSCH MOTORSPORT KIT, 6 POS, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/6-way-connector-kit-same-as-bosch-d261-205-358-01-23-20-awg?variant=40430818852899</t>
+        </is>
+      </c>
       <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>2.4 m in the master + 15% margin</t>
-        </is>
-      </c>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11979,47 +11971,59 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>DR-25-1-0-SP</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 4 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 25.4 MM EXPANDED ID, 12.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/1-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737243683</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $6.12 per ft</t>
+        </is>
+      </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>3.2 m in the master + 15% margin</t>
+          <t>0.8 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12036,57 +12040,49 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>D 261 205 358-01</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, BOSCH MOTORSPORT KIT, 6 POS, SOCKET CONTACTS</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 38.1 MM EXPANDED ID, 19.0 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M63" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/6-way-connector-kit-same-as-bosch-d261-205-358-01-23-20-awg?variant=40430818852899</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+      <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
-        </is>
-      </c>
+      <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q63" s="3" t="inlineStr"/>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>1.3 m of bundle + 10 % cut / recovery margin</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12101,7 +12097,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-0-SP</t>
+          <t>DR-25-1/2-0-SP</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -12112,11 +12108,11 @@
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 25.4 MM EXPANDED ID, 12.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 12.7 MM EXPANDED ID, 6.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -12127,23 +12123,23 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>20.08</v>
+        <v>14.24</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>20.08</v>
+        <v>85.44</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/1-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737243683</t>
+          <t>https://www.ksvlooms.com/products/1-2-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735736355</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $6.12 per ft</t>
+          <t>KSV Looms, 2026-10-20; $4.34 per ft</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -12153,7 +12149,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>0.8 m of bundle + 10 % cut / recovery margin</t>
+          <t>5.3 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12166,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>DR-25-1/4-0-SP</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -12181,11 +12177,11 @@
       <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 38.1 MM EXPANDED ID, 19.0 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 6.4 MM EXPANDED ID, 3.2 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -12196,21 +12192,33 @@
         <v>0</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/1-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735113763</t>
+        </is>
+      </c>
       <c r="N65" s="3" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $1.71 per ft</t>
+        </is>
+      </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>1.3 m of bundle + 10 % cut / recovery margin</t>
+          <t>3.9 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12235,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1/2-0-SP</t>
+          <t>DR-25-3/16-0-SP</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -12238,11 +12246,11 @@
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 12.7 MM EXPANDED ID, 6.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -12253,23 +12261,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>14.24</v>
+        <v>5.54</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>99.68000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/1-2-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735736355</t>
+          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $4.34 per ft</t>
+          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -12279,7 +12287,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>5.6 m of bundle + 10 % cut / recovery margin</t>
+          <t>11.6 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12304,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1/4-0-SP</t>
+          <t>DR-25-3/4-0-SP</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -12307,11 +12315,11 @@
       <c r="E67" s="3" t="inlineStr"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 6.4 MM EXPANDED ID, 3.2 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 19.0 MM EXPANDED ID, 9.5 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -12322,23 +12330,23 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>5.61</v>
+        <v>14.99</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>28.05</v>
+        <v>119.92</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/1-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735113763</t>
+          <t>https://www.ksvlooms.com/products/3-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737112611</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $1.71 per ft</t>
+          <t>KSV Looms, 2026-10-20; $4.57 per ft</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -12348,7 +12356,7 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>3.9 m of bundle + 10 % cut / recovery margin</t>
+          <t>7.2 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12373,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/16-0-SP</t>
+          <t>DR-25-3/8-0-SP</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -12376,7 +12384,7 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 9.53 MM EXPANDED ID, 4.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
@@ -12394,20 +12402,20 @@
         <v>13</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5.54</v>
+        <v>10.83</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>72.02</v>
+        <v>140.79</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
+          <t>https://www.ksvlooms.com/products/3-8-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735343139</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
+          <t>KSV Looms, 2026-10-20; $3.30 per ft</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -12417,7 +12425,7 @@
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>11.6 m of bundle + 10 % cut / recovery margin</t>
+          <t>11.2 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12434,61 +12442,61 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/4-0-SP</t>
+          <t>DRB12-102PAE-L018</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 19.0 MM EXPANDED ID, 9.5 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, DRB, 102 POS, PIN CONTACTS, E SEAL, A KEY, WIRE ROUTER, FLANGE MOUNT</t>
         </is>
       </c>
       <c r="G69" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>14.99</v>
+        <v>55.13</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>119.92</v>
+        <v>55.13</v>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737112611</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB12-102PAE-L018/10461602</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $4.57 per ft</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>6.8 m of bundle + 10 % cut / recovery margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 61 in stock</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12503,61 +12511,57 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/8-0-SP</t>
+          <t>DRB16-102SAE-L018</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 9.53 MM EXPANDED ID, 4.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>CONNECTOR, PLUG, DRB, 102 POS, SOCKET CONTACTS, E SEAL, A KEY, WIRE ROUTER</t>
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>10.83</v>
+        <v>46.89</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>140.79</v>
+        <v>46.89</v>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-8-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735343139</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB16-102SAE-L018/10461459</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $3.30 per ft</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>11.2 m of bundle + 10 % cut / recovery margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 45 in stock</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -12572,7 +12576,7 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>DRB12-102PAE-L018</t>
+          <t>DRBF-1A</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -12587,7 +12591,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DRB, 102 POS, PIN CONTACTS, E SEAL, A KEY, WIRE ROUTER, FLANGE MOUNT</t>
+          <t>FLANGE, MOUNTING, DRB 102/128 SERIES</t>
         </is>
       </c>
       <c r="G71" s="3" t="n">
@@ -12605,25 +12609,25 @@
         <v>1</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>55.13</v>
+        <v>179.14</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>55.13</v>
+        <v>179.14</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB12-102PAE-L018/10461602</t>
+          <t>https://www.digikey.com/en/products/detail/powell-electronics/DRBF-1A/29580951</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 10 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 61 in stock</t>
+          <t>Digi-Key API 2026-10-20: 37 in stock</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr"/>
@@ -12641,7 +12645,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>DRB16-102SAE-L018</t>
+          <t>DT04-08PA-P021</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -12652,7 +12656,7 @@
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DRB, 102 POS, SOCKET CONTACTS, E SEAL, A KEY, WIRE ROUTER</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 8 POS, BUSSED 1 X 8, NICKEL PINS MOULDED IN, 13 A PER PIN, 52 A BUS, WEDGELOCK INCLUDED, GRAY</t>
         </is>
       </c>
       <c r="G72" s="2" t="n">
@@ -12670,25 +12674,25 @@
         <v>1</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>46.89</v>
+        <v>144.42</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>46.89</v>
+        <v>144.42</v>
       </c>
       <c r="M72" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB16-102SAE-L018/10461459</t>
+          <t>https://www.digikey.com/en/products/detail/powell-electronics/DT04-08PA-P021/29660378</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 10 (Tray), 2026-10-20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 45 in stock</t>
+          <t>Digi-Key API 2026-10-20: 30 in stock</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr"/>
@@ -12706,7 +12710,7 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>DRBF-1A</t>
+          <t>DT04-12PA-P021</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -12714,18 +12718,14 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+      <c r="E73" s="3" t="inlineStr"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>FLANGE, MOUNTING, DRB 102/128 SERIES</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 12 POS, BUSSED 1 X 12, NICKEL PINS MOULDED IN, 13 A PER PIN, 78 A BUS, WEDGELOCK INCLUDED, GRAY</t>
         </is>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
@@ -12736,28 +12736,28 @@
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>179.14</v>
+        <v>12.35</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>179.14</v>
+        <v>49.4</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/powell-electronics/DRBF-1A/29580951</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-12PA-P021/9923072</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 10 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 37 in stock</t>
+          <t>Digi-Key API 2026-10-20: 1418 in stock</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr"/>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>DT04-08PA-P021</t>
+          <t>DT04-2P</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -12783,14 +12783,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 8 POS, BUSSED 1 X 8, NICKEL PINS MOULDED IN, 13 A PER PIN, 52 A BUS, WEDGELOCK INCLUDED, GRAY</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 2 POS, PIN CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12801,28 +12805,28 @@
         <v>0</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>144.42</v>
+        <v>0.67</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>144.42</v>
+        <v>1.34</v>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/powell-electronics/DT04-08PA-P021/29660378</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-2P/6566582</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 10 (Tray), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 30 in stock</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr"/>
@@ -12840,7 +12844,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>DT04-12PA-P021</t>
+          <t>DT04-6P</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -12848,14 +12852,18 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr"/>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 12 POS, BUSSED 1 X 12, NICKEL PINS MOULDED IN, 13 A PER PIN, 78 A BUS, WEDGELOCK INCLUDED, GRAY</t>
+          <t>CONNECTOR, RECEPTACLE, DT, 6 POS, PIN CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
@@ -12866,28 +12874,28 @@
         <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>12.35</v>
+        <v>2.34</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>49.4</v>
+        <v>4.68</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-12PA-P021/9923072</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-6P/6566585</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 1418 in stock</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr"/>
@@ -12905,7 +12913,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>DT04-2P</t>
+          <t>DT06-08SA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -12920,11 +12928,11 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 2 POS, PIN CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -12935,17 +12943,17 @@
         <v>0</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.67</v>
+        <v>3.81</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1.34</v>
+        <v>3.81</v>
       </c>
       <c r="M76" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-2P/6566582</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr"/>
@@ -12974,58 +12982,54 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>DT04-6P</t>
+          <t>DT06-12SA</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>TE Connectivity DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, DT, 6 POS, PIN CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
         </is>
       </c>
       <c r="G77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J77" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>2.34</v>
+        <v>4.22</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>4.68</v>
+        <v>12.66</v>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT04-6P/6566585</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-12SA/6566568</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 14204 in stock</t>
         </is>
       </c>
       <c r="Q77" s="3" t="inlineStr"/>
@@ -13043,7 +13047,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>DT06-08SA</t>
+          <t>DT06-2S</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -13051,18 +13055,14 @@
           <t>TE DEUTSCH</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+      <c r="E78" s="2" t="inlineStr"/>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 8 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -13073,28 +13073,28 @@
         <v>0</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>3.81</v>
+        <v>0.77</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3.81</v>
+        <v>2.31</v>
       </c>
       <c r="M78" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-08SA/6566565</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 41242 in stock</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr"/>
@@ -13112,22 +13112,26 @@
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>DT06-12SA</t>
+          <t>DT06-2S-CE05</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 12 POS, SOCKET CONTACTS, N SEAL, KEY A, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G79" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
@@ -13135,31 +13139,31 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>4.22</v>
+        <v>0.77</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>12.66</v>
+        <v>6.16</v>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-12SA/6566568</t>
+          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
         </is>
       </c>
       <c r="N79" s="3" t="inlineStr"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P79" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 14204 in stock</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="3" t="inlineStr"/>
@@ -13177,22 +13181,22 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>DT06-2S</t>
+          <t>DT06-3S</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>TE Connectivity DEUTSCH</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -13203,28 +13207,28 @@
         <v>0</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-2S/6566572</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S/6566573</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 41242 in stock</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr"/>
@@ -13242,12 +13246,12 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>DT06-2S-CE05</t>
+          <t>DT06-3S-CE05</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>TE Connectivity DEUTSCH</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -13257,11 +13261,11 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 2 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
@@ -13272,28 +13276,28 @@
         <v>0</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>0.77</v>
+        <v>2.06</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>6.16</v>
+        <v>2.06</v>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-DT06-2S-CE05.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>family price (DT06-2S, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="3" t="inlineStr"/>
@@ -13311,22 +13315,22 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>DT06-3S</t>
+          <t>DT06-6S</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -13337,28 +13341,28 @@
         <v>0</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.52</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.04</v>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S/6566573</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr"/>
@@ -13376,12 +13380,12 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>DT06-3S-CE05</t>
+          <t>DTHD06-1-8S</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity DEUTSCH</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -13391,11 +13395,11 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 3 POS, SOCKET CONTACTS, E SEAL, INSUL 1.35-3.05 MM, ENHANCED SEAL RETENTION, END CAP, BLACK</t>
+          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
@@ -13406,17 +13410,17 @@
         <v>0</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>2.06</v>
+        <v>3.48</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>2.06</v>
+        <v>13.92</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-3S-CE05/7219768</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
         </is>
       </c>
       <c r="N83" s="3" t="inlineStr"/>
@@ -13445,22 +13449,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>DT06-6S</t>
+          <t>DTM06-4S</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DT, 6 POS, SOCKET CONTACTS, N SEAL, GRAY</t>
+          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -13471,28 +13475,28 @@
         <v>0</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>5.04</v>
+        <v>2.05</v>
       </c>
       <c r="M84" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DT06-6S/6566575</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTM06-4S/6566635</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 15700 in stock</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr"/>
@@ -13510,26 +13514,22 @@
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>DTHD06-1-8S</t>
+          <t>DTM06-6S</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTHD, 1 POS, SIZE 8 SOCKET CONTACT, 8-10 AWG, 60 A</t>
+          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
         </is>
       </c>
       <c r="G85" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
@@ -13540,28 +13540,28 @@
         <v>0</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>3.48</v>
+        <v>2.48</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>13.92</v>
+        <v>2.48</v>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTHD06-1-8S/9554131</t>
+          <t>https://www.ksvlooms.com/products/dtm06-6s-deutsch-dtm-housing?variant=43643315290147</t>
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr"/>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P85" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q85" s="3" t="inlineStr"/>
@@ -13579,18 +13579,18 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>DTM06-4S</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 4 POS, SOCKET CONTACTS, GRAY</t>
+          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
@@ -13607,26 +13607,14 @@
       <c r="J86" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K86" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M86" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DTM06-4S/6566635</t>
-        </is>
-      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O86" s="2" t="inlineStr"/>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 15700 in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr"/>
@@ -13644,22 +13632,22 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>DTM06-6S</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>CNLINKO</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, DTM, 6 POS, SOCKET CONTACTS, GRAY</t>
+          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
@@ -13670,28 +13658,16 @@
         <v>0</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="M87" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/dtm06-6s-deutsch-dtm-housing?variant=43643315290147</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
+      <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q87" s="3" t="inlineStr"/>
@@ -13709,45 +13685,61 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>M22759/16-10-0</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, HD30, SHELL 24, 33 POS, SOCKET CONTACTS, E SEAL</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="M88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/10-awg-black-tefzel-wire-m22759-16-10-0-cut-length?variant=40451551199267</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q88" s="2" t="inlineStr"/>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>0.9 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -13762,45 +13754,61 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>M22759/16-10-1</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>CNLINKO</t>
+          <t>M22759</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CIRCULAR, LP-16, CABLE PLUG, FEMALE, 5 POS, PLASTIC, SOLDER, 22-20 AWG, IP68 MATED, LATCH</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K89" s="3" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/10-awg-brown-tefzel-wire-m22759-16-10-1-spool?variant=40423436288035</t>
+        </is>
+      </c>
       <c r="N89" s="3" t="inlineStr"/>
-      <c r="O89" s="3" t="inlineStr"/>
+      <c r="O89" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P89" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q89" s="3" t="inlineStr"/>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>2.0 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -13815,7 +13823,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-0</t>
+          <t>M22759/16-10-2</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -13826,11 +13834,11 @@
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -13841,17 +13849,17 @@
         <v>0</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>4.08</v>
+        <v>3.5</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>16.32</v>
+        <v>115.5</v>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-black-tefzel-wire-m22759-16-10-0-cut-length?variant=40451551199267</t>
+          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
@@ -13867,7 +13875,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>0.9 m in the master + 15% margin</t>
+          <t>8.7 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13892,7 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-1</t>
+          <t>M22759/16-12-0</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -13895,11 +13903,11 @@
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
@@ -13910,17 +13918,17 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>2.72</v>
+        <v>3.56</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>21.76</v>
+        <v>7.12</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-brown-tefzel-wire-m22759-16-10-1-spool?variant=40423436288035</t>
+          <t>https://www.ksvlooms.com/products/12-awg-black-tefzel-wire-m22759-16-12-0-spool?variant=40415052726307</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr"/>
@@ -13936,7 +13944,7 @@
       </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>0.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13961,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-10-2</t>
+          <t>M22759/16-12-2</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -13964,11 +13972,11 @@
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 10 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -13979,17 +13987,17 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>115.5</v>
+        <v>10.68</v>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/10-awg-red-tefzel-wire-m22759-16-10-2-cut-length?variant=40451119939619</t>
+          <t>https://www.ksvlooms.com/products/12-awg-red-tefzel-wire-m22759-16-12-2-spool?variant=40415053152291</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr"/>
@@ -14005,7 +14013,7 @@
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>8.7 m in the master + 15% margin</t>
+          <t>0.7 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14030,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-12-0</t>
+          <t>M22759/16-14-0</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -14033,11 +14041,11 @@
       <c r="E93" s="3" t="inlineStr"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
@@ -14048,17 +14056,17 @@
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>3.56</v>
+        <v>2.56</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>7.12</v>
+        <v>10.24</v>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/12-awg-black-tefzel-wire-m22759-16-12-0-spool?variant=40415052726307</t>
+          <t>https://www.ksvlooms.com/products/14-awg-black-tefzel-wire-m22759-16-14-0-spool?variant=40415048695843</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr"/>
@@ -14074,7 +14082,7 @@
       </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
-          <t>0.3 m in the master + 15% margin</t>
+          <t>0.9 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14099,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-12-2</t>
+          <t>M22759/16-14-2</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -14102,11 +14110,11 @@
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 12 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
@@ -14117,33 +14125,33 @@
         <v>0</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>3.56</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>10.68</v>
+        <v>31</v>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/12-awg-red-tefzel-wire-m22759-16-12-2-spool?variant=40415053152291</t>
+          <t>https://www.awcwire.com/product/m22759_16-14</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>0.7 m in the master + 15% margin</t>
+          <t>8.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14168,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-0</t>
+          <t>M22759/16-14-6</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -14171,11 +14179,11 @@
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
@@ -14186,17 +14194,17 @@
         <v>0</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>10.24</v>
+        <v>87.36</v>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/14-awg-black-tefzel-wire-m22759-16-14-0-spool?variant=40415048695843</t>
+          <t>https://www.ksvlooms.com/products/14-awg-blue-tefzel-wire-m22759-16-14-6-spool?variant=40423417708579</t>
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr"/>
@@ -14212,7 +14220,7 @@
       </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
-          <t>0.9 m in the master + 15% margin</t>
+          <t>7.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14237,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-2</t>
+          <t>M22759/16-14-60</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -14240,11 +14248,11 @@
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
@@ -14255,33 +14263,21 @@
         <v>0</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K96" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="M96" s="4" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-14</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14294,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-6</t>
+          <t>M22759/16-14-62</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -14309,11 +14305,11 @@
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
@@ -14324,33 +14320,21 @@
         <v>0</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>87.36</v>
-      </c>
-      <c r="M97" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/14-awg-blue-tefzel-wire-m22759-16-14-6-spool?variant=40423417708579</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
+      <c r="L97" s="3" t="inlineStr"/>
+      <c r="M97" s="3" t="inlineStr"/>
       <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
-          <t>7.3 m in the master + 15% margin</t>
+          <t>2.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14367,7 +14351,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-60</t>
+          <t>M22759/16-14-63</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -14378,7 +14362,7 @@
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
@@ -14424,7 +14408,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-62</t>
+          <t>M22759/16-14-69</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -14435,11 +14419,11 @@
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
@@ -14450,7 +14434,7 @@
         <v>0</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
       <c r="L99" s="3" t="inlineStr"/>
@@ -14464,7 +14448,7 @@
       </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
-          <t>2.8 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14481,7 +14465,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-63</t>
+          <t>M22759/16-16-0</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -14492,11 +14476,11 @@
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -14507,21 +14491,33 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K100" s="2" t="inlineStr"/>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>3.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14534,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-14-69</t>
+          <t>M22759/16-16-2</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -14549,11 +14545,11 @@
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 14 AWG, BLUE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
@@ -14564,21 +14560,33 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
-      <c r="L101" s="3" t="inlineStr"/>
-      <c r="M101" s="3" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-16</t>
+        </is>
+      </c>
       <c r="N101" s="3" t="inlineStr"/>
-      <c r="O101" s="3" t="inlineStr"/>
+      <c r="O101" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P101" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>8.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14603,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-0</t>
+          <t>M22759/16-16-20</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -14606,11 +14614,11 @@
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -14621,33 +14629,21 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K102" s="2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="M102" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/16-awg-black-tefzel-wire-m22759-16-16-0-spool?variant=40415046434851</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O102" s="2" t="inlineStr"/>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>3.5 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14660,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-2</t>
+          <t>M22759/16-16-26</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -14675,11 +14671,11 @@
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
@@ -14690,33 +14686,21 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="K103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L103" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="M103" s="5" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-16</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K103" s="3" t="inlineStr"/>
+      <c r="L103" s="3" t="inlineStr"/>
+      <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="inlineStr"/>
-      <c r="O103" s="3" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>8.4 m in the master + 15% margin</t>
+          <t>2.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14733,7 +14717,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-20</t>
+          <t>M22759/16-16-50</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -14744,11 +14728,11 @@
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -14759,7 +14743,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
@@ -14773,7 +14757,7 @@
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>4.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14790,7 +14774,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-26</t>
+          <t>M22759/16-16-53</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -14801,11 +14785,11 @@
       <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, RED/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -14816,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K105" s="3" t="inlineStr"/>
       <c r="L105" s="3" t="inlineStr"/>
@@ -14830,7 +14814,7 @@
       </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>2.4 m in the master + 15% margin</t>
+          <t>4.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14831,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-50</t>
+          <t>M22759/16-16-59</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -14858,11 +14842,11 @@
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -14873,7 +14857,7 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
@@ -14887,7 +14871,7 @@
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>4.2 m in the master + 15% margin</t>
+          <t>1.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14888,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-53</t>
+          <t>M22759/16-16-90</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
@@ -14915,11 +14899,11 @@
       <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 16 AWG, WHITE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -14930,7 +14914,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K107" s="3" t="inlineStr"/>
       <c r="L107" s="3" t="inlineStr"/>
@@ -14944,7 +14928,7 @@
       </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
-          <t>4.1 m in the master + 15% margin</t>
+          <t>2.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -14961,7 +14945,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-16-59</t>
+          <t>M22759/16-18-0</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -14972,11 +14956,11 @@
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, GREEN/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -14987,21 +14971,33 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K108" s="2" t="inlineStr"/>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="M108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-black-tefzel-wire-m22759-16-18-0-spool?variant=40415044370467</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>1.4 m in the master + 15% margin</t>
+          <t>0.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15014,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-90</t>
+          <t>M22759/16-18-2</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
@@ -15029,11 +15025,11 @@
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 16 AWG, WHITE/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
@@ -15044,21 +15040,33 @@
         <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr"/>
-      <c r="M109" s="3" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.awcwire.com/product/m22759_16-18</t>
+        </is>
+      </c>
       <c r="N109" s="3" t="inlineStr"/>
-      <c r="O109" s="3" t="inlineStr"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
       <c r="P109" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
-          <t>2.3 m in the master + 15% margin</t>
+          <t>9.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15083,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-0</t>
+          <t>M22759/16-18-29</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -15086,7 +15094,7 @@
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, RED/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
@@ -15103,26 +15111,14 @@
       <c r="J110" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K110" s="2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="M110" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/18-awg-black-tefzel-wire-m22759-16-18-0-spool?variant=40415044370467</t>
-        </is>
-      </c>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
       <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -15144,7 +15140,7 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-2</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -15155,11 +15151,11 @@
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
@@ -15170,33 +15166,21 @@
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="K111" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="M111" s="5" t="inlineStr">
-        <is>
-          <t>https://www.awcwire.com/product/m22759_16-18</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K111" s="3" t="inlineStr"/>
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="inlineStr"/>
-      <c r="O111" s="3" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
-          <t>5.7 m in the master + 15% margin</t>
+          <t>1.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15197,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-29</t>
+          <t>M22759/16-18-50</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -15224,11 +15208,11 @@
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, RED/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -15239,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
@@ -15253,7 +15237,7 @@
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>0.4 m in the master + 15% margin</t>
+          <t>7.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15270,7 +15254,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>M22759/16-18-54</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -15281,11 +15265,11 @@
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -15296,7 +15280,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr"/>
@@ -15310,7 +15294,7 @@
       </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
-          <t>7.2 m in the master + 15% margin</t>
+          <t>8.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15311,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>M22759/16-18-7</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -15338,11 +15322,11 @@
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, GREEN/YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -15353,21 +15337,33 @@
         <v>0</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K114" s="2" t="inlineStr"/>
-      <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="M114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/18-awg-purple-tefzel-wire-m22759-16-18-7-spool?variant=40423402700835</t>
+        </is>
+      </c>
       <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
         <is>
-          <t>8.3 m in the master + 15% margin</t>
+          <t>7.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15380,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-7</t>
+          <t>M22759/16-18-9</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -15395,11 +15391,11 @@
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -15410,17 +15406,17 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>38.08</v>
+        <v>20.8</v>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/18-awg-purple-tefzel-wire-m22759-16-18-7-spool?variant=40423402700835</t>
+          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr"/>
@@ -15436,7 +15432,7 @@
       </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>7.4 m in the master + 15% margin</t>
+          <t>3.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15453,7 +15449,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-9</t>
+          <t>M22759/16-20-0</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -15464,11 +15460,11 @@
       <c r="E116" s="2" t="inlineStr"/>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 18 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
@@ -15479,17 +15475,17 @@
         <v>0</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>16</v>
+        <v>27.72</v>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/18-awg-white-tefzel-wire-m22759-16-18-9-spool?variant=40415044829219</t>
+          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr"/>
@@ -15505,7 +15501,7 @@
       </c>
       <c r="Q116" s="2" t="inlineStr">
         <is>
-          <t>2.6 m in the master + 15% margin</t>
+          <t>5.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15522,7 +15518,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-0</t>
+          <t>M22759/16-20-06</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -15533,11 +15529,11 @@
       <c r="E117" s="3" t="inlineStr"/>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G117" s="3" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
@@ -15548,33 +15544,21 @@
         <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K117" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="L117" s="3" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="M117" s="5" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-black-tefzel-wire-m22759-16-20-0-spool?variant=40415026577443</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr"/>
       <c r="N117" s="3" t="inlineStr"/>
-      <c r="O117" s="3" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O117" s="3" t="inlineStr"/>
       <c r="P117" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>5.4 m in the master + 15% margin</t>
+          <t>0.6 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15575,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>M22759/16-20-09</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -15602,11 +15586,11 @@
       <c r="E118" s="2" t="inlineStr"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
@@ -15617,7 +15601,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
@@ -15631,7 +15615,7 @@
       </c>
       <c r="Q118" s="2" t="inlineStr">
         <is>
-          <t>0.6 m in the master + 15% margin</t>
+          <t>6.4 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15632,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>M22759/16-20-1</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -15659,11 +15643,11 @@
       <c r="E119" s="3" t="inlineStr"/>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLACK/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G119" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
@@ -15674,21 +15658,33 @@
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K119" s="3" t="inlineStr"/>
-      <c r="L119" s="3" t="inlineStr"/>
-      <c r="M119" s="3" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-brown-tefzel-wire-m22759-16-20-1-spool?variant=40415026708515</t>
+        </is>
+      </c>
       <c r="N119" s="3" t="inlineStr"/>
-      <c r="O119" s="3" t="inlineStr"/>
+      <c r="O119" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P119" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
-          <t>6.4 m in the master + 15% margin</t>
+          <t>6.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15705,7 +15701,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-1</t>
+          <t>M22759/16-20-2</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -15716,11 +15712,11 @@
       <c r="E120" s="2" t="inlineStr"/>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BROWN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
@@ -15731,33 +15727,33 @@
         <v>0</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>23.52</v>
+        <v>14</v>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-brown-tefzel-wire-m22759-16-20-1-spool?variant=40415026708515</t>
+          <t>https://www.awcwire.com/product/m22759_16-20</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr"/>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
         <is>
-          <t>6.3 m in the master + 15% margin</t>
+          <t>3.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15770,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-2</t>
+          <t>M22759/16-20-3</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
@@ -15785,11 +15781,11 @@
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G121" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
@@ -15800,33 +15796,33 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>14</v>
+        <v>33.28</v>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>https://www.awcwire.com/product/m22759_16-20</t>
+          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
         </is>
       </c>
       <c r="N121" s="3" t="inlineStr"/>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>KSV Looms, 2026-10-20</t>
         </is>
       </c>
       <c r="P121" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
-          <t>3.5 m in the master + 15% margin</t>
+          <t>8.3 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15839,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-3</t>
+          <t>M22759/16-20-39</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -15854,11 +15850,11 @@
       <c r="E122" s="2" t="inlineStr"/>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G122" s="2" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
@@ -15869,33 +15865,21 @@
         <v>0</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>32.24</v>
-      </c>
-      <c r="M122" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/20-awg-orange-tefzel-wire-m22759-16-20-3-spool?variant=40415028019235</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
       <c r="N122" s="2" t="inlineStr"/>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O122" s="2" t="inlineStr"/>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>1.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15896,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>M22759/16-20-4</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
@@ -15923,11 +15907,11 @@
       <c r="E123" s="3" t="inlineStr"/>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, ORANGE/WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G123" s="3" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
@@ -15938,21 +15922,33 @@
         <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K123" s="3" t="inlineStr"/>
-      <c r="L123" s="3" t="inlineStr"/>
-      <c r="M123" s="3" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L123" s="3" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
+        </is>
+      </c>
       <c r="N123" s="3" t="inlineStr"/>
-      <c r="O123" s="3" t="inlineStr"/>
+      <c r="O123" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P123" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
-          <t>1.1 m in the master + 15% margin</t>
+          <t>8.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -15969,7 +15965,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-4</t>
+          <t>M22759/16-20-5</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -15980,11 +15976,11 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, YELLOW, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, GREEN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -15995,17 +15991,17 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>36.96</v>
+        <v>32.24</v>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-yellow-tefzel-wire-m22759-16-20-4-spool?variant=40415028477987</t>
+          <t>https://www.ksvlooms.com/products/20-awg-green-tefzel-wire-m22759-16-20-5-spool?variant=40415028838435</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr"/>
@@ -16021,7 +16017,7 @@
       </c>
       <c r="Q124" s="2" t="inlineStr">
         <is>
-          <t>8.5 m in the master + 15% margin</t>
+          <t>8.1 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16038,7 +16034,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-5</t>
+          <t>M22759/16-20-6</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
@@ -16049,11 +16045,11 @@
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GREEN, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -16064,17 +16060,17 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>32.24</v>
+        <v>19.44</v>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-green-tefzel-wire-m22759-16-20-5-spool?variant=40415028838435</t>
+          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr"/>
@@ -16090,7 +16086,7 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>8.1 m in the master + 15% margin</t>
+          <t>4.6 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16103,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-6</t>
+          <t>M22759/16-20-7</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -16118,11 +16114,11 @@
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, BLUE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
@@ -16133,17 +16129,17 @@
         <v>0</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>6.48</v>
+        <v>24.36</v>
       </c>
       <c r="M126" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-blue-tefzel-wire-m22759-16-20-6-spool?variant=40415028903971</t>
+          <t>https://www.ksvlooms.com/products/20-awg-purple-tefzel-wire-m22759-16-20-7-spool?variant=40415029198883</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr"/>
@@ -16159,7 +16155,7 @@
       </c>
       <c r="Q126" s="2" t="inlineStr">
         <is>
-          <t>1.5 m in the master + 15% margin</t>
+          <t>5.5 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16172,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-7</t>
+          <t>M22759/16-20-8</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
@@ -16187,11 +16183,11 @@
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, VIOLET, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, GRAY, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
@@ -16202,17 +16198,17 @@
         <v>0</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K127" s="3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>24.36</v>
+        <v>21.6</v>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-purple-tefzel-wire-m22759-16-20-7-spool?variant=40415029198883</t>
+          <t>https://www.ksvlooms.com/products/20-awg-gray-tefzel-wire-m22759-16-20-8-spool?variant=40415029264419</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr"/>
@@ -16228,7 +16224,7 @@
       </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
-          <t>5.5 m in the master + 15% margin</t>
+          <t>4.7 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16245,7 +16241,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-8</t>
+          <t>M22759/16-20-9</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -16256,11 +16252,11 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, GRAY, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -16271,20 +16267,24 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.2</v>
+        <v>0.96</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>25.2</v>
+        <v>45.12</v>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-gray-tefzel-wire-m22759-16-20-8-spool?variant=40415029264419</t>
-        </is>
-      </c>
-      <c r="N128" s="2" t="inlineStr"/>
+          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
+        </is>
+      </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
+        </is>
+      </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
           <t>KSV Looms, 2026-10-20</t>
@@ -16297,7 +16297,7 @@
       </c>
       <c r="Q128" s="2" t="inlineStr">
         <is>
-          <t>5.3 m in the master + 15% margin</t>
+          <t>12.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-9</t>
+          <t>M22759/16-6-9</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -16325,11 +16325,11 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 20 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 6 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -16340,24 +16340,20 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>0.96</v>
+        <v>8.09</v>
       </c>
       <c r="L129" s="3" t="n">
-        <v>31.68</v>
+        <v>64.72</v>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/20-awg-white-tefzel-wire-m22759-16-20-9-spool?variant=40415029297187</t>
-        </is>
-      </c>
-      <c r="N129" s="5" t="inlineStr">
-        <is>
-          <t>https://www.flightstore.com.au/M22759/16-Extruded-ETFE-Tefzel-Wire-20AWG-Per-FT</t>
-        </is>
-      </c>
+          <t>https://www.ksvlooms.com/products/6-awg-white-tefzel-wire-m22759-16-6-9-spool?variant=40415058198563</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr"/>
       <c r="O129" s="3" t="inlineStr">
         <is>
           <t>KSV Looms, 2026-10-20</t>
@@ -16370,7 +16366,7 @@
       </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
-          <t>8.5 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16387,7 +16383,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-6-9</t>
+          <t>M22759/16-8-0</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -16398,11 +16394,11 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 6 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -16413,17 +16409,17 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>8.09</v>
+        <v>6.08</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>64.72</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/6-awg-white-tefzel-wire-m22759-16-6-9-spool?variant=40415058198563</t>
+          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr"/>
@@ -16439,7 +16435,7 @@
       </c>
       <c r="Q130" s="2" t="inlineStr">
         <is>
-          <t>2.0 m in the master + 15% margin</t>
+          <t>3.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16456,7 +16452,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-0</t>
+          <t>M22759/16-8-2</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
@@ -16467,11 +16463,11 @@
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, BLACK, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -16482,17 +16478,17 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>6.08</v>
+        <v>6.1</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>79.04000000000001</v>
+        <v>183</v>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/8-awg-black-tefzel-wire-m22759-16-8-0-cut-length?variant=40451555557411</t>
+          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
         </is>
       </c>
       <c r="N131" s="3" t="inlineStr"/>
@@ -16508,7 +16504,7 @@
       </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
-          <t>3.2 m in the master + 15% margin</t>
+          <t>7.8 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16521,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-8-2</t>
+          <t>M22759/16-8-9</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -16536,11 +16532,11 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, RED, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>WIRE, ELECTRICAL, 8 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -16551,17 +16547,17 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>6.1</v>
+        <v>6.44</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>183</v>
+        <v>51.52</v>
       </c>
       <c r="M132" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/8-awg-red-tefzel-wire-m22759-16-8-2-cut-length?variant=40451557523491</t>
+          <t>https://www.ksvlooms.com/products/8-awg-white-tefzel-wire-m22759-16-8-9-spool?variant=40415055740963</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr"/>
@@ -16577,7 +16573,7 @@
       </c>
       <c r="Q132" s="2" t="inlineStr">
         <is>
-          <t>7.8 m in the master + 15% margin</t>
+          <t>2.0 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16594,61 +16590,57 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-8-9</t>
+          <t>RL00801-50BK</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>M22759</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>WIRE, ELECTRICAL, 8 AWG, WHITE, ETFE (TEFZEL) INSULATED, TIN PLATED COPPER, 150 C, 600 V</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>6.44</v>
+        <v>13.46</v>
       </c>
       <c r="L133" s="3" t="n">
-        <v>51.52</v>
+        <v>26.92</v>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/8-awg-white-tefzel-wire-m22759-16-8-9-spool?variant=40415055740963</t>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
         </is>
       </c>
       <c r="N133" s="3" t="inlineStr"/>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P133" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q133" s="3" t="inlineStr">
-        <is>
-          <t>2.0 m in the master + 15% margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 65 in stock</t>
+        </is>
+      </c>
+      <c r="Q133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -16663,7 +16655,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>RL00801-50BK</t>
+          <t>RL00801-50RE</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -16674,7 +16666,7 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), BLACK</t>
+          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
@@ -16699,7 +16691,7 @@
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50BK/16271509</t>
+          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr"/>
@@ -16710,7 +16702,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 65 in stock</t>
+          <t>Digi-Key API 2026-10-20: 72 in stock</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr"/>
@@ -16728,57 +16720,57 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>RL00801-50RE</t>
+          <t>RNF-100-3/16-4-STK</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, CABLE, RADLOK 8.0, FEMALE, 200 A, 50 MM2 (1/0), RED</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I135" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>13.46</v>
+        <v>0</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="M135" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/amphenol-technical-products-international/RL00801-50RE/16271290</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr"/>
       <c r="N135" s="3" t="inlineStr"/>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P135" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 72 in stock</t>
-        </is>
-      </c>
-      <c r="Q135" s="3" t="inlineStr"/>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q135" s="3" t="inlineStr">
+        <is>
+          <t>50 bands of 6 mm, both ends of each wire</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -16793,7 +16785,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-4-STK</t>
+          <t>RNF-100-3/16-6-STK</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -16804,7 +16796,7 @@
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
@@ -16841,7 +16833,7 @@
       </c>
       <c r="Q136" s="2" t="inlineStr">
         <is>
-          <t>50 bands of 6 mm, both ends of each wire</t>
+          <t>60 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16850,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-6-STK</t>
+          <t>RNF-100-3/16-9-STK</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
@@ -16869,7 +16861,7 @@
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
@@ -16906,7 +16898,7 @@
       </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
-          <t>60 bands of 6 mm, both ends of each wire</t>
+          <t>54 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -16923,7 +16915,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/16-9-STK</t>
+          <t>RNF-100-3/32-4-STK</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -16934,11 +16926,11 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -16949,7 +16941,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -16971,7 +16963,7 @@
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>54 bands of 6 mm, both ends of each wire</t>
+          <t>580 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -16988,7 +16980,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-4-STK</t>
+          <t>RNF-100-3/32-6-STK</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
@@ -16999,11 +16991,11 @@
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, YELLOW, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
@@ -17014,7 +17006,7 @@
         <v>0</v>
       </c>
       <c r="J139" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K139" s="3" t="n">
         <v>0</v>
@@ -17036,7 +17028,7 @@
       </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
-          <t>590 bands of 6 mm, both ends of each wire</t>
+          <t>850 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17045,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-6-STK</t>
+          <t>RNF-100-3/32-9-STK</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -17064,11 +17056,11 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, BLUE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -17079,7 +17071,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -17101,7 +17093,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>840 bands of 6 mm, both ends of each wire</t>
+          <t>420 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17118,18 +17110,14 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-9-STK</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, RNF-100, WHITE, 2:1, 2.4 MM EXPANDED ID, 1.2 MM RECOVERED ID, 1.2 M STICK</t>
+          <t>part number not confirmed yet: contact / plug (ALT-PLUG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
@@ -17137,7 +17125,7 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I141" s="3" t="n">
@@ -17146,27 +17134,19 @@
       <c r="J141" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L141" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="K141" s="3" t="inlineStr"/>
+      <c r="L141" s="3" t="inlineStr"/>
       <c r="M141" s="3" t="inlineStr"/>
       <c r="N141" s="3" t="inlineStr"/>
-      <c r="O141" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O141" s="3" t="inlineStr"/>
       <c r="P141" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>408 bands of 6 mm, both ends of each wire</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -17190,11 +17170,11 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ALT-PLUG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -17205,7 +17185,7 @@
         <v>0</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
@@ -17243,11 +17223,11 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
@@ -17258,7 +17238,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
       <c r="L143" s="3" t="inlineStr"/>
@@ -17296,11 +17276,11 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -17311,7 +17291,7 @@
         <v>0</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
@@ -17349,7 +17329,7 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
@@ -17402,7 +17382,7 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -17455,7 +17435,7 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
@@ -17508,7 +17488,7 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ECU-A) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
@@ -17565,7 +17545,7 @@
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17556,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
@@ -18992,7 +18972,7 @@
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
@@ -19045,11 +19025,11 @@
       <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -19060,7 +19040,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177" s="3" t="inlineStr"/>
       <c r="L177" s="3" t="inlineStr"/>
@@ -19098,7 +19078,7 @@
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
@@ -19151,11 +19131,11 @@
       <c r="E179" s="3" t="inlineStr"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
@@ -19166,7 +19146,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K179" s="3" t="inlineStr"/>
       <c r="L179" s="3" t="inlineStr"/>
@@ -19204,7 +19184,7 @@
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
@@ -19257,7 +19237,7 @@
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
@@ -19310,7 +19290,7 @@
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
@@ -19363,7 +19343,7 @@
       <c r="E183" s="3" t="inlineStr"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -19416,7 +19396,7 @@
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G184" s="2" t="n">
@@ -19469,7 +19449,7 @@
       <c r="E185" s="3" t="inlineStr"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G185" s="3" t="n">
@@ -19522,7 +19502,7 @@
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G186" s="2" t="n">
@@ -19575,7 +19555,7 @@
       <c r="E187" s="3" t="inlineStr"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G187" s="3" t="n">
@@ -19628,7 +19608,7 @@
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G188" s="2" t="n">
@@ -19681,22 +19661,22 @@
       <c r="E189" s="3" t="inlineStr"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
+          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="G189" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I189" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K189" s="3" t="inlineStr"/>
       <c r="L189" s="3" t="inlineStr"/>
@@ -19710,7 +19690,7 @@
       </c>
       <c r="Q189" s="3" t="inlineStr">
         <is>
-          <t>no maker document in the repo yet; never guessed</t>
+          <t>OPEN-ITEMS row 140</t>
         </is>
       </c>
     </row>
@@ -19727,18 +19707,22 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr"/>
+          <t>TMS-SCE-1/2-2.0-9</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -19749,23 +19733,27 @@
         <v>0</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K190" s="2" t="inlineStr"/>
-      <c r="L190" s="2" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M190" s="2" t="inlineStr"/>
       <c r="N190" s="2" t="inlineStr"/>
-      <c r="O190" s="2" t="inlineStr"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q190" s="2" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -19780,18 +19768,22 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr"/>
+          <t>TMS-SCE-3/16-2.0-9</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E191" s="3" t="inlineStr"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G191" s="3" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
@@ -19802,23 +19794,27 @@
         <v>0</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K191" s="3" t="inlineStr"/>
-      <c r="L191" s="3" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="K191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M191" s="3" t="inlineStr"/>
       <c r="N191" s="3" t="inlineStr"/>
-      <c r="O191" s="3" t="inlineStr"/>
+      <c r="O191" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P191" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q191" s="3" t="inlineStr">
-        <is>
-          <t>no maker document in the repo yet; never guessed</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -19833,45 +19829,53 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr"/>
+          <t>TMS-SCE-3/8-2.0-9</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I192" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K192" s="2" t="inlineStr"/>
-      <c r="L192" s="2" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="K192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M192" s="2" t="inlineStr"/>
       <c r="N192" s="2" t="inlineStr"/>
-      <c r="O192" s="2" t="inlineStr"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q192" s="2" t="inlineStr">
-        <is>
-          <t>OPEN-ITEMS row 140</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -19886,22 +19890,22 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Deutsch (TE Connectivity)</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr"/>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G193" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
@@ -19909,27 +19913,31 @@
         </is>
       </c>
       <c r="I193" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J193" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K193" s="3" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="L193" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" s="3" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="M193" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+        </is>
+      </c>
       <c r="N193" s="3" t="inlineStr"/>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>not priced (Dan)</t>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P193" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
         </is>
       </c>
       <c r="Q193" s="3" t="inlineStr"/>
@@ -19947,22 +19955,26 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E194" s="2" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -19973,24 +19985,28 @@
         <v>0</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M194" s="2" t="inlineStr"/>
+        <v>0.26</v>
+      </c>
+      <c r="M194" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+        </is>
+      </c>
       <c r="N194" s="2" t="inlineStr"/>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>not priced (Dan)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr"/>
@@ -20008,22 +20024,26 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>W2S</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G195" s="3" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
@@ -20034,24 +20054,28 @@
         <v>0</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="K195" s="3" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="L195" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" s="3" t="inlineStr"/>
+        <v>1.43</v>
+      </c>
+      <c r="M195" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-W2S.html</t>
+        </is>
+      </c>
       <c r="N195" s="3" t="inlineStr"/>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>not priced (Dan)</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P195" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="3" t="inlineStr"/>
@@ -20069,22 +20093,26 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>W12S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Deutsch (TE Connectivity)</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr"/>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G196" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
@@ -20092,31 +20120,31 @@
         </is>
       </c>
       <c r="I196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J196" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="K196" s="2" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>1.26</v>
+        <v>0.26</v>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr"/>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr"/>
@@ -20134,7 +20162,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>W2P</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -20149,7 +20177,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G197" s="3" t="n">
@@ -20167,25 +20195,25 @@
         <v>2</v>
       </c>
       <c r="K197" s="3" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="L197" s="3" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr"/>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P197" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
         </is>
       </c>
       <c r="Q197" s="3" t="inlineStr"/>
@@ -20203,7 +20231,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -20218,11 +20246,11 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -20233,28 +20261,28 @@
         <v>0</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>1.43</v>
+        <v>0.42</v>
       </c>
       <c r="M198" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr"/>
@@ -20272,12 +20300,12 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -20287,11 +20315,11 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G199" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
@@ -20302,28 +20330,28 @@
         <v>0</v>
       </c>
       <c r="J199" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K199" s="3" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="L199" s="3" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr"/>
       <c r="O199" s="3" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P199" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
         </is>
       </c>
       <c r="Q199" s="3" t="inlineStr"/>
@@ -20341,7 +20369,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>WM-4S</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -20356,11 +20384,11 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="G200" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -20371,28 +20399,28 @@
         <v>0</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="L200" s="2" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="M200" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr"/>
@@ -20410,12 +20438,12 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -20425,11 +20453,11 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="G201" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
@@ -20440,241 +20468,34 @@
         <v>0</v>
       </c>
       <c r="J201" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K201" s="3" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="L201" s="3" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="M201" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr"/>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P201" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
       <c r="Q201" s="3" t="inlineStr"/>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>W8S</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J202" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K202" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L202" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="M202" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
-        </is>
-      </c>
-      <c r="N202" s="2" t="inlineStr"/>
-      <c r="O202" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P202" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
-        </is>
-      </c>
-      <c r="Q202" s="2" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>WM-4S</t>
-        </is>
-      </c>
-      <c r="D203" s="3" t="inlineStr">
-        <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K203" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L203" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M203" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
-        </is>
-      </c>
-      <c r="N203" s="3" t="inlineStr"/>
-      <c r="O203" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P203" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
-        </is>
-      </c>
-      <c r="Q203" s="3" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K204" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L204" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M204" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
-        </is>
-      </c>
-      <c r="N204" s="2" t="inlineStr"/>
-      <c r="O204" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P204" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
-        </is>
-      </c>
-      <c r="Q204" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q204"/>
+  <autoFilter ref="A1:Q201"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -20691,8 +20512,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId20"/>
@@ -20701,7 +20522,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId29"/>
@@ -20716,17 +20537,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId54"/>
@@ -20747,48 +20568,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M95" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M117" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M122" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M115" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M116" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M119" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M120" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M121" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M123" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M124" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M125" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M126" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M127" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M128" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M129" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M135" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M202" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M203" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M204" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M130" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M131" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -20801,7 +20620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21104,7 +20923,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>3.9k 1/4W 1%</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -21764,7 +21583,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-50</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -21786,7 +21605,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-18-54</t>
+          <t>M22759/16-18-50</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -21808,7 +21627,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-06</t>
+          <t>M22759/16-18-54</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -21830,7 +21649,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-20-09</t>
+          <t>M22759/16-20-06</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -21852,7 +21671,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-20-39</t>
+          <t>M22759/16-20-09</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -21874,7 +21693,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-20-39</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -21884,7 +21703,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -22966,30 +22785,8 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D99"/>
+  <autoFilter ref="A1:D98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>103</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4787.24</v>
+        <v>4788.32</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>195</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5198.78</v>
+        <v>5199.86</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>23</v>
@@ -8127,7 +8127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="G125" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
@@ -16060,13 +16060,13 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>1.08</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>19.44</v>
+        <v>20.52</v>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>4.6 m in the master + 15% margin</t>
+          <t>4.9 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16963,7 +16963,7 @@
       </c>
       <c r="Q138" s="2" t="inlineStr">
         <is>
-          <t>580 bands of 6 mm, both ends of each wire</t>
+          <t>586 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17093,7 +17093,7 @@
       </c>
       <c r="Q140" s="2" t="inlineStr">
         <is>
-          <t>420 bands of 6 mm, both ends of each wire</t>
+          <t>432 bands of 6 mm, both ends of each wire</t>
         </is>
       </c>
     </row>
@@ -17488,11 +17488,11 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ECU-A) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr"/>
@@ -17541,11 +17541,11 @@
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
       <c r="L149" s="3" t="inlineStr"/>
@@ -17594,11 +17594,11 @@
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -17647,11 +17647,11 @@
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -17700,11 +17700,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
@@ -17753,11 +17753,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -17806,7 +17806,7 @@
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
@@ -17859,11 +17859,11 @@
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K155" s="3" t="inlineStr"/>
       <c r="L155" s="3" t="inlineStr"/>
@@ -17912,11 +17912,11 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr"/>
@@ -17965,11 +17965,11 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K157" s="3" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr"/>
@@ -18018,7 +18018,7 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
@@ -18071,7 +18071,7 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
@@ -18124,7 +18124,7 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
@@ -18177,7 +18177,7 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
@@ -18230,7 +18230,7 @@
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -18283,7 +18283,7 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
@@ -18336,7 +18336,7 @@
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
@@ -18389,7 +18389,7 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
@@ -18442,7 +18442,7 @@
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
@@ -18495,7 +18495,7 @@
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
@@ -18548,7 +18548,7 @@
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -18601,7 +18601,7 @@
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
@@ -18654,11 +18654,11 @@
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
@@ -18707,11 +18707,11 @@
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K171" s="3" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr"/>
@@ -18760,11 +18760,11 @@
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
@@ -18813,11 +18813,11 @@
       <c r="E173" s="3" t="inlineStr"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K173" s="3" t="inlineStr"/>
       <c r="L173" s="3" t="inlineStr"/>
@@ -18866,7 +18866,7 @@
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
@@ -18919,7 +18919,7 @@
       <c r="E175" s="3" t="inlineStr"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
@@ -18972,11 +18972,11 @@
       <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
@@ -19025,7 +19025,7 @@
       <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
@@ -19078,11 +19078,11 @@
       <c r="E178" s="2" t="inlineStr"/>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
@@ -19131,7 +19131,7 @@
       <c r="E179" s="3" t="inlineStr"/>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
@@ -19184,7 +19184,7 @@
       <c r="E180" s="2" t="inlineStr"/>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
@@ -19237,7 +19237,7 @@
       <c r="E181" s="3" t="inlineStr"/>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
@@ -19290,7 +19290,7 @@
       <c r="E182" s="2" t="inlineStr"/>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
@@ -19343,7 +19343,7 @@
       <c r="E183" s="3" t="inlineStr"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -19396,7 +19396,7 @@
       <c r="E184" s="2" t="inlineStr"/>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G184" s="2" t="n">
@@ -19449,7 +19449,7 @@
       <c r="E185" s="3" t="inlineStr"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G185" s="3" t="n">
@@ -19502,7 +19502,7 @@
       <c r="E186" s="2" t="inlineStr"/>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G186" s="2" t="n">
@@ -19555,7 +19555,7 @@
       <c r="E187" s="3" t="inlineStr"/>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G187" s="3" t="n">
@@ -19608,22 +19608,22 @@
       <c r="E188" s="2" t="inlineStr"/>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
+          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="G188" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I188" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="Q188" s="2" t="inlineStr">
         <is>
-          <t>no maker document in the repo yet; never guessed</t>
+          <t>OPEN-ITEMS row 140</t>
         </is>
       </c>
     </row>
@@ -19654,45 +19654,53 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr"/>
+          <t>TMS-SCE-1/2-2.0-9</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
       <c r="E189" s="3" t="inlineStr"/>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G189" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I189" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J189" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K189" s="3" t="inlineStr"/>
-      <c r="L189" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="K189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="M189" s="3" t="inlineStr"/>
       <c r="N189" s="3" t="inlineStr"/>
-      <c r="O189" s="3" t="inlineStr"/>
+      <c r="O189" s="3" t="inlineStr">
+        <is>
+          <t>not priced (Dan)</t>
+        </is>
+      </c>
       <c r="P189" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q189" s="3" t="inlineStr">
-        <is>
-          <t>OPEN-ITEMS row 140</t>
-        </is>
-      </c>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+        </is>
+      </c>
+      <c r="Q189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -19707,7 +19715,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -19718,11 +19726,11 @@
       <c r="E190" s="2" t="inlineStr"/>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G190" s="2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
@@ -19733,7 +19741,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>0</v>
@@ -19768,7 +19776,7 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
@@ -19779,11 +19787,11 @@
       <c r="E191" s="3" t="inlineStr"/>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G191" s="3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
@@ -19794,7 +19802,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K191" s="3" t="n">
         <v>0</v>
@@ -19829,22 +19837,22 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Deutsch (TE Connectivity)</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr"/>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G192" s="2" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
@@ -19852,27 +19860,31 @@
         </is>
       </c>
       <c r="I192" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="L192" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" s="2" t="inlineStr"/>
+        <v>1.26</v>
+      </c>
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+        </is>
+      </c>
       <c r="N192" s="2" t="inlineStr"/>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>not priced (Dan)</t>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr"/>
@@ -19890,22 +19902,26 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>W12S</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>Deutsch (TE Connectivity)</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G193" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
@@ -19913,31 +19929,31 @@
         </is>
       </c>
       <c r="I193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J193" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="K193" s="3" t="n">
-        <v>0.42</v>
+        <v>0.13</v>
       </c>
       <c r="L193" s="3" t="n">
-        <v>1.26</v>
+        <v>0.26</v>
       </c>
       <c r="M193" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
         </is>
       </c>
       <c r="N193" s="3" t="inlineStr"/>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P193" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="3" t="inlineStr"/>
@@ -19955,7 +19971,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>W2P</t>
+          <t>W2S</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -19970,11 +19986,11 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G194" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
@@ -19985,28 +20001,28 @@
         <v>0</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0.13</v>
       </c>
       <c r="L194" s="2" t="n">
-        <v>0.26</v>
+        <v>1.43</v>
       </c>
       <c r="M194" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
+          <t>https://www.te.com/en/product-W2S.html</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr"/>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr"/>
@@ -20024,12 +20040,12 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -20039,11 +20055,11 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G195" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
@@ -20054,17 +20070,17 @@
         <v>0</v>
       </c>
       <c r="J195" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K195" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="L195" s="3" t="n">
-        <v>1.43</v>
+        <v>0.26</v>
       </c>
       <c r="M195" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N195" s="3" t="inlineStr"/>
@@ -20075,7 +20091,7 @@
       </c>
       <c r="P195" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q195" s="3" t="inlineStr"/>
@@ -20093,12 +20109,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -20108,7 +20124,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G196" s="2" t="n">
@@ -20126,25 +20142,25 @@
         <v>2</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="L196" s="2" t="n">
-        <v>0.26</v>
+        <v>0.4</v>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr"/>
       <c r="O196" s="2" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr"/>
@@ -20162,7 +20178,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
@@ -20177,7 +20193,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G197" s="3" t="n">
@@ -20195,14 +20211,14 @@
         <v>2</v>
       </c>
       <c r="K197" s="3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="L197" s="3" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="M197" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
         </is>
       </c>
       <c r="N197" s="3" t="inlineStr"/>
@@ -20213,7 +20229,7 @@
       </c>
       <c r="P197" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
         </is>
       </c>
       <c r="Q197" s="3" t="inlineStr"/>
@@ -20231,7 +20247,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -20246,11 +20262,11 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -20261,28 +20277,28 @@
         <v>0</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="L198" s="2" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="M198" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr"/>
@@ -20300,7 +20316,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>WM-4S</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
@@ -20315,7 +20331,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
         </is>
       </c>
       <c r="G199" s="3" t="n">
@@ -20333,14 +20349,14 @@
         <v>1</v>
       </c>
       <c r="K199" s="3" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="L199" s="3" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="M199" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
         </is>
       </c>
       <c r="N199" s="3" t="inlineStr"/>
@@ -20351,7 +20367,7 @@
       </c>
       <c r="P199" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
         </is>
       </c>
       <c r="Q199" s="3" t="inlineStr"/>
@@ -20369,12 +20385,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>WM-6S</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -20384,7 +20400,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
         </is>
       </c>
       <c r="G200" s="2" t="n">
@@ -20402,14 +20418,14 @@
         <v>1</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="L200" s="2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="M200" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr"/>
@@ -20420,82 +20436,13 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr"/>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B201" s="3" t="inlineStr">
-        <is>
-          <t>All harnesses (master wire list)</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="inlineStr">
-        <is>
-          <t>WM-6S</t>
-        </is>
-      </c>
-      <c r="D201" s="3" t="inlineStr">
-        <is>
-          <t>Deutsch</t>
-        </is>
-      </c>
-      <c r="E201" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>ea</t>
-        </is>
-      </c>
-      <c r="I201" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K201" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L201" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="M201" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
-        </is>
-      </c>
-      <c r="N201" s="3" t="inlineStr"/>
-      <c r="O201" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
-        </is>
-      </c>
-      <c r="P201" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key API 2026-10-20: 2478 in stock</t>
-        </is>
-      </c>
-      <c r="Q201" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q201"/>
+  <autoFilter ref="A1:Q200"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -20599,15 +20546,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M132" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M133" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M134" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M201" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M192" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M193" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M194" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M195" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M196" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M197" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M198" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M199" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M200" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -20620,7 +20567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22763,30 +22710,8 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Wire harness</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D98"/>
+  <autoFilter ref="A1:D97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="To do" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To do" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>411.54</v>
+        <v>437.86</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -562,19 +562,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5186.23</v>
+        <v>5212.55</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q115"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6169,22 +6169,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Accu HHTPS-M5-8-40-BR-NI</t>
+          <t>Bopaodao B09Z7NBLDK</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Accu</t>
+          <t>Bopaodao (Amazon)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Brass hex standoff M5 female-female, 8 AF, 40 mm (ONE part number for all 14): Threaded hexagon spacer, female-female M5, 8 AF, 40 mm, nickel-plated brass, thread depth 10 mm each end</t>
+          <t>Output C-straps 3 x 15, tinned: 14 blanks 63.9 mm (drawing ST185-FB-117): Tinned copper bus bar 3 x 15 x 1000 mm C110: ONE bar makes all 14 straps (923 mm with 2 mm saw kerf, 77 spare)</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -6195,23 +6195,23 @@
         <v>0</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.6</v>
+        <v>51.99</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>8.4</v>
+        <v>51.99</v>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>https://accu-components.com/us/threaded-standoffs/464940-HHTPS-M5-8-40-BR-NI</t>
+          <t>https://www.amazon.com/dp/B09Z7NBLDK</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>seen</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -6234,22 +6234,22 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Bopaodao B09Z7NBLDK</t>
+          <t>EFC 10S00056</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Bopaodao (Amazon)</t>
+          <t>EFC International</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Output pads 15 x 3 x 17.5 mm, tinned (14 here + 1 in BATTRELAY): Tinned copper bus bar 3 x 15 x 1000 mm C110: ONE bar makes all 15 pads (290 mm with kerf)</t>
+          <t>Compression limiter, feet (4): Knurled solid compression limiter, M6, ID 6.80, OD 9.8, L 6 mm, zinc-plated steel</t>
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
@@ -6260,23 +6260,23 @@
         <v>0</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>51.99</v>
+        <v>0.3</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>51.99</v>
+        <v>1.5</v>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B09Z7NBLDK</t>
+          <t>https://efc-intl.com/compare/metal-compression-limiters/standard-solid-knurled-compression-limiters</t>
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>seen</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P87" s="3" t="inlineStr">
@@ -6299,22 +6299,22 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>EFC 10S00056</t>
+          <t>Klauke 2R5</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>EFC International</t>
+          <t>Klauke</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Compression limiter, feet (4): Knurled solid compression limiter, M6, ID 6.80, OD 9.8, L 6 mm, zinc-plated steel</t>
+          <t>Tubular lug 10 mm2, M5 hole (8-10 AWG): Tinned copper tubular ring lug, 10 mm2, M5, hole 5.3; b 12, l 22</t>
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -6325,17 +6325,17 @@
         <v>0</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="M88" s="4" t="inlineStr">
         <is>
-          <t>https://efc-intl.com/compare/metal-compression-limiters/standard-solid-knurled-compression-limiters</t>
+          <t>https://www.buerklin.com/en/p/klauke/cable-lugs/2r5/07F2065/</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Klauke 2R5</t>
+          <t>Klauke 3R5MS</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -6375,11 +6375,11 @@
       <c r="E89" s="3" t="inlineStr"/>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Tubular lug 10 mm2, M5 hole (8-10 AWG): Tinned copper tubular ring lug, 10 mm2, M5, hole 5.3; b 12, l 22</t>
+          <t>Tubular lug 16 mm2, M5 hole (6 AWG): Tinned copper tubular ring lug with inspection hole, 16 mm2, M5, hole 5.5; b 13, l 26</t>
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
@@ -6390,17 +6390,17 @@
         <v>0</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="L89" s="3" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
-          <t>https://www.buerklin.com/en/p/klauke/cable-lugs/2r5/07F2065/</t>
+          <t>https://buerklin.com/en/p/klauke/cable-lugs/3r5ms/07F9752</t>
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr"/>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Klauke 3R5MS</t>
+          <t>Klauke 6R8</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -6440,11 +6440,11 @@
       <c r="E90" s="2" t="inlineStr"/>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Tubular lug 16 mm2, M5 hole (6 AWG): Tinned copper tubular ring lug with inspection hole, 16 mm2, M5, hole 5.5; b 13, l 26</t>
+          <t>Tubular lug 50 mm2, M8 hole (the 6 1/0 bus cables): Tinned copper tubular ring lug, 50 mm2, M8, hole 8.4; b 20, l 47</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -6455,17 +6455,17 @@
         <v>0</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2.2</v>
+        <v>18.2</v>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>https://buerklin.com/en/p/klauke/cable-lugs/3r5ms/07F9752</t>
+          <t>https://www.buerklin.com/en/p/klauke/cable-lugs/6r8/07F2081/</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
@@ -6494,22 +6494,22 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Klauke 6R8</t>
+          <t>MECCANIXITY B0CGJBRNJX</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Klauke</t>
+          <t>MECCANIXITY (Amazon)</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Tubular lug 50 mm2, M8 hole (1/0 input): Tinned copper tubular ring lug, 50 mm2, M8, hole 8.4; b 20, l 47</t>
+          <t>POS bus bar 25.4 x 6.35 x 226 mm + NEG bus bar 25.4 x 6.35 x 105 mm, tinned: 12 in x 1 in x 1/4 in tinned copper flat bar: bar 1 = POS bar (226 mm) + battery block bar (36.5 mm); bar 2 = NEG bar (105 mm), 195 mm spare</t>
         </is>
       </c>
       <c r="G91" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
@@ -6520,23 +6520,23 @@
         <v>0</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>2.6</v>
+        <v>26.19</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>2.6</v>
+        <v>52.38</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>https://www.buerklin.com/en/p/klauke/cable-lugs/6r8/07F2081/</t>
+          <t>https://www.amazon.com/dp/B0CGJBRNJX</t>
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr"/>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>seen</t>
         </is>
       </c>
       <c r="P91" s="3" t="inlineStr">
@@ -6559,22 +6559,22 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>MECCANIXITY B0CGJBRNJX</t>
+          <t>PEM FHS-M5-12</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>MECCANIXITY (Amazon)</t>
+          <t>PennEngineering (PEM)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Power bar 25.4 x 6.35 x 148 mm, tinned: 12 in x 1 in x 1/4 in tinned copper flat bar: ONE bar makes the POWER bar (148 mm) and the battery block bar (36.5 mm)</t>
+          <t>Flush-head self-clinching stud M5 x 12, stainless, pressed into each strap's lug end (lug, flange nut on it): Self-clinching flush-head stud M5 x 12, type FHS (400-series stainless), mounting hole 5.0 +0.08, head 6.5 flush, min hole centre to edge 7.2, for sheet HRB 70 / HB 125 or less</t>
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
@@ -6585,28 +6585,16 @@
         <v>0</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="M92" s="4" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0CGJBRNJX</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>seen</t>
-        </is>
-      </c>
+      <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr"/>
@@ -6635,7 +6623,7 @@
       <c r="E93" s="3" t="inlineStr"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Power Base: Deck on four angular legs, open underneath; PA12</t>
+          <t>Power Base (with the bus zone): Deck on four angular legs, solid block under the deck plate with only the needed cuts (R127), 62 mm bus zone at the rear, printed barrier wall NEG / POS; PA12</t>
         </is>
       </c>
       <c r="G93" s="3" t="n">
@@ -6696,7 +6684,7 @@
       <c r="E94" s="2" t="inlineStr"/>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Power Cover: Snap-on cover, etched labels, vent slots; PA12</t>
+          <t>Power Cover: Snap-on cover, etched labels (AMI, relays, bus terminals), vent slots; PA12</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
@@ -6746,7 +6734,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Power_Pan_PA12_printed.stl + .step (PA12)</t>
+          <t>Power_NutHolder_PA12_printed.stl + .step (PA12)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -6757,11 +6745,11 @@
       <c r="E95" s="3" t="inlineStr"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Power Pan (belly pan): Snap-on belly pan, 4 integral tongues (no separate clips); PA12</t>
+          <t>Top-nut holder inside each C-strap (N37 C1): Column between the strap legs with a hex pocket for the DIN 934 nut; drops through the well with the strap</t>
         </is>
       </c>
       <c r="G95" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
@@ -6772,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K95" s="3" t="n">
         <v>0</v>
@@ -6807,7 +6795,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Power_Retainer_R1_PA12_printed.stl + .step (PA12)</t>
+          <t>Power_Pan_PA12_printed.stl + .step (PA12)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -6818,7 +6806,7 @@
       <c r="E96" s="2" t="inlineStr"/>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Retainer clip under the heater relay R1 (R123 B): Plate (2.0) with a hole per R1 wire and two barbed legs that snap into the cavity collar: stops the 62998-2 (no lance made for 8 AWG on a 6.3 blade) and the other R1 terminals backing out</t>
+          <t>Power Pan (belly pan): Snap-on belly pan, 4 integral tongues (no separate clips); PA12</t>
         </is>
       </c>
       <c r="G96" s="2" t="n">
@@ -6868,18 +6856,18 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-1/4-0-STK</t>
+          <t>Power_Retainer_R1_PA12_printed.stl + .step (PA12)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>print (your PA12 powder-bed printer)</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Insulation build-up sleeve 1/4, 2 ends x 15 mm: RNF-100 heat shrink 2:1, black, 4 ft stick: one piece under the insulation crimp of each thin-wall end</t>
+          <t>Retainer clip under the heater relay R1 (R123 B): Plate (2.0) with a hole per R1 wire and two barbed legs that snap into the cavity collar: stops the 62998-2 (no lance made for 8 AWG on a 6.3 blade) and the other R1 terminals backing out</t>
         </is>
       </c>
       <c r="G97" s="3" t="n">
@@ -6897,25 +6885,21 @@
         <v>1</v>
       </c>
       <c r="K97" s="3" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="M97" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-4-0-STK/26583229</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr"/>
       <c r="N97" s="3" t="inlineStr"/>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bag), 2026-10-20</t>
+          <t>made at work (Dan, R210)</t>
         </is>
       </c>
       <c r="P97" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>printed on Dan's PA12 printer (R82: no buy link)</t>
         </is>
       </c>
       <c r="Q97" s="3" t="inlineStr"/>
@@ -6933,7 +6917,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>RNF-100-1/8-0-STK</t>
+          <t>RNF-100-1/4-0-STK</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -6944,7 +6928,7 @@
       <c r="E98" s="2" t="inlineStr"/>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Insulation build-up sleeve 1/8, 15 ends x 15 mm: RNF-100 heat shrink 2:1, black, 4 ft stick: one piece under the insulation crimp of each thin-wall end</t>
+          <t>Insulation build-up sleeve 1/4, 2 ends x 15 mm: RNF-100 heat shrink 2:1, black, 4 ft stick: one piece under the insulation crimp of each thin-wall end</t>
         </is>
       </c>
       <c r="G98" s="2" t="n">
@@ -6962,20 +6946,20 @@
         <v>1</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>3.81</v>
+        <v>3.29</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>3.81</v>
+        <v>3.29</v>
       </c>
       <c r="M98" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-8-0-STK/26583058</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-4-0-STK/26583229</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bag), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Bag), 2026-10-20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -6998,7 +6982,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>RNF-100-3/32-0-STK</t>
+          <t>RNF-100-1/8-0-STK</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -7009,7 +6993,7 @@
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Insulation build-up sleeve 3/32, 12 ends x 15 mm: RNF-100 heat shrink 2:1, black, 4 ft stick: one piece under the insulation crimp of each thin-wall end</t>
+          <t>Insulation build-up sleeve 1/8, 15 ends x 15 mm: RNF-100 heat shrink 2:1, black, 4 ft stick: one piece under the insulation crimp of each thin-wall end</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
@@ -7027,14 +7011,14 @@
         <v>1</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>1.91</v>
+        <v>3.81</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>1.91</v>
+        <v>3.81</v>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-3-32-0-STK/26583372</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-1-8-0-STK/26583058</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr"/>
@@ -7045,7 +7029,7 @@
       </c>
       <c r="P99" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 1599 in stock</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q99" s="3" t="inlineStr"/>
@@ -7063,22 +7047,22 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>RS 190-276</t>
+          <t>RNF-100-3/32-0-STK</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>RS PRO</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Hex bolt M8 x 25 (1/0 input stud): RS PRO stainless hex bolt M8 x 25, DIN 933 (grade not stated on the listing)</t>
+          <t>Insulation build-up sleeve 3/32, 12 ends x 15 mm: RNF-100 heat shrink 2:1, black, 4 ft stick: one piece under the insulation crimp of each thin-wall end</t>
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
@@ -7089,28 +7073,28 @@
         <v>0</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.3</v>
+        <v>1.91</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0.6</v>
+        <v>1.91</v>
       </c>
       <c r="M100" s="4" t="inlineStr">
         <is>
-          <t>https://ph.rs-online.com/web/p/hex-bolts/0190276</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-raychem-cable-protection/RNF-100-3-32-0-STK/26583372</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>Digi-Key qty 2 (Bag), 2026-10-20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>Digi-Key API 2026-10-20: 1599 in stock</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr"/>
@@ -7128,7 +7112,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>RS 263-2205</t>
+          <t>RS 190-276</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -7139,11 +7123,11 @@
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Hex bolt M5 x 16 (AMI input stud on the bar, head captured): RS PRO stainless hex bolt M5 x 16, DIN 933 (grade not stated on the listing)</t>
+          <t>Hex bolt M8 x 25 (bus studs: 3 POS + 5 NEG, head captured): RS PRO stainless hex bolt M8 x 25, DIN 933 (grade not stated on the listing)</t>
         </is>
       </c>
       <c r="G101" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
@@ -7154,17 +7138,17 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>1.92</v>
+        <v>2.7</v>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>https://ph.rs-online.com/web/p/hex-bolts/2632205</t>
+          <t>https://ph.rs-online.com/web/p/hex-bolts/0190276</t>
         </is>
       </c>
       <c r="N101" s="3" t="inlineStr"/>
@@ -7193,7 +7177,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>RS 264-6432</t>
+          <t>RS 263-2205</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -7204,11 +7188,11 @@
       <c r="E102" s="2" t="inlineStr"/>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Keps nut M5 (AMI input + output ears, 2 per position): RS PRO A2/304 stainless serrated flange hex nut M5, DIN 6923</t>
+          <t>Hex bolt M5 x 16 (AMI input stud on the bar, head captured): RS PRO stainless hex bolt M5 x 16, DIN 933 (grade not stated on the listing)</t>
         </is>
       </c>
       <c r="G102" s="2" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
@@ -7219,17 +7203,17 @@
         <v>0</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>https://se.rs-online.com/web/p/products/2646432</t>
+          <t>https://ph.rs-online.com/web/p/hex-bolts/2632205</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr"/>
@@ -7258,7 +7242,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>RS 287-3921</t>
+          <t>RS 264-6432</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
@@ -7269,11 +7253,11 @@
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Hex bolt M5 x 10 (lug under each standoff, IN and OUT rows): RS PRO A2/304 stainless hex bolt M5 x 10, DIN 933</t>
+          <t>Keps (flange) nut M5: AMI input ear on the bar stud + the lug on each strap's FHS stud (2 per position): RS PRO A2/304 stainless serrated flange hex nut M5, DIN 6923</t>
         </is>
       </c>
       <c r="G103" s="3" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
@@ -7284,17 +7268,17 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>https://th.rs-online.com/web/p/hex-bolts/2873921</t>
+          <t>https://se.rs-online.com/web/p/products/2646432</t>
         </is>
       </c>
       <c r="N103" s="3" t="inlineStr"/>
@@ -7323,7 +7307,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>RS 530-769</t>
+          <t>RS 287-3921</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -7334,11 +7318,11 @@
       <c r="E104" s="2" t="inlineStr"/>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Hex nut M8 (1/0 input stud): RS PRO A2/304 stainless hex nut M8, DIN 934</t>
+          <t>Hex bolt M5 x 10 (AMI output ear down through the strap into the DIN 934 top nut, every strap): RS PRO A2/304 stainless hex bolt M5 x 10, DIN 933</t>
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
@@ -7349,17 +7333,17 @@
         <v>0</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0.16</v>
+        <v>1.6</v>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>https://hkcn.rs-online.com/web/p/products/530769</t>
+          <t>https://th.rs-online.com/web/p/hex-bolts/2873921</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr"/>
@@ -7388,7 +7372,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>RS 797-6068</t>
+          <t>RS 527-268</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -7399,11 +7383,11 @@
       <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Plain washer M8 (1/0 input stud): RS PRO stainless plain washer M8, DIN 125A</t>
+          <t>Hex nut M5 DIN 934, top of every strap, held in its printed holder (the AMI ear bolt screws into it): RS PRO plain stainless hex nut M5, DIN 934, 4 mm high (grade not stated on the listing)</t>
         </is>
       </c>
       <c r="G105" s="3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
@@ -7414,28 +7398,16 @@
         <v>0</v>
       </c>
       <c r="J105" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K105" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L105" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M105" s="5" t="inlineStr">
-        <is>
-          <t>https://th.rs-online.com/web/p/washers/7976068</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="K105" s="3" t="inlineStr"/>
+      <c r="L105" s="3" t="inlineStr"/>
+      <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="inlineStr"/>
-      <c r="O105" s="3" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
+      <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="3" t="inlineStr">
         <is>
-          <t>from cad/fusebox parts list (R82 checked)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q105" s="3" t="inlineStr"/>
@@ -7453,22 +7425,22 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>SSCF-M3-10-A4</t>
+          <t>RS 530-769</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Accu</t>
+          <t>RS PRO</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>OPTIONAL cover backup: M3 x 10 cap screw, one beside each cover catch: Socket head cap screw M3 x 10, DIN 912 / ISO 4762, A4 (316) stainless</t>
+          <t>Hex nut M8 (bus studs): RS PRO A2/304 stainless hex nut M8, DIN 934</t>
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
@@ -7479,17 +7451,17 @@
         <v>0</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.5</v>
+        <v>0.08</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>2.5</v>
+        <v>0.72</v>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>https://accu-components.com/us/metric-cap-head-screws/3975-SSCF-M3-10-A4</t>
+          <t>https://hkcn.rs-online.com/web/p/products/530769</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr"/>
@@ -7518,22 +7490,22 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>bolts.co.uk SSPMCA205020</t>
+          <t>RS 797-6068</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Bolts.co.uk</t>
+          <t>RS PRO</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Set screw M5 x 20 (stud on each pad standoff): Socket set screw M5 x 20, plain cup point, DIN 916, A2 stainless (pack of 25)</t>
+          <t>Plain washer M8 (bus studs): RS PRO stainless plain washer M8, DIN 125A</t>
         </is>
       </c>
       <c r="G107" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
@@ -7544,23 +7516,23 @@
         <v>0</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0.63</v>
+        <v>0.05</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>10.08</v>
+        <v>0.45</v>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
-          <t>https://bolts.co.uk/m5-x-20mm-socket-set-screw-plain-cup-point-pcp-din-916-a2-stainless-steel-pack-of-25-p-SSPMCA205020</t>
+          <t>https://th.rs-online.com/web/p/washers/7976068</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr"/>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>seen</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P107" s="3" t="inlineStr">
@@ -7578,27 +7550,27 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>VRC enclosure (2 per car)</t>
+          <t>POWER box</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>50M060100P030</t>
+          <t>SSCF-M3-10-A4</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Essentra</t>
+          <t>Accu</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>screw_tab: Tab screw, nylon, M6 (box mounts on nylon)</t>
+          <t>OPTIONAL cover backup: M3 x 10 cap screw, one beside each cover catch: Socket head cap screw M3 x 10, DIN 912 / ISO 4762, A4 (316) stainless</t>
         </is>
       </c>
       <c r="G108" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
@@ -7609,28 +7581,28 @@
         <v>0</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/essentra-components/50M060100P030/11641017</t>
+          <t>https://accu-components.com/us/metric-cap-head-screws/3975-SSCF-M3-10-A4</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+          <t>est</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 1581 in stock</t>
+          <t>from cad/fusebox parts list (R82 checked)</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr"/>
@@ -7648,18 +7620,18 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>ISO 10642 M3 x 12 A2</t>
+          <t>50M060100P030</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>Essentra</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>screw_lid: Lid screw, countersunk socket head</t>
+          <t>screw_tab: Tab screw, nylon, M6 (box mounts on nylon)</t>
         </is>
       </c>
       <c r="G109" s="3" t="n">
@@ -7676,14 +7648,26 @@
       <c r="J109" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="K109" s="3" t="inlineStr"/>
-      <c r="L109" s="3" t="inlineStr"/>
-      <c r="M109" s="3" t="inlineStr"/>
+      <c r="K109" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/essentra-components/50M060100P030/11641017</t>
+        </is>
+      </c>
       <c r="N109" s="3" t="inlineStr"/>
-      <c r="O109" s="3" t="inlineStr"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P109" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 1581 in stock</t>
         </is>
       </c>
       <c r="Q109" s="3" t="inlineStr"/>
@@ -7701,22 +7685,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>ISO 10642 M3 x 12 A2</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>CNLINKO</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>in: LP-16 male panel socket IN (rear nut), mates the IN cable plug LP-16-J05PE-02-001</t>
+          <t>screw_lid: Lid screw, countersunk socket head</t>
         </is>
       </c>
       <c r="G110" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
@@ -7727,7 +7711,7 @@
         <v>0</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
@@ -7765,7 +7749,7 @@
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>out: LP-16 male panel socket OUT (rear nut), mates the OUT cable plug LP-16-J05PE-02-001</t>
+          <t>in: LP-16 male panel socket IN (rear nut), mates the IN cable plug LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="G111" s="3" t="n">
@@ -7807,22 +7791,22 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Lemu 2990806014</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Lemu</t>
+          <t>CNLINKO</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>screw_holder: Holder-to-floor screw, M6 x 14 ISO 10642 / DIN 7991 A2 countersunk, TX30 (into the 2 floor bosses, tapped M6x1.0)</t>
+          <t>out: LP-16 male panel socket OUT (rear nut), mates the OUT cable plug LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="G112" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -7833,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
@@ -7860,22 +7844,22 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>N0674-70 2-039</t>
+          <t>Lemu 2990806014</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Lemu</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>oring: Lid face-seal O-ring, AS568-039 (69.57 ID x 1.78), NBR 70</t>
+          <t>screw_holder: Holder-to-floor screw, M6 x 14 ISO 10642 / DIN 7991 A2 countersunk, TX30 (into the 2 floor bosses, tapped M6x1.0)</t>
         </is>
       </c>
       <c r="G113" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
@@ -7886,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
       <c r="L113" s="3" t="inlineStr"/>
@@ -7913,18 +7897,18 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ST185-VRC-Enclosure</t>
+          <t>N0674-70 2-039</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Custom (machined, 6061-T6)</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>box: Custom machined enclosure: body + lid, O-ring face seal, 4 slotted mounting tabs</t>
+          <t>oring: Lid face-seal O-ring, AS568-039 (69.57 ID x 1.78), NBR 70</t>
         </is>
       </c>
       <c r="G114" s="2" t="n">
@@ -7941,22 +7925,14 @@
       <c r="J114" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
       <c r="M114" s="2" t="inlineStr"/>
       <c r="N114" s="2" t="inlineStr"/>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>made at work (Dan, R210)</t>
-        </is>
-      </c>
+      <c r="O114" s="2" t="inlineStr"/>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>machined to the drawing (R210: made at work, no buy link)</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr"/>
@@ -7974,18 +7950,18 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>ST185_VRC_board_holder_PA12</t>
+          <t>ST185-VRC-Enclosure</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>3D printed</t>
+          <t>Custom (machined, 6061-T6)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>holder: Board holder: one extruded PA12 block, board flush in a pocket held by 4 snap tabs (wires soldered on the board top)</t>
+          <t>box: Custom machined enclosure: body + lid, O-ring face seal, 4 slotted mounting tabs</t>
         </is>
       </c>
       <c r="G115" s="3" t="n">
@@ -8017,13 +7993,74 @@
       </c>
       <c r="P115" s="3" t="inlineStr">
         <is>
+          <t>machined to the drawing (R210: made at work, no buy link)</t>
+        </is>
+      </c>
+      <c r="Q115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical assemblies</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>VRC enclosure (2 per car)</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>ST185_VRC_board_holder_PA12</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>3D printed</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>holder: Board holder: one extruded PA12 block, board flush in a pocket held by 4 snap tabs (wires soldered on the board top)</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>made at work (Dan, R210)</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
           <t>printed on Dan's PA12 printer (R82: no buy link)</t>
         </is>
       </c>
-      <c r="Q115" s="3" t="inlineStr"/>
+      <c r="Q116" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q115"/>
+  <autoFilter ref="A1:Q116"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -8102,19 +8139,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M90" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M98" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M99" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M100" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M101" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -19474,7 +19509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19645,7 +19680,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ISO 10642 M3 x 12 A2</t>
+          <t>PEM FHS-M5-12</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -19655,7 +19690,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19667,7 +19702,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>RS 527-268</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -19689,7 +19724,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LP-16-C05SX-02-101</t>
+          <t>ISO 10642 M3 x 12 A2</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -19699,7 +19734,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19711,7 +19746,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Lemu 2990806014</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -19733,7 +19768,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>N0674-70 2-039</t>
+          <t>LP-16-C05SX-02-101</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -19750,12 +19785,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Wire harness</t>
+          <t>Mechanical assemblies</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>1 928 403 874</t>
+          <t>Lemu 2990806014</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -19772,12 +19807,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Wire harness</t>
+          <t>Mechanical assemblies</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>N0674-70 2-039</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -19787,7 +19822,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19799,7 +19834,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>1 928 403 874</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -19821,17 +19856,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>2.2k 1/4W 1%</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>generic part: name a real PN (TE first, then an approved supplier); I propose one on your OK</t>
         </is>
       </c>
     </row>
@@ -19843,12 +19878,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -19865,7 +19900,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -19887,7 +19922,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -19909,17 +19944,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19931,17 +19966,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>90980-10942</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -19953,7 +19988,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -19975,7 +20010,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>90980-10942</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -19997,7 +20032,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>90980-11143</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -20019,7 +20054,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>90980-12068</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -20041,7 +20076,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -20051,7 +20086,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20063,7 +20098,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>90980-12068</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20073,7 +20108,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20085,7 +20120,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -20107,7 +20142,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20129,17 +20164,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20151,17 +20186,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20173,12 +20208,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -20195,17 +20230,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20252,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -20227,7 +20262,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20274,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -20261,7 +20296,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -20283,7 +20318,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -20305,7 +20340,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -20315,7 +20350,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -20327,7 +20362,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -20337,7 +20372,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21419,8 +21454,52 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D88"/>
+  <autoFilter ref="A1:D90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -11247,7 +11247,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>6 cable runs, 5.9 m + 15% margin</t>
+          <t>6 cable runs, 5.2 m + 15% margin</t>
         </is>
       </c>
     </row>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4774.69</v>
+        <v>4768.97</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5212.55</v>
+        <v>5206.83</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>24</v>
@@ -8162,7 +8162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q183"/>
+  <dimension ref="A1:Q186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -9340,13 +9340,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.24</v>
+        <v>0.32</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12110293</t>
+          <t>12191819</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, METRI-PACK 150.2, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -9481,14 +9481,14 @@
         <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.95</v>
+        <v>0.18</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.8</v>
+        <v>0.72</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12110293?variant=45536279953726</t>
+          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>13519047</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -9528,11 +9528,11 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -9543,17 +9543,17 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.18</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
+          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>13519047</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -9593,11 +9593,11 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -9608,17 +9608,17 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.95</v>
+        <v>3.15</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
+          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>15419715</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -9658,11 +9658,11 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -9673,17 +9673,17 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.15</v>
+        <v>4.36</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
+          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
@@ -9712,22 +9712,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>1N5822</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
+          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -9738,28 +9738,28 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4.36</v>
+        <v>0.71</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
+          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -9777,18 +9777,18 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1N5822</t>
+          <t>1k 1/4W</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
+          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
@@ -9806,25 +9806,25 @@
         <v>1</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
+          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1k 1/4W</t>
+          <t>2.2k 1/4W 1%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
+          <t>RESISTOR, FIXED, METAL FILM, 2.2 KOHM, 1 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -9870,26 +9870,14 @@
       <c r="J26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
-        </is>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
-        </is>
-      </c>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -9907,22 +9895,22 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 2.2 KOHM, 1 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -9930,19 +9918,29 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.41</v>
+      </c>
       <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -9960,7 +9958,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -9971,11 +9969,11 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -9983,29 +9981,29 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
+          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
+          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -10023,22 +10021,22 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3.9k 1/4W</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
+          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -10046,29 +10044,31 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
+          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -10086,22 +10086,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3.9k 1/4W</t>
+          <t>301A011-25-0</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 5 PCT, 1/4 W</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -10112,28 +10112,28 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.1</v>
+        <v>27.58</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.1</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
+          <t>Digi-Key API 2026-10-20: 236 in stock</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>301A011-25-0</t>
+          <t>301A022-25-0</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -10162,11 +10162,11 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -10177,28 +10177,28 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>27.58</v>
+        <v>40.77</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 236 in stock</t>
+          <t>Digi-Key API 2026-10-20: 151 in stock</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>301A022-25-0</t>
+          <t>301A028-25-0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -10245,14 +10245,14 @@
         <v>2</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>40.77</v>
+        <v>37.65</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>81.54000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 151 in stock</t>
+          <t>Digi-Key API 2026-10-20: 94 in stock</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>301A028-25-0</t>
+          <t>342A012-25-0</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -10292,11 +10292,11 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -10307,28 +10307,28 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>37.65</v>
+        <v>35.59</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>75.3</v>
+        <v>427.08</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 94 in stock</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>342A012-25-0</t>
+          <t>342A024-25-0</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -10357,11 +10357,11 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -10372,28 +10372,28 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>35.59</v>
+        <v>50.66</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>427.08</v>
+        <v>557.26</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>Digi-Key API 2026-10-20: 140 in stock</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>342A024-25-0</t>
+          <t>342A034-25-0</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -10422,11 +10422,11 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -10437,28 +10437,28 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>50.66</v>
+        <v>75.67</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>557.26</v>
+        <v>605.36</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 140 in stock</t>
+          <t>Digi-Key API 2026-10-20: 57 in stock</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>342A034-25-0</t>
+          <t>342A048-25-0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10487,11 +10487,11 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -10502,28 +10502,28 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>75.67</v>
+        <v>117.77</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>605.36</v>
+        <v>235.54</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 57 in stock</t>
+          <t>Digi-Key API 2026-10-20: 46 in stock</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>342A048-25-0</t>
+          <t>354404</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Lowdoller Motorsports</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR KIT, PRESSURE / MAP SENSOR, 3 PIN, DELPHI GT150 (PLUG, PINS, SEALS)</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -10567,28 +10567,20 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>117.77</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>235.54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
+          <t>https://lowdoller-motorsports.com/products/3-pin-connector-pins-and-grommets-for-pressure-sensor</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 46 in stock</t>
+          <t>maker page read 2026-10-25 (one ships with each Lowdoller sensor)</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -16067,11 +16059,11 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (CLNT-P) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -16082,7 +16074,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
@@ -16120,7 +16112,7 @@
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
@@ -16173,7 +16165,7 @@
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -16226,7 +16218,7 @@
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
@@ -16279,11 +16271,11 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -16294,7 +16286,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
@@ -16332,11 +16324,11 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -16347,7 +16339,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
@@ -16385,11 +16377,11 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -16400,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
@@ -16438,11 +16430,11 @@
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -16453,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" s="3" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr"/>
@@ -16491,11 +16483,11 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -16506,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
@@ -16544,11 +16536,11 @@
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -16559,7 +16551,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K133" s="3" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr"/>
@@ -16597,7 +16589,7 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
@@ -16650,11 +16642,11 @@
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -16665,7 +16657,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
@@ -16703,11 +16695,11 @@
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -16718,7 +16710,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
@@ -16756,11 +16748,11 @@
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
@@ -16771,7 +16763,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K137" s="3" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr"/>
@@ -16809,7 +16801,7 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
@@ -16862,7 +16854,7 @@
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
@@ -16915,7 +16907,7 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -16968,7 +16960,7 @@
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
@@ -17021,7 +17013,7 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
@@ -17074,7 +17066,7 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
@@ -17127,7 +17119,7 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
@@ -17180,7 +17172,7 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
@@ -17233,7 +17225,7 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CLNT-P) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -17286,7 +17278,7 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
@@ -17339,7 +17331,7 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
@@ -17392,7 +17384,7 @@
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
@@ -17445,11 +17437,11 @@
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -17460,7 +17452,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -17498,11 +17490,11 @@
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -17513,7 +17505,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -17551,11 +17543,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -17566,7 +17558,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
@@ -17604,11 +17596,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -17619,7 +17611,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -17657,11 +17649,11 @@
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -17672,7 +17664,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
@@ -17710,7 +17702,7 @@
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
@@ -17763,7 +17755,7 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
@@ -17816,11 +17808,11 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -17831,7 +17823,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K157" s="3" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr"/>
@@ -17869,11 +17861,11 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -17884,7 +17876,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
@@ -17922,11 +17914,11 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -17937,7 +17929,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K159" s="3" t="inlineStr"/>
       <c r="L159" s="3" t="inlineStr"/>
@@ -17975,11 +17967,11 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -17990,7 +17982,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr"/>
@@ -18028,7 +18020,7 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
@@ -18081,7 +18073,7 @@
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -18134,7 +18126,7 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
@@ -18187,7 +18179,7 @@
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
@@ -18240,7 +18232,7 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
@@ -18293,7 +18285,7 @@
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
@@ -18346,7 +18338,7 @@
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
@@ -18399,7 +18391,7 @@
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -18452,7 +18444,7 @@
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
@@ -18505,7 +18497,7 @@
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -18558,22 +18550,22 @@
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I171" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K171" s="3" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr"/>
@@ -18587,7 +18579,7 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>OPEN-ITEMS row 140</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -18604,22 +18596,18 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -18630,27 +18618,23 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr"/>
       <c r="N172" s="2" t="inlineStr"/>
-      <c r="O172" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O172" s="2" t="inlineStr"/>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q172" s="2" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>no maker document in the repo yet; never guessed</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -18665,53 +18649,45 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="K173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K173" s="3" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr"/>
       <c r="M173" s="3" t="inlineStr"/>
       <c r="N173" s="3" t="inlineStr"/>
-      <c r="O173" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q173" s="3" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="inlineStr">
+        <is>
+          <t>OPEN-ITEMS row 140</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -18726,7 +18702,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>TMS-SCE-1/2-2.0-9</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -18737,11 +18713,11 @@
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -18752,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>0</v>
@@ -18787,22 +18763,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>W12S</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Deutsch (TE Connectivity)</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -18810,31 +18786,27 @@
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K175" s="3" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="L175" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M175" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr"/>
       <c r="N175" s="3" t="inlineStr"/>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P175" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q175" s="3" t="inlineStr"/>
@@ -18852,26 +18824,22 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>W2P</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -18882,28 +18850,24 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M176" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr"/>
@@ -18921,26 +18885,22 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>Deutsch (TE Connectivity)</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -18948,31 +18908,31 @@
         </is>
       </c>
       <c r="I177" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K177" s="3" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="L177" s="3" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr"/>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P177" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
         </is>
       </c>
       <c r="Q177" s="3" t="inlineStr"/>
@@ -18990,12 +18950,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -19005,7 +18965,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
@@ -19030,18 +18990,18 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr"/>
@@ -19059,7 +19019,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>W2S</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -19074,11 +19034,11 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
@@ -19089,28 +19049,28 @@
         <v>0</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K179" s="3" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="L179" s="3" t="n">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
+          <t>https://www.te.com/en/product-W2S.html</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr"/>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P179" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="3" t="inlineStr"/>
@@ -19128,12 +19088,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -19143,7 +19103,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
@@ -19161,25 +19121,25 @@
         <v>2</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="L180" s="2" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr"/>
@@ -19197,7 +19157,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -19212,11 +19172,11 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
@@ -19227,28 +19187,28 @@
         <v>0</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" s="3" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="L181" s="3" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr"/>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P181" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
         </is>
       </c>
       <c r="Q181" s="3" t="inlineStr"/>
@@ -19266,7 +19226,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -19281,11 +19241,11 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -19296,28 +19256,28 @@
         <v>0</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr"/>
@@ -19335,12 +19295,12 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -19350,7 +19310,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -19368,14 +19328,14 @@
         <v>1</v>
       </c>
       <c r="K183" s="3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="L183" s="3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
         </is>
       </c>
       <c r="N183" s="3" t="inlineStr"/>
@@ -19386,13 +19346,196 @@
       </c>
       <c r="P183" s="3" t="inlineStr">
         <is>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>All harnesses (master wire list)</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>All harnesses (master wire list)</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>WM-6S</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M185" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr"/>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
           <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
-      <c r="Q183" s="3" t="inlineStr"/>
+      <c r="Q185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>All harnesses (master wire list)</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q183"/>
+  <autoFilter ref="A1:Q186"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -19418,7 +19561,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId28"/>
@@ -19488,15 +19631,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -19509,7 +19652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19878,12 +20021,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>354404</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>maker page read 2026-10-25 (one ships with each Lowdoller sensor)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -19900,12 +20043,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -19922,7 +20065,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -19944,7 +20087,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -19966,7 +20109,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -19988,17 +20131,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20153,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>90980-10942</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -20032,7 +20175,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>90980-10942</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -20054,7 +20197,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>90980-11143</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -20076,7 +20219,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -20098,7 +20241,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>90980-12068</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20120,7 +20263,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>90980-12068</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -20130,7 +20273,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20142,7 +20285,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20164,7 +20307,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -20186,7 +20329,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -20208,17 +20351,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20230,7 +20373,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -20252,12 +20395,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -20274,7 +20417,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -20284,7 +20427,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20296,7 +20439,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -20318,7 +20461,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -20340,7 +20483,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -20362,7 +20505,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -20384,7 +20527,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -20394,7 +20537,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21498,8 +21641,96 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D90"/>
+  <autoFilter ref="A1:D94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$183</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4774.69</v>
+        <v>4768.97</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5212.55</v>
+        <v>5206.83</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>24</v>
@@ -8162,7 +8162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q183"/>
+  <dimension ref="A1:Q186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -9340,13 +9340,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2.24</v>
+        <v>0.32</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12110293</t>
+          <t>12191819</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, METRI-PACK 150.2, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
@@ -9481,14 +9481,14 @@
         <v>4</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.95</v>
+        <v>0.18</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.8</v>
+        <v>0.72</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12110293?variant=45536279953726</t>
+          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>13519047</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -9528,11 +9528,11 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -9543,17 +9543,17 @@
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.18</v>
+        <v>0.95</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.72</v>
+        <v>0.95</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
+          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>13519047</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -9593,11 +9593,11 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -9608,17 +9608,17 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.95</v>
+        <v>0.45</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.95</v>
+        <v>3.15</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
+          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>15419715</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -9658,11 +9658,11 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -9673,17 +9673,17 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.15</v>
+        <v>4.36</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
+          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
@@ -9712,22 +9712,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>1N5822</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
+          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -9738,28 +9738,28 @@
         <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4.36</v>
+        <v>0.71</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
+          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -9777,18 +9777,18 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1N5822</t>
+          <t>1k 1/4W</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
+          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
@@ -9806,25 +9806,25 @@
         <v>1</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
+          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1k 1/4W</t>
+          <t>2.2k 1/4W 1%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
+          <t>RESISTOR, FIXED, METAL FILM, 2.2 KOHM, 1 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
@@ -9870,26 +9870,14 @@
       <c r="J26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
-        </is>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
-        </is>
-      </c>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -9907,22 +9895,22 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 2.2 KOHM, 1 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -9930,19 +9918,29 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.41</v>
+      </c>
       <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
+        </is>
+      </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -9960,7 +9958,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -9971,11 +9969,11 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -9983,29 +9981,29 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
+          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
+          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -10023,22 +10021,22 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>3.9k 1/4W</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
+          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -10046,29 +10044,31 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
+          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -10086,22 +10086,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>3.9k 1/4W</t>
+          <t>301A011-25-0</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 5 PCT, 1/4 W</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -10112,28 +10112,28 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.1</v>
+        <v>27.58</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.1</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
+          <t>Digi-Key API 2026-10-20: 236 in stock</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>301A011-25-0</t>
+          <t>301A022-25-0</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -10162,11 +10162,11 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -10177,28 +10177,28 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>27.58</v>
+        <v>40.77</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>82.73999999999999</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 236 in stock</t>
+          <t>Digi-Key API 2026-10-20: 151 in stock</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>301A022-25-0</t>
+          <t>301A028-25-0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
@@ -10245,14 +10245,14 @@
         <v>2</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>40.77</v>
+        <v>37.65</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>81.54000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 151 in stock</t>
+          <t>Digi-Key API 2026-10-20: 94 in stock</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>301A028-25-0</t>
+          <t>342A012-25-0</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -10292,11 +10292,11 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -10307,28 +10307,28 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>37.65</v>
+        <v>35.59</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>75.3</v>
+        <v>427.08</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 94 in stock</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>342A012-25-0</t>
+          <t>342A024-25-0</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -10357,11 +10357,11 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -10372,28 +10372,28 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>35.59</v>
+        <v>50.66</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>427.08</v>
+        <v>557.26</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>Digi-Key API 2026-10-20: 140 in stock</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>342A024-25-0</t>
+          <t>342A034-25-0</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -10422,11 +10422,11 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -10437,28 +10437,28 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>50.66</v>
+        <v>75.67</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>557.26</v>
+        <v>605.36</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 140 in stock</t>
+          <t>Digi-Key API 2026-10-20: 57 in stock</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>342A034-25-0</t>
+          <t>342A048-25-0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10487,11 +10487,11 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -10502,28 +10502,28 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>75.67</v>
+        <v>117.77</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>605.36</v>
+        <v>235.54</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 57 in stock</t>
+          <t>Digi-Key API 2026-10-20: 46 in stock</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -10541,22 +10541,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>342A048-25-0</t>
+          <t>354404</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Lowdoller Motorsports</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR KIT, PRESSURE / MAP SENSOR, 3 PIN, DELPHI GT150 (PLUG, PINS, SEALS)</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -10567,28 +10567,20 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>117.77</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>235.54</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="K37" s="3" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
+          <t>https://lowdoller-motorsports.com/products/3-pin-connector-pins-and-grommets-for-pressure-sensor</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 46 in stock</t>
+          <t>maker page read 2026-10-25 (one ships with each Lowdoller sensor)</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -11247,7 +11239,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -11258,7 +11250,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
@@ -11276,7 +11268,7 @@
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>6 cable runs, 5.9 m + 15% margin</t>
+          <t>6 cable runs, 5.2 m + 15% margin</t>
         </is>
       </c>
     </row>
@@ -16067,11 +16059,11 @@
       <c r="E124" s="2" t="inlineStr"/>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (CLNT-P) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
@@ -16082,7 +16074,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
@@ -16120,7 +16112,7 @@
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G125" s="3" t="n">
@@ -16173,7 +16165,7 @@
       <c r="E126" s="2" t="inlineStr"/>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G126" s="2" t="n">
@@ -16226,7 +16218,7 @@
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G127" s="3" t="n">
@@ -16279,11 +16271,11 @@
       <c r="E128" s="2" t="inlineStr"/>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (COIL-4) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G128" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
@@ -16294,7 +16286,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
@@ -16332,11 +16324,11 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ECU-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G129" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
@@ -16347,7 +16339,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
       <c r="L129" s="3" t="inlineStr"/>
@@ -16385,11 +16377,11 @@
       <c r="E130" s="2" t="inlineStr"/>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (ETB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G130" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
@@ -16400,7 +16392,7 @@
         <v>0</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
@@ -16438,11 +16430,11 @@
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G131" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
@@ -16453,7 +16445,7 @@
         <v>0</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" s="3" t="inlineStr"/>
       <c r="L131" s="3" t="inlineStr"/>
@@ -16491,11 +16483,11 @@
       <c r="E132" s="2" t="inlineStr"/>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G132" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -16506,7 +16498,7 @@
         <v>0</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
@@ -16544,11 +16536,11 @@
       <c r="E133" s="3" t="inlineStr"/>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KILL-SW) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
@@ -16559,7 +16551,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K133" s="3" t="inlineStr"/>
       <c r="L133" s="3" t="inlineStr"/>
@@ -16597,7 +16589,7 @@
       <c r="E134" s="2" t="inlineStr"/>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (KNOCK-1) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G134" s="2" t="n">
@@ -16650,11 +16642,11 @@
       <c r="E135" s="3" t="inlineStr"/>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-A) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G135" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
@@ -16665,7 +16657,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
       <c r="L135" s="3" t="inlineStr"/>
@@ -16703,11 +16695,11 @@
       <c r="E136" s="2" t="inlineStr"/>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -16718,7 +16710,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
@@ -16756,11 +16748,11 @@
       <c r="E137" s="3" t="inlineStr"/>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: contact / plug (MRS-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G137" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
@@ -16771,7 +16763,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K137" s="3" t="inlineStr"/>
       <c r="L137" s="3" t="inlineStr"/>
@@ -16809,7 +16801,7 @@
       <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-CHG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G138" s="2" t="n">
@@ -16862,7 +16854,7 @@
       <c r="E139" s="3" t="inlineStr"/>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-HB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G139" s="3" t="n">
@@ -16915,7 +16907,7 @@
       <c r="E140" s="2" t="inlineStr"/>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-OIL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G140" s="2" t="n">
@@ -16968,7 +16960,7 @@
       <c r="E141" s="3" t="inlineStr"/>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-PK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G141" s="3" t="n">
@@ -17021,7 +17013,7 @@
       <c r="E142" s="2" t="inlineStr"/>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G142" s="2" t="n">
@@ -17074,7 +17066,7 @@
       <c r="E143" s="3" t="inlineStr"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: diode (D-TR) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G143" s="3" t="n">
@@ -17127,7 +17119,7 @@
       <c r="E144" s="2" t="inlineStr"/>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (APS-PEDAL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G144" s="2" t="n">
@@ -17180,7 +17172,7 @@
       <c r="E145" s="3" t="inlineStr"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CAM) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G145" s="3" t="n">
@@ -17233,7 +17225,7 @@
       <c r="E146" s="2" t="inlineStr"/>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (CLNT-P) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G146" s="2" t="n">
@@ -17286,7 +17278,7 @@
       <c r="E147" s="3" t="inlineStr"/>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (FUEL-PUMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G147" s="3" t="n">
@@ -17339,7 +17331,7 @@
       <c r="E148" s="2" t="inlineStr"/>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (JUMP-POST) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G148" s="2" t="n">
@@ -17392,7 +17384,7 @@
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: housing (OPTO-8) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G149" s="3" t="n">
@@ -17445,11 +17437,11 @@
       <c r="E150" s="2" t="inlineStr"/>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (BATT-POS) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G150" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -17460,7 +17452,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
@@ -17498,11 +17490,11 @@
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (ENG-GND-RING) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G151" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
@@ -17513,7 +17505,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
       <c r="L151" s="3" t="inlineStr"/>
@@ -17551,11 +17543,11 @@
       <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EA) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G152" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -17566,7 +17558,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
@@ -17604,11 +17596,11 @@
       <c r="E153" s="3" t="inlineStr"/>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-EB) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G153" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
@@ -17619,7 +17611,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
       <c r="L153" s="3" t="inlineStr"/>
@@ -17657,11 +17649,11 @@
       <c r="E154" s="2" t="inlineStr"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-ID) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
@@ -17672,7 +17664,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
@@ -17710,7 +17702,7 @@
       <c r="E155" s="3" t="inlineStr"/>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (GND-IG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G155" s="3" t="n">
@@ -17763,7 +17755,7 @@
       <c r="E156" s="2" t="inlineStr"/>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (STARTER-TRIGGER) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G156" s="2" t="n">
@@ -17816,11 +17808,11 @@
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AC-BTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G157" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
@@ -17831,7 +17823,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K157" s="3" t="inlineStr"/>
       <c r="L157" s="3" t="inlineStr"/>
@@ -17869,11 +17861,11 @@
       <c r="E158" s="2" t="inlineStr"/>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ALT-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
@@ -17884,7 +17876,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
@@ -17922,11 +17914,11 @@
       <c r="E159" s="3" t="inlineStr"/>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G159" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
@@ -17937,7 +17929,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K159" s="3" t="inlineStr"/>
       <c r="L159" s="3" t="inlineStr"/>
@@ -17975,11 +17967,11 @@
       <c r="E160" s="2" t="inlineStr"/>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -17990,7 +17982,7 @@
         <v>0</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr"/>
@@ -18028,7 +18020,7 @@
       <c r="E161" s="3" t="inlineStr"/>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-AT-GND-C) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G161" s="3" t="n">
@@ -18081,7 +18073,7 @@
       <c r="E162" s="2" t="inlineStr"/>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G162" s="2" t="n">
@@ -18134,7 +18126,7 @@
       <c r="E163" s="3" t="inlineStr"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G163" s="3" t="n">
@@ -18187,7 +18179,7 @@
       <c r="E164" s="2" t="inlineStr"/>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-ENG-BLOCK-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G164" s="2" t="n">
@@ -18240,7 +18232,7 @@
       <c r="E165" s="3" t="inlineStr"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-RTN) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G165" s="3" t="n">
@@ -18293,7 +18285,7 @@
       <c r="E166" s="2" t="inlineStr"/>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-EVAP-TEMP) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G166" s="2" t="n">
@@ -18346,7 +18338,7 @@
       <c r="E167" s="3" t="inlineStr"/>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-RL-GND-BL) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G167" s="3" t="n">
@@ -18399,7 +18391,7 @@
       <c r="E168" s="2" t="inlineStr"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G168" s="2" t="n">
@@ -18452,7 +18444,7 @@
       <c r="E169" s="3" t="inlineStr"/>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-2) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G169" s="3" t="n">
@@ -18505,7 +18497,7 @@
       <c r="E170" s="2" t="inlineStr"/>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
+          <t>part number not confirmed yet: lug / terminal (T-STARTER-B-3) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G170" s="2" t="n">
@@ -18558,22 +18550,22 @@
       <c r="E171" s="3" t="inlineStr"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-FP-GND) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G171" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I171" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J171" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K171" s="3" t="inlineStr"/>
       <c r="L171" s="3" t="inlineStr"/>
@@ -18587,7 +18579,7 @@
       </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
-          <t>OPEN-ITEMS row 140</t>
+          <t>no maker document in the repo yet; never guessed</t>
         </is>
       </c>
     </row>
@@ -18604,22 +18596,18 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-1/2-2.0-9</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr"/>
       <c r="E172" s="2" t="inlineStr"/>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>part number not confirmed yet: lug / terminal (T-TRUNK-NEG) (check_wiring.py --tbd)</t>
         </is>
       </c>
       <c r="G172" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
@@ -18630,27 +18618,23 @@
         <v>0</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr"/>
       <c r="N172" s="2" t="inlineStr"/>
-      <c r="O172" s="2" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O172" s="2" t="inlineStr"/>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q172" s="2" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
+          <t>no maker document in the repo yet; never guessed</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -18665,53 +18649,45 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/16-2.0-9</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr"/>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>shielded cable, part number not confirmed: CAB-CAN-CLU, CAB-CAN-CSB, CAB-CAN-ECU, CAB-CAN-RD, CAB-CANBH-BC, CAB-ETBM-AE, CAB-LAMCAN-BE</t>
         </is>
       </c>
       <c r="G173" s="3" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I173" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J173" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="K173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L173" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K173" s="3" t="inlineStr"/>
+      <c r="L173" s="3" t="inlineStr"/>
       <c r="M173" s="3" t="inlineStr"/>
       <c r="N173" s="3" t="inlineStr"/>
-      <c r="O173" s="3" t="inlineStr">
-        <is>
-          <t>not priced (Dan)</t>
-        </is>
-      </c>
+      <c r="O173" s="3" t="inlineStr"/>
       <c r="P173" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
-        </is>
-      </c>
-      <c r="Q173" s="3" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q173" s="3" t="inlineStr">
+        <is>
+          <t>OPEN-ITEMS row 140</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -18726,7 +18702,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>TMS-SCE-3/8-2.0-9</t>
+          <t>TMS-SCE-1/2-2.0-9</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -18737,11 +18713,11 @@
       <c r="E174" s="2" t="inlineStr"/>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 12.7 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G174" s="2" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
@@ -18752,7 +18728,7 @@
         <v>0</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>0</v>
@@ -18787,22 +18763,22 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>W12S</t>
+          <t>TMS-SCE-3/16-2.0-9</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Deutsch (TE Connectivity)</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr"/>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 4.8 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G175" s="3" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
@@ -18810,31 +18786,27 @@
         </is>
       </c>
       <c r="I175" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J175" s="3" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="K175" s="3" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="L175" s="3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M175" s="5" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr"/>
       <c r="N175" s="3" t="inlineStr"/>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P175" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q175" s="3" t="inlineStr"/>
@@ -18852,26 +18824,22 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>W2P</t>
+          <t>TMS-SCE-3/8-2.0-9</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E176" s="2" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>TE Connectivity (Raychem)</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
+          <t>MARKER, HEAT SHRINK, PRINTABLE, TMS-SCE, WHITE, 3:1, 9.5 MM EXPANDED ID, 50 MM, THERMAL TRANSFER PRINT</t>
         </is>
       </c>
       <c r="G176" s="2" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
@@ -18882,28 +18850,24 @@
         <v>0</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="L176" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M176" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr"/>
       <c r="N176" s="2" t="inlineStr"/>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1, 2026-10-19</t>
+          <t>not priced (Dan)</t>
         </is>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key product page opened 2026-10-19</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr"/>
@@ -18921,26 +18885,22 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>W2S</t>
+          <t>W12S</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>✓ TE</t>
-        </is>
-      </c>
+          <t>Deutsch (TE Connectivity)</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr"/>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 12 POS, PLUG</t>
         </is>
       </c>
       <c r="G177" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
@@ -18948,31 +18908,31 @@
         </is>
       </c>
       <c r="I177" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J177" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="K177" s="3" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="L177" s="3" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="M177" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W2S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W12S/6566599</t>
         </is>
       </c>
       <c r="N177" s="3" t="inlineStr"/>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 3 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P177" s="3" t="inlineStr">
         <is>
-          <t>te.com page opened 2026-10-19</t>
+          <t>Digi-Key API 2026-10-20: 22279 in stock</t>
         </is>
       </c>
       <c r="Q177" s="3" t="inlineStr"/>
@@ -18990,12 +18950,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>W3S</t>
+          <t>W2P</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -19005,7 +18965,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 2-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G178" s="2" t="n">
@@ -19030,18 +18990,18 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-W3S.html</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W2P/6566600</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr"/>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
+          <t>Digi-Key qty 1, 2026-10-19</t>
         </is>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>Digi-Key product page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr"/>
@@ -19059,7 +19019,7 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>W6P</t>
+          <t>W2S</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
@@ -19074,11 +19034,11 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
+          <t>WEDGELOCK, DT, 2-WAY PLUG</t>
         </is>
       </c>
       <c r="G179" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
@@ -19089,28 +19049,28 @@
         <v>0</v>
       </c>
       <c r="J179" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K179" s="3" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="L179" s="3" t="n">
-        <v>0.4</v>
+        <v>1.43</v>
       </c>
       <c r="M179" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
+          <t>https://www.te.com/en/product-W2S.html</t>
         </is>
       </c>
       <c r="N179" s="3" t="inlineStr"/>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P179" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
+          <t>te.com page opened 2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="3" t="inlineStr"/>
@@ -19128,12 +19088,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>W6S</t>
+          <t>W3S</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Deutsch</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -19143,7 +19103,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
+          <t>WEDGELOCK, DT, 3 POS, PLUG</t>
         </is>
       </c>
       <c r="G180" s="2" t="n">
@@ -19161,25 +19121,25 @@
         <v>2</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="L180" s="2" t="n">
-        <v>0.42</v>
+        <v>0.26</v>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
+          <t>https://www.te.com/en/product-W3S.html</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr"/>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
+          <t>family price (W2P, Digi-Key qty 1, 2026-10-19)</t>
         </is>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr"/>
@@ -19197,7 +19157,7 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>W8S</t>
+          <t>W6P</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
@@ -19212,11 +19172,11 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY RECEPTACLE</t>
         </is>
       </c>
       <c r="G181" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
@@ -19227,28 +19187,28 @@
         <v>0</v>
       </c>
       <c r="J181" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K181" s="3" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="L181" s="3" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6P/6566692</t>
         </is>
       </c>
       <c r="N181" s="3" t="inlineStr"/>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P181" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+          <t>Digi-Key API 2026-10-20: 18695 in stock</t>
         </is>
       </c>
       <c r="Q181" s="3" t="inlineStr"/>
@@ -19266,7 +19226,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>WM-4S</t>
+          <t>W6S</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -19281,11 +19241,11 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 6-WAY PLUG</t>
         </is>
       </c>
       <c r="G182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
@@ -19296,28 +19256,28 @@
         <v>0</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="L182" s="2" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W6S/6566605</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr"/>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+          <t>Digi-Key API 2026-10-20: 50335 in stock</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr"/>
@@ -19335,12 +19295,12 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>WM-6S</t>
+          <t>W8S</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>Deutsch</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -19350,7 +19310,7 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
+          <t>WEDGELOCK, DT, 8 POS, PLUG</t>
         </is>
       </c>
       <c r="G183" s="3" t="n">
@@ -19368,14 +19328,14 @@
         <v>1</v>
       </c>
       <c r="K183" s="3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="L183" s="3" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/W8S/9744670</t>
         </is>
       </c>
       <c r="N183" s="3" t="inlineStr"/>
@@ -19386,13 +19346,196 @@
       </c>
       <c r="P183" s="3" t="inlineStr">
         <is>
+          <t>Digi-Key API 2026-10-20: 2460 in stock</t>
+        </is>
+      </c>
+      <c r="Q183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>All harnesses (master wire list)</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>WM-4S</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>WEDGELOCK, DTM, 4 POS, PLUG</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-4S/6566615</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key API 2026-10-20: 12271 in stock</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>All harnesses (master wire list)</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>WM-6S</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Deutsch</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="inlineStr">
+        <is>
+          <t>WEDGELOCK, DTM, 6 POS, PLUG</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" s="3" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L185" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M185" s="5" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/WM-6S/6566617</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr"/>
+      <c r="O185" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Box), 2026-10-20</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
           <t>Digi-Key API 2026-10-20: 2478 in stock</t>
         </is>
       </c>
-      <c r="Q183" s="3" t="inlineStr"/>
+      <c r="Q185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>All harnesses (master wire list)</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr"/>
+      <c r="O186" s="2" t="inlineStr"/>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q183"/>
+  <autoFilter ref="A1:Q186"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -19418,7 +19561,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId28"/>
@@ -19488,15 +19631,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M175" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M176" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M177" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M178" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M179" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M180" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M181" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M182" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M183" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M184" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M185" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -19509,7 +19652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19878,12 +20021,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>354404</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>maker page read 2026-10-25 (one ships with each Lowdoller sensor)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -19900,12 +20043,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -19922,7 +20065,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -19944,7 +20087,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -19966,7 +20109,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -19988,17 +20131,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20153,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>90980-10942</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -20032,7 +20175,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>90980-11143</t>
+          <t>90980-10942</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -20054,7 +20197,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>90980-11143</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -20076,7 +20219,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>90980-11250</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -20098,7 +20241,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>90980-12068</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -20120,7 +20263,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>90980-12068</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -20130,7 +20273,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
+          <t>OEM Toyota part: buy from a Toyota parts dealer; confirm it is not already on the car</t>
         </is>
       </c>
     </row>
@@ -20142,7 +20285,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -20164,7 +20307,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -20186,7 +20329,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>BC-2-RED</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -20208,17 +20351,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>pick a welding / battery cable supplier (no PN exists for this drawn wire); recommend ProWire USA</t>
         </is>
       </c>
     </row>
@@ -20230,7 +20373,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>HD36-24-33SE</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -20252,12 +20395,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LP-16-J05PE-02-001</t>
+          <t>HD36-24-33SE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -20274,7 +20417,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-10-9</t>
+          <t>LP-16-J05PE-02-001</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -20284,7 +20427,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
+          <t>I find and validate a maker page or approved-supplier listing</t>
         </is>
       </c>
     </row>
@@ -20296,7 +20439,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-14-4</t>
+          <t>M22759/16-10-9</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -20318,7 +20461,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-16-4</t>
+          <t>M22759/16-14-4</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -20340,7 +20483,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>M22759/16-18-4</t>
+          <t>M22759/16-16-4</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -20362,7 +20505,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>M22759/16-6-2</t>
+          <t>M22759/16-18-4</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -20384,7 +20527,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>M22759/16-6-2</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -20394,7 +20537,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>I find and validate a maker page or approved-supplier listing</t>
+          <t>buy by the foot (Wings and Wheels / Flight Store); confirm the supplier and the colour code page</t>
         </is>
       </c>
     </row>
@@ -21498,8 +21641,96 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Wire harness</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>in kit 354404</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>I find and validate a maker page or approved-supplier listing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D90"/>
+  <autoFilter ref="A1:D94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/sourcing/PROJECT-BOM.xlsx
+++ b/docs/sourcing/PROJECT-BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To do" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mechanical assemblies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Wire harness" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="To do" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mechanical assemblies'!$A$1:$Q$116</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$186</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wire harness'!$A$1:$Q$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'To do'!$A$1:$D$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>4768.97</v>
+        <v>4637.41</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>9</v>
@@ -562,16 +562,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5206.83</v>
+        <v>5075.27</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>24</v>
@@ -8162,7 +8162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q186"/>
+  <dimension ref="A1:Q180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8470,7 +8470,11 @@
           <t>Digi-Key API 2026-10-20: 45820 in stock</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -8567,7 +8571,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -8575,17 +8579,15 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.41</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>25.01</v>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="4" t="inlineStr">
         <is>
           <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/0462-201-16141/7200924</t>
@@ -8602,7 +8604,11 @@
           <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -8898,10 +8904,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="inlineStr"/>
@@ -8913,7 +8919,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8993,22 +9003,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>10k 1/4W</t>
+          <t>114017</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 10 KOHM, 5 PCT, 1/4 W</t>
+          <t>PLUG, SEALING, CAVITY, SIZE 16, WHITE</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -9019,28 +9029,28 @@
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.1</v>
+        <v>12.76</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT10K0/1741265</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114017-ZZ/6566679</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT10K0</t>
+          <t>Digi-Key qty 58 (Box), 2026-10-20; listed as 114017-ZZ</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 568040 in stock</t>
+          <t>Digi-Key API 2026-10-20: 267877 in stock</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr"/>
@@ -9058,7 +9068,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>114017</t>
+          <t>114018-ZZ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9069,11 +9079,11 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PLUG, SEALING, CAVITY, SIZE 16, WHITE</t>
+          <t>PLUG, SEALING, CAVITY, SIZE 8, WHITE</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -9081,31 +9091,29 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>12.76</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114017-ZZ/6566679</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114018-ZZ/9923101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 58 (Box), 2026-10-20; listed as 114017-ZZ</t>
+          <t>Digi-Key qty 8 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 267877 in stock</t>
+          <t>Digi-Key API 2026-10-20: 6856 in stock</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -9123,7 +9131,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>114018-ZZ</t>
+          <t>114019-ZZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -9134,11 +9142,11 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>PLUG, SEALING, CAVITY, SIZE 8, WHITE</t>
+          <t>PLUG, SEALING, CAVITY, SIZE 4, WHITE</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -9146,29 +9154,29 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.75</v>
+        <v>1.82</v>
       </c>
       <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114018-ZZ/9923101</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114019-ZZ/6566680</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 8 (Box), 2026-10-20</t>
+          <t>Digi-Key qty 4 (Box), 2026-10-20</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 6856 in stock</t>
+          <t>Digi-Key API 2026-10-20: 2935 in stock</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr"/>
@@ -9186,22 +9194,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>114019-ZZ</t>
+          <t>12052641</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>TE DEUTSCH</t>
+          <t>Aptiv (Delphi) Metri-Pack 150</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>PLUG, SEALING, CAVITY, SIZE 4, WHITE</t>
+          <t>CONNECTOR, 2 POS, SEALED</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -9209,29 +9217,31 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+        <v>0.89</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0.89</v>
+      </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/114019-ZZ/6566680</t>
+          <t>https://www.customconnectorkits.com/products/12052641?variant=45536631554366</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 4 (Box), 2026-10-20</t>
+          <t>Custom Connector Kits, 2026-10-20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2935 in stock</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -9249,22 +9259,22 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>12052641</t>
+          <t>12084200</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Aptiv (Delphi) Metri-Pack 150</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, 2 POS, SEALED</t>
+          <t>CONTACT, SOCKET, CRIMP, METRI-PACK 150.2, TIN, CABLE-SEALED, 0.35-0.5 MM2 (22-20 AWG)</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -9275,20 +9285,24 @@
         <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.89</v>
+        <v>0.16</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.89</v>
+        <v>0.32</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12052641?variant=45536631554366</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+          <t>https://www.customconnectorkits.com/products/12084200-l?variant=45536283525438</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ebay.de/itm/145990327082</t>
+        </is>
+      </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
           <t>Custom Connector Kits, 2026-10-20</t>
@@ -9299,7 +9313,11 @@
           <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>confirm 150 vs 150.2 against Aptiv drawing</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9314,18 +9332,18 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12084200</t>
+          <t>120R 1/4W</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Generic</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, METRI-PACK 150.2, TIN, CABLE-SEALED, 0.35-0.5 MM2 (22-20 AWG)</t>
+          <t>RESISTOR, FIXED, METAL FILM, 120 OHM, 1 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G18" s="2" t="n">
@@ -9343,36 +9361,28 @@
         <v>2</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12084200-l?variant=45536283525438</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ebay.de/itm/145990327082</t>
-        </is>
-      </c>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RNMF14FTC120R/2617285</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>Digi-Key qty 2 (Cut Tape (CT)), 2026-10-20; listed as RNMF14FTC120R</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>confirm 150 vs 150.2 against Aptiv drawing</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 124869 in stock</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -9387,22 +9397,22 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>120R 1/4W</t>
+          <t>12191819</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Generic</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 120 OHM, 1 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -9413,28 +9423,28 @@
         <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/RNMF14FTC120R/2617285</t>
+          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Cut Tape (CT)), 2026-10-20; listed as RNMF14FTC120R</t>
+          <t>Custom Connector Kits, 2026-10-20</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 124869 in stock</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr"/>
@@ -9452,7 +9462,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12191819</t>
+          <t>13519047</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -9463,11 +9473,11 @@
       <c r="E20" s="2" t="inlineStr"/>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, TIN, SEALED, 18-16 AWG, CABLE OD 1.70-2.25 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -9475,20 +9485,18 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0.72</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/12191819-l?variant=45536512966974</t>
+          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -9502,7 +9510,11 @@
           <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -9517,7 +9529,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>13519047</t>
+          <t>15326426</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -9528,11 +9540,11 @@
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 3 POS, SEALED, SOCKET CONTACTS</t>
+          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -9540,20 +9552,18 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.95</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/13519047?variant=45536514539838</t>
+          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
@@ -9567,7 +9577,11 @@
           <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
-      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -9582,7 +9596,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>15326426</t>
+          <t>15419715</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -9593,11 +9607,11 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, GT 150, GOLD, SEALED, 0.35-0.50 MM2 (22-20 AWG), CABLE OD 1.20-1.85 MM</t>
+          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -9608,17 +9622,17 @@
         <v>0</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.45</v>
+        <v>1.09</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>3.15</v>
+        <v>4.36</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15326426-l?variant=48621504332094</t>
+          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
@@ -9647,22 +9661,22 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>15419715</t>
+          <t>1N5822</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, GT 150, 2 POS, SEALED, GRAY, USCAR / EV6</t>
+          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -9673,28 +9687,28 @@
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.09</v>
+        <v>0.71</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.36</v>
+        <v>0.71</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>https://www.customconnectorkits.com/products/15419715?variant=45536627917118</t>
+          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr"/>
@@ -9712,18 +9726,18 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1N5822</t>
+          <t>1k 1/4W</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>DIODE, SCHOTTKY, RECTIFIER, 40 V, 3 A, DO-201AD AXIAL</t>
+          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G24" s="2" t="n">
@@ -9741,25 +9755,25 @@
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0.71</v>
+        <v>0.1</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/taiwan-semiconductor-corporation/1N5822/7366597</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 2377 in stock</t>
+          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
@@ -9777,22 +9791,22 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>1k 1/4W</t>
+          <t>3-1447221-3</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 1 KOHM, 5 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -9800,31 +9814,29 @@
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT1K00/1741314</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT1K00</t>
+          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 615946 in stock</t>
+          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr"/>
@@ -9842,22 +9854,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2.2k 1/4W 1%</t>
+          <t>3-1447221-4</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 2.2 KOHM, 1 PCT, 1/4 W</t>
+          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -9865,19 +9877,29 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.28</v>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
@@ -9895,22 +9917,22 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>3-1447221-3</t>
+          <t>301A011-25-0</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.75-0.85 MM2 (18 AWG)</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -9918,29 +9940,31 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
+        <v>27.58</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>82.73999999999999</v>
+      </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/3-1447221-3/2135580</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 18 (Cut Tape (CT)), 2026-10-20</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10959 in stock</t>
+          <t>Digi-Key API 2026-10-20: 236 in stock</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr"/>
@@ -9958,22 +9982,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>3-1447221-4</t>
+          <t>301A022-25-0</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CONTACT, SOCKET, CRIMP, SUPERSEAL 1.0, GOLD, 0.5 MM2 (20 AWG), INSUL 1.6-2.2 MM</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -9981,29 +10005,31 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+        <v>40.77</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>81.54000000000001</v>
+      </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/wec/3-1447221-4/29355733</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 7000 (Tape &amp; Reel (TR)), 2026-10-20; reel only at Digi-Key (min 7000), unit price is the reel price</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 10000 in stock</t>
+          <t>Digi-Key API 2026-10-20: 151 in stock</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
@@ -10021,22 +10047,22 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3.9k 1/4W</t>
+          <t>301A028-25-0</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 3.9 KOHM, 5 PCT, 1/4 W</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -10047,28 +10073,28 @@
         <v>0</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.1</v>
+        <v>37.65</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1</v>
+        <v>75.3</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT3K90/1741386</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT3K90</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 44589 in stock</t>
+          <t>Digi-Key API 2026-10-20: 94 in stock</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr"/>
@@ -10086,7 +10112,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>301A011-25-0</t>
+          <t>342A012-25-0</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -10097,11 +10123,11 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -10112,28 +10138,28 @@
         <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>27.58</v>
+        <v>35.59</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>82.73999999999999</v>
+        <v>427.08</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A011-25-0/2394181</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 236 in stock</t>
+          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
@@ -10151,7 +10177,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>301A022-25-0</t>
+          <t>342A024-25-0</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -10162,11 +10188,11 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
@@ -10177,28 +10203,28 @@
         <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>40.77</v>
+        <v>50.66</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>81.54000000000001</v>
+        <v>557.26</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A022-25-0/2394178</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 151 in stock</t>
+          <t>Digi-Key API 2026-10-20: 140 in stock</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr"/>
@@ -10216,7 +10242,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>301A028-25-0</t>
+          <t>342A034-25-0</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -10227,11 +10253,11 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, T, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 20/10.2 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -10242,28 +10268,28 @@
         <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>37.65</v>
+        <v>75.67</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>75.3</v>
+        <v>605.36</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/301A028-25-0/3318081</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 94 in stock</t>
+          <t>Digi-Key API 2026-10-20: 57 in stock</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -10281,7 +10307,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>342A012-25-0</t>
+          <t>342A048-25-0</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -10292,11 +10318,11 @@
       <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.9 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
@@ -10307,28 +10333,28 @@
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>35.59</v>
+        <v>117.77</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>427.08</v>
+        <v>235.54</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A012-25-0/2394240</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 12 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: not stocked at Digi-Key now</t>
+          <t>Digi-Key API 2026-10-20: 46 in stock</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr"/>
@@ -10346,22 +10372,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>342A024-25-0</t>
+          <t>354404</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Lowdoller Motorsports</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.7 X 6.6/3.6 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR KIT, PRESSURE / MAP SENSOR, 3 PIN, DELPHI GT150 (PLUG, PINS, SEALS)</t>
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -10369,34 +10395,30 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>50.66</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>557.26</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A024-25-0/2394208</t>
+          <t>https://lowdoller-motorsports.com/products/3-pin-connector-pins-and-grommets-for-pressure-sensor</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 11 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 140 in stock</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr"/>
+          <t>maker page read 2026-10-25 (one ships with each Lowdoller sensor)</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -10411,7 +10433,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>342A034-25-0</t>
+          <t>382A012-25-0</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -10422,11 +10444,11 @@
       <c r="E35" s="3" t="inlineStr"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.7 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.1 X 6.6/3.3 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
@@ -10437,28 +10459,28 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>75.67</v>
+        <v>31</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>605.36</v>
+        <v>124</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A034-25-0/2394180</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A012-25-0/2394192</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 8 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 57 in stock</t>
+          <t>Digi-Key API 2026-10-20: 380 in stock</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr"/>
@@ -10476,7 +10498,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>342A048-25-0</t>
+          <t>382A023-25-0</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10487,11 +10509,11 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 45 DEG BREAKOUT, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 55.6/26.9 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.4 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -10502,28 +10524,28 @@
         <v>0</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>117.77</v>
+        <v>46.9</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>235.54</v>
+        <v>140.7</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/342A048-25-0/2394190</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A023-25-0/2394201</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 2 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 46 in stock</t>
+          <t>Digi-Key API 2026-10-20: 152 in stock</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
@@ -10541,22 +10563,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>354404</t>
+          <t>382A034-25-0</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Lowdoller Motorsports</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr"/>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR KIT, PRESSURE / MAP SENSOR, 3 PIN, DELPHI GT150 (PLUG, PINS, SEALS)</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 38.6/18.0 X 26.9/12.4 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
@@ -10567,20 +10589,28 @@
         <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>93.31999999999999</v>
+      </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>https://lowdoller-motorsports.com/products/3-pin-connector-pins-and-grommets-for-pressure-sensor</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A034-25-0/2394193</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+        </is>
+      </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>maker page read 2026-10-25 (one ships with each Lowdoller sensor)</t>
+          <t>Digi-Key API 2026-10-20: 34 in stock</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr"/>
@@ -10598,22 +10628,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>382A012-25-0</t>
+          <t>4-1437290-0</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 13.2/6.1 X 6.6/3.3 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 1, SOCKET CONTACTS, BLUE</t>
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -10621,31 +10651,29 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>124</v>
-      </c>
+        <v>10.82</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A012-25-0/2394192</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-0/2054331</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key qty 4 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 380 in stock</t>
+          <t>Digi-Key API 2026-10-20: 1305 in stock</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
@@ -10663,22 +10691,22 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>382A023-25-0</t>
+          <t>4-1437290-1</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr"/>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/12.4 X 13.2/6.1 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 2, SOCKET CONTACTS, BLUE</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
@@ -10686,31 +10714,29 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>140.7</v>
-      </c>
+        <v>11.92</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A023-25-0/2394201</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-1/2329261</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 3 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Tube), 2026-10-20</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 152 in stock</t>
+          <t>Digi-Key API 2026-10-20: 506 in stock</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr"/>
@@ -10728,7 +10754,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>382A034-25-0</t>
+          <t>462A023-25-0</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10739,7 +10765,7 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, Y, 3 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 38.6/18.0 X 26.9/12.4 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>TRANSITION, MOULDED, HEAT SHRINK, 1 TO 3, 4 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.2 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G40" s="2" t="n">
@@ -10757,14 +10783,14 @@
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>72.52</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>93.31999999999999</v>
+        <v>72.52</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/382A034-25-0/2394193</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/462A023-25-0/2394175</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
@@ -10775,7 +10801,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 34 in stock</t>
+          <t>Digi-Key API 2026-10-20: 33 in stock</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
@@ -10793,18 +10819,18 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>4-1437290-0</t>
+          <t>470R 1/4W</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 1, SOCKET CONTACTS, BLUE</t>
+          <t>RESISTOR, FIXED, METAL FILM, 470 OHM, 5 PCT, 1/4 W</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
@@ -10816,29 +10842,31 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-0/2054331</t>
+          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT470R/1741440</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
+          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT470R</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 1305 in stock</t>
+          <t>Digi-Key API 2026-10-20: 327849 in stock</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr"/>
@@ -10856,18 +10884,18 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>4-1437290-1</t>
+          <t>52-45780</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>Longacre</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, RECEPTACLE, SUPERSEAL 1.0, 34 POS, CODE 2, SOCKET CONTACTS, BLUE</t>
+          <t>SWITCH, BATTERY DISCONNECT, 4 TERMINAL, 2 POLE, 175 A CONTINUOUS, 1000 A PEAK, 20 A AUXILIARY POLE, 6-36 V</t>
         </is>
       </c>
       <c r="G42" s="2" t="n">
@@ -10879,29 +10907,19 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>11.92</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-amp-connectors/4-1437290-1/2329261</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Tube), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 506 in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
@@ -10919,7 +10937,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>462A023-25-0</t>
+          <t>55A1811-20-9-9CS2275</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -10930,46 +10948,42 @@
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>TRANSITION, MOULDED, HEAT SHRINK, 1 TO 3, 4 BRANCHES, -25 FLUID RESISTANT ELASTOMER, BLACK, 26.9/13.2 X 13.2/6.9 MM SUPPLIED / RECOVERED, -75 TO 150 C</t>
+          <t>CABLE, SHIELDED, 1 CONDUCTOR, 20 AWG, WHITE, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>72.52</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>72.52</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/te-connectivity-aerospace-defense-and-marine/462A023-25-0/2394175</t>
+          <t>https://www.te.com/en/product-55A1811-20-9-9CS2275.html</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 33 in stock</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr"/>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>3 cable runs, 3.0 m + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -10984,57 +10998,53 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>470R 1/4W</t>
+          <t>55A1821-20-6/9-9</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>RESISTOR, FIXED, METAL FILM, 470 OHM, 5 PCT, 1/4 W</t>
+          <t>CABLE, SHIELDED, 2 CONDUCTOR TWISTED PAIR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0.1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>https://www.digikey.com/en/products/detail/stackpole-electronics-inc/CF14JT470R/1741440</t>
+          <t>https://www.te.com/en/product-55A1821-20-6-9-9.html</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>Digi-Key qty 1 (Cut Tape (CT)), 2026-10-20; listed as CF14JT470R</t>
-        </is>
-      </c>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Digi-Key API 2026-10-20: 327849 in stock</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr"/>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>5 cable runs, 3.1 m + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -11049,45 +11059,53 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>52-45780</t>
+          <t>55A1831-20-2/4/6-9</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Longacre</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>SWITCH, BATTERY DISCONNECT, 4 TERMINAL, 2 POLE, 175 A CONTINUOUS, 1000 A PEAK, 20 A AUXILIARY POLE, 6-36 V</t>
+          <t>CABLE, SHIELDED, 3 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
       <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.te.com/en/product-55A1831-20-2-4-6-9.html</t>
+        </is>
+      </c>
       <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q45" s="3" t="inlineStr"/>
+          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>6 cable runs, 5.2 m + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -11102,7 +11120,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>55A1811-20-9-9CS2275</t>
+          <t>55A1841-20-2/4/5/6-9</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -11113,11 +11131,11 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 1 CONDUCTOR, 20 AWG, WHITE, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CABLE, SHIELDED, 4 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -11128,13 +11146,13 @@
         <v>0</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-55A1811-20-9-9CS2275.html</t>
+          <t>https://www.te.com/en/product-55A1841-20-2-4-5-6-9.html</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
@@ -11146,7 +11164,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>3 cable runs, 3.0 m + 15% margin</t>
+          <t>4 cable runs, 4.9 m + 15% margin</t>
         </is>
       </c>
     </row>
@@ -11163,51 +11181,57 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>55A1821-20-6/9-9</t>
+          <t>8100-0461</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Sumitomo</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 2 CONDUCTOR TWISTED PAIR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CONTACT, SOCKET, CRIMP, SUMITOMO TS 090 (2.3 MM), TIN, 0.5-1.25 MM2 (20-16 AWG)</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K47" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-55A1821-20-6-9-9.html</t>
+          <t>https://www.customconnectorkits.com/products/8100-0461-l?variant=46049028800830</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>Custom Connector Kits, 2026-10-20</t>
+        </is>
+      </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>5 cable runs, 3.1 m + 15% margin</t>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
         </is>
       </c>
     </row>
@@ -11224,53 +11248,45 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>55A1831-20-2/4/6-9</t>
+          <t>90980-10341</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>CABLE, SHIELDED, 3 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
+          <t>CONNECTOR, PLUG, TOYOTA, ROUND, 3 POS</t>
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.te.com/en/product-55A1831-20-2-4-6-9.html</t>
-        </is>
-      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>6 cable runs, 5.2 m + 15% margin</t>
-        </is>
-      </c>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -11285,53 +11301,49 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>55A1841-20-2/4/5/6-9</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
+          <t>90980-10897</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>CABLE, SHIELDED, 4 CONDUCTOR, 20 AWG, TINNED COPPER BRAID, WHITE ETFE JACKET, 600 V, -65 TO 150 C</t>
-        </is>
-      </c>
+      <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>8.050000000000001</v>
+      </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t>https://www.te.com/en/product-55A1841-20-2-4-5-6-9.html</t>
+          <t>https://www.ksvlooms.com/products/toyota-lexus-90980-10897-8-pin-connector-kit?variant=29504109805610</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>te.com URL form, page NOT opened (te.com blocked the automated check): confirm</t>
-        </is>
-      </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>4 cable runs, 4.9 m + 15% margin</t>
-        </is>
-      </c>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -11346,22 +11358,14 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>8100-0461</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Sumitomo</t>
-        </is>
-      </c>
+          <t>90980-10942</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>CONTACT, SOCKET, CRIMP, SUMITOMO TS 090 (2.3 MM), TIN, 0.5-1.25 MM2 (20-16 AWG)</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -11372,28 +11376,16 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
-          <t>https://www.customconnectorkits.com/products/8100-0461-l?variant=46049028800830</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>Custom Connector Kits, 2026-10-20</t>
-        </is>
-      </c>
+      <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
@@ -11411,7 +11403,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>90980-10341</t>
+          <t>90980-11062</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -11422,11 +11414,11 @@
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA, ROUND, 3 POS</t>
+          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
@@ -11434,22 +11426,36 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>4.52</v>
+      </c>
       <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/2-way-connector-kit-for-toyota-lexus-90980-11062-water-temperature-sensor-22-18-awg?variant=11482559741994</t>
+        </is>
+      </c>
       <c r="N51" s="3" t="inlineStr"/>
-      <c r="O51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q51" s="3" t="inlineStr"/>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -11464,12 +11470,20 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>90980-10897</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr"/>
+          <t>90980-11143</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>CONNECTOR, PLUG, TOYOTA OVAL, 3 POS, SOCKET CONTACTS</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
@@ -11479,34 +11493,26 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" s="2" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="M52" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/toyota-lexus-90980-10897-8-pin-connector-kit?variant=29504109805610</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
-        </is>
-      </c>
+      <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr"/>
+          <t>NO LINK</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -11521,12 +11527,20 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>90980-10942</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr"/>
+          <t>90980-11250</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
       <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS (HOUSING CONNECTOR F), BACK-UP LIGHT SWITCH</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="n">
         <v>1</v>
       </c>
@@ -11536,10 +11550,10 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K53" s="3" t="inlineStr"/>
       <c r="L53" s="3" t="inlineStr"/>
@@ -11551,7 +11565,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>on hand (sensor plug / terminal: never a buy)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -11566,7 +11584,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>90980-11062</t>
+          <t>90980-11885</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11577,7 +11595,7 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS</t>
+          <t>CONNECTOR, PLUG, TOYOTA, 4 POS</t>
         </is>
       </c>
       <c r="G54" s="2" t="n">
@@ -11594,26 +11612,14 @@
       <c r="J54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K54" s="2" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t>https://www.ksvlooms.com/products/2-way-connector-kit-for-toyota-lexus-90980-11062-water-temperature-sensor-22-18-awg?variant=11482559741994</t>
-        </is>
-      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
-        </is>
-      </c>
+      <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+          <t>NO LINK</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr"/>
@@ -11631,20 +11637,12 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>90980-11143</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
+          <t>90980-12068</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>CONNECTOR, PLUG, TOYOTA OVAL, 3 POS, SOCKET CONTACTS</t>
-        </is>
-      </c>
+      <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="n">
         <v>1</v>
       </c>
@@ -11684,33 +11682,33 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>90980-11250</t>
+          <t>BC-1/0-BLK</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA, 2 POS, SOCKET CONTACTS (HOUSING CONNECTOR F), BACK-UP LIGHT SWITCH</t>
+          <t>CABLE, BATTERY, 1/0 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
@@ -11722,7 +11720,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>7.2 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -11737,33 +11739,33 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>90980-11885</t>
+          <t>BC-1/0-RED</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, TOYOTA, 4 POS</t>
+          <t>CABLE, BATTERY, 1/0 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K57" s="3" t="inlineStr"/>
       <c r="L57" s="3" t="inlineStr"/>
@@ -11775,7 +11777,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>5.8 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11790,25 +11796,33 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>90980-12068</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
+          <t>BC-2-RED</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>CABLE, BATTERY, 2 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>ft</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
@@ -11820,7 +11834,11 @@
           <t>NO LINK</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>2.4 m in the master + 15% margin</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -11835,7 +11853,7 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BC-1/0-BLK</t>
+          <t>BC-4-BLK</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -11846,11 +11864,11 @@
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 1/0 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>CABLE, BATTERY, 4 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
         </is>
       </c>
       <c r="G59" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
@@ -11861,7 +11879,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
@@ -11875,7 +11893,7 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>7.2 m in the master + 15% margin</t>
+          <t>3.2 m in the master + 15% margin</t>
         </is>
       </c>
     </row>
@@ -11892,49 +11910,57 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>BC-1/0-RED</t>
+          <t>D 261 205 358-01</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 1/0 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>CONNECTOR, PLUG, BOSCH MOTORSPORT KIT, 6 POS, SOCKET CONTACTS</t>
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/6-way-connector-kit-same-as-bosch-d261-205-358-01-23-20-awg?variant=40430818852899</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+        </is>
+      </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>5.8 m in the master + 15% margin</t>
-        </is>
-      </c>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -11949,47 +11975,59 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>BC-2-RED</t>
+          <t>DR-25-1-0-SP</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 2 AWG, RED, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 25.4 MM EXPANDED ID, 12.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>40.16</v>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/1-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737243683</t>
+        </is>
+      </c>
       <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr"/>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $6.12 per ft</t>
+        </is>
+      </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>2.4 m in the master + 15% margin</t>
+          <t>0.9 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12006,33 +12044,33 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>BC-4-BLK</t>
+          <t>DR-25-1-1/2-0-SP</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>CABLE, BATTERY, 4 AWG, BLACK, FINE-STRAND COPPER, SAE J1127 SGX 125 C OR EQUIV</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 38.1 MM EXPANDED ID, 19.0 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>ft</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
@@ -12041,12 +12079,12 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO LINK</t>
+          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>3.2 m in the master + 15% margin</t>
+          <t>1.2 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12063,49 +12101,49 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>D 261 205 358-01</t>
+          <t>DR-25-1/2-0-SP</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>TE Connectivity (Raychem)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR, PLUG, BOSCH MOTORSPORT KIT, 6 POS, SOCKET CONTACTS</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 12.7 MM EXPANDED ID, 6.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G63" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>4.3</v>
+        <v>14.24</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>4.3</v>
+        <v>113.92</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/6-way-connector-kit-same-as-bosch-d261-205-358-01-23-20-awg?variant=40430818852899</t>
+          <t>https://www.ksvlooms.com/products/1-2-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735736355</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; equivalent connector kit, not the OEM part: confirm it fits</t>
+          <t>KSV Looms, 2026-10-20; $4.34 per ft</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
@@ -12113,7 +12151,11 @@
           <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
-      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>7.0 m of bundle + 10 % cut / recovery margin</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12128,7 +12170,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1-0-SP</t>
+          <t>DR-25-1/4-0-SP</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -12139,11 +12181,11 @@
       <c r="E64" s="2" t="inlineStr"/>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 25.4 MM EXPANDED ID, 12.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 6.4 MM EXPANDED ID, 3.2 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -12154,23 +12196,23 @@
         <v>0</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>20.08</v>
+        <v>5.61</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>20.08</v>
+        <v>33.66</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/1-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737243683</t>
+          <t>https://www.ksvlooms.com/products/1-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735113763</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $6.12 per ft</t>
+          <t>KSV Looms, 2026-10-20; $1.71 per ft</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -12180,7 +12222,7 @@
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>0.8 m of bundle + 10 % cut / recovery margin</t>
+          <t>5.0 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12197,7 +12239,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1-1/2-0-SP</t>
+          <t>DR-25-3/16-0-SP</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -12208,11 +12250,11 @@
       <c r="E65" s="3" t="inlineStr"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 38.1 MM EXPANDED ID, 19.0 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
@@ -12223,21 +12265,33 @@
         <v>0</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-      <c r="L65" s="3" t="inlineStr"/>
-      <c r="M65" s="3" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
+        </is>
+      </c>
       <c r="N65" s="3" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr"/>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
+        </is>
+      </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>404: te.com URL form is not a product page (checked 2026-10-19); find the real page</t>
+          <t>vendor page read 2026-10-20 (products.json), in stock</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>1.3 m of bundle + 10 % cut / recovery margin</t>
+          <t>11.1 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12308,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>DR-25-1/2-0-SP</t>
+          <t>DR-25-3/4-0-SP</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -12265,11 +12319,11 @@
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 12.7 MM EXPANDED ID, 6.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 19.0 MM EXPANDED ID, 9.5 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -12280,23 +12334,23 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>14.24</v>
+        <v>14.99</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>99.68000000000001</v>
+        <v>89.94</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/1-2-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735736355</t>
+          <t>https://www.ksvlooms.com/products/3-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443737112611</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $4.34 per ft</t>
+          <t>KSV Looms, 2026-10-20; $4.57 per ft</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -12306,7 +12360,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>5.6 m of bundle + 10 % cut / recovery margin</t>
+          <t>4.9 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12323,7 +12377,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>DR-25-1/4-0-SP</t>
+          <t>DR-25-3/8-0-SP</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -12334,11 +12388,11 @@
       <c r="E67" s="3" t="inlineStr"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 6.4 MM EXPANDED ID, 3.2 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 9.53 MM EXPANDED ID, 4.8 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
         </is>
       </c>
       <c r="G67" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
@@ -12349,23 +12403,23 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>5.61</v>
+        <v>10.83</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>28.05</v>
+        <v>119.13</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/1-4-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735113763</t>
+          <t>https://www.ksvlooms.com/products/3-8-raychem-dr-25-yellow-label-heat-shrink-tubing?variant=40443735343139</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $1.71 per ft</t>
+          <t>KSV Looms, 2026-10-20; $3.30 per ft</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -12375,7 +12429,7 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>3.9 m of bundle + 10 % cut / recovery margin</t>
+          <t>9.5 m of bundle + 10 % cut / recovery margin</t>
         </is>
       </c>
     </row>
@@ -12392,61 +12446,61 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>DR-25-3/16-0-SP</t>
+          <t>DRB12-102PAE-L018</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+          <t>TE DEUTSCH</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>✓ TE</t>
+        </is>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>TUBING, HEAT SHRINK, DR-25, BLACK, 2:1, 4.8 MM EXPANDED ID, 2.4 MM RECOVERED ID, FLUID RESISTANT ELASTOMER, -75 TO 150 C</t>
+          <t>CONNECTOR, RECEPTACLE, DRB, 102 POS, PIN CONTACTS, E SEAL, A KEY, WIRE ROUTER, FLANGE MOUNT</t>
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>ea</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5.54</v>
+        <v>55.13</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>72.02</v>
+        <v>55.13</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>https://www.ksvlooms.com/products/3-16-raychem-dr-25-yellow-label-heat-shrink-tubing-per-foot?variant=40443733803043</t>
+          <t>https://www.digikey.com/en/products/detail/te-connectivity-deutsch-ict-connectors/DRB12-102PAE-L018/10461602</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>KSV Looms, 2026-10-20; $1.69 per ft</t>
+          <t>Digi-Key qty 1 (Bulk), 2026-10-20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>vendor page read 2026-10-20 (products.json), in stock</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>11.6 m of bundle + 10 % cut / recovery margin</t>
-        </is>
-      </c>
+          <t>Digi-Key API 2026-10-20: 61 in stock</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -12461,61 +12515,57 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>DR-25-3/4-0-SP</t>
+          <t>DRB16-102SAE-L018</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>TE Connectivity (Raychem)</t>
+          <t>TE DEUTSCH</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr">
        